--- a/tame_output/ON/bt/strategyON_20240623.xlsx
+++ b/tame_output/ON/bt/strategyON_20240623.xlsx
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310979</v>
+        <v>3.284619513310978</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006531</v>
+        <v>3.30584953900653</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232413</v>
+        <v>3.747702660232412</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436229</v>
+        <v>3.766317079436228</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.78468452131195</v>
+        <v>3.784684521311949</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097245</v>
+        <v>3.800829354097244</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017773</v>
+        <v>3.789311112017772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883074</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074785</v>
+        <v>3.798814771074783</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242296</v>
+        <v>3.797694884242294</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367687</v>
+        <v>3.821593509367685</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879968</v>
+        <v>3.822326997879967</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502341</v>
+        <v>3.84861662650234</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675943</v>
+        <v>3.818668951675941</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539954</v>
+        <v>3.843274527539952</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496263</v>
+        <v>3.845047386496261</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577</v>
+        <v>3.791273551576998</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942104</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674516</v>
+        <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430697</v>
+        <v>3.729146398430695</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003604</v>
+        <v>3.743220196003602</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508372</v>
+        <v>3.71417913950837</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417706</v>
+        <v>3.710906731417705</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205903</v>
+        <v>3.746042526205901</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225448</v>
+        <v>3.765024323225446</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111295</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264164</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316048</v>
+        <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803192</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809499</v>
+        <v>3.733390600809497</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560425</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
@@ -46349,7 +46349,7 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.72107719547274</v>
+        <v>3.721077195472738</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
@@ -46372,7 +46372,7 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798539</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
@@ -46395,7 +46395,7 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498867</v>
+        <v>3.689597840498865</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
@@ -46418,7 +46418,7 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705327</v>
+        <v>3.643069621705325</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
@@ -46441,7 +46441,7 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729271</v>
+        <v>3.68271631072927</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
@@ -46464,7 +46464,7 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190771</v>
+        <v>3.733012441190769</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
@@ -46487,7 +46487,7 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913428</v>
+        <v>3.741174069913426</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
@@ -46510,7 +46510,7 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532489</v>
+        <v>3.751147197532487</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
@@ -46533,7 +46533,7 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793906</v>
+        <v>3.741328448793904</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
@@ -46556,7 +46556,7 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011239</v>
+        <v>3.750729377011237</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
@@ -46579,7 +46579,7 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982233</v>
+        <v>3.716991718982231</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
@@ -46602,7 +46602,7 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509542</v>
+        <v>3.737026608509541</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
@@ -46625,7 +46625,7 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760813</v>
+        <v>3.702309454760811</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
@@ -46648,7 +46648,7 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815456</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
@@ -46671,7 +46671,7 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378102</v>
+        <v>3.7095104433781</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
@@ -46694,7 +46694,7 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131253</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
@@ -46717,7 +46717,7 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067869</v>
+        <v>3.722447362067867</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
@@ -46740,7 +46740,7 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789125</v>
+        <v>3.787425580789124</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
@@ -46763,7 +46763,7 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519912</v>
+        <v>3.781501250519911</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
@@ -46786,7 +46786,7 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181174</v>
+        <v>3.802245929181173</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
@@ -47620,10 +47620,10 @@
         <v>3.522061802898103</v>
       </c>
       <c r="D2003" t="n">
-        <v>-4.007282413131334</v>
+        <v>-4.007248777609875</v>
       </c>
       <c r="E2003" t="n">
-        <v>1.918792413331822</v>
+        <v>1.918805867540406</v>
       </c>
       <c r="F2003" t="n">
         <v>0.003465461399837777</v>

--- a/tame_output/ON/bt/strategyON_20240623.xlsx
+++ b/tame_output/ON/bt/strategyON_20240623.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>60.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-11.7%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>50.4%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>75.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>37.2%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>61.9%</t>
+          <t>60.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.3%</t>
+          <t>30.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>36.1%</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>458.8%</t>
+          <t>459.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-562.3%</t>
+          <t>-562.5%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>19.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.2%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>120.7%</t>
+          <t>120.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-184.3%</t>
+          <t>-188.9%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.6%</t>
+          <t>-17.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>33.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-93.6%</t>
+          <t>-98.1%</t>
         </is>
       </c>
     </row>
@@ -46740,7 +46740,7 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789124</v>
+        <v>3.787425580789123</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519911</v>
+        <v>3.78150125051991</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.954497965677528</v>
+        <v>2.909559048546589</v>
       </c>
       <c r="D1966" t="n">
         <v>-4.487819796453111</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.159013622782537</v>
+        <v>1.114074705651597</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.3409289239641921</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.749940611299013</v>
+        <v>2.705001694168074</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181173</v>
+        <v>3.802245929181172</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.957291587209009</v>
+        <v>2.91235267007807</v>
       </c>
       <c r="D1967" t="n">
         <v>-4.589834478984332</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.121001371301529</v>
+        <v>1.07606245417059</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.3409289239641921</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.752734232830494</v>
+        <v>2.707795315699555</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394734</v>
+        <v>3.805608985394732</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.957953935600667</v>
+        <v>2.913015018469728</v>
       </c>
       <c r="D1968" t="n">
         <v>-4.583681772931548</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.124124802114301</v>
+        <v>1.079185884983362</v>
       </c>
       <c r="F1968" t="n">
         <v>-0.3347762179114078</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.757088204853823</v>
+        <v>2.712149287722884</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.798239794890611</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.957034412340778</v>
+        <v>2.912095495209838</v>
       </c>
       <c r="D1969" t="n">
         <v>-4.600491071082049</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.116481559594211</v>
+        <v>1.071542642463271</v>
       </c>
       <c r="F1969" t="n">
         <v>-0.3515855160619094</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.746083102703632</v>
+        <v>2.701144185572693</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798428</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
-        <v>3.023369966137599</v>
+        <v>2.978431049006659</v>
       </c>
       <c r="D1970" t="n">
         <v>-4.538193072305927</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.20773631290148</v>
+        <v>1.162797395770541</v>
       </c>
       <c r="F1970" t="n">
         <v>-0.3515855160619094</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.812418656500453</v>
+        <v>2.767479739369514</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992195</v>
+        <v>3.848729139992193</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.731950838526997</v>
+        <v>2.687011921396057</v>
       </c>
       <c r="D1971" t="n">
         <v>-4.336402874640769</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9970332643569417</v>
+        <v>0.9520943472260024</v>
       </c>
       <c r="F1971" t="n">
         <v>-0.153567323892755</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.639810444191344</v>
+        <v>2.594871527060405</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852425</v>
+        <v>3.841444817852423</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.802241070849172</v>
+        <v>2.757302153718233</v>
       </c>
       <c r="D1972" t="n">
         <v>-4.276512192998176</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.091279769336154</v>
+        <v>1.046340852205215</v>
       </c>
       <c r="F1972" t="n">
         <v>-0.09367664225016153</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.746035085499075</v>
+        <v>2.701096168368136</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.81906330031955</v>
+        <v>3.819063300319548</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.816868806965215</v>
+        <v>2.771929889834276</v>
       </c>
       <c r="D1973" t="n">
         <v>-4.37425273762315</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.066811287602208</v>
+        <v>1.021872370471269</v>
       </c>
       <c r="F1973" t="n">
         <v>-0.1095659203831417</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.751129254735331</v>
+        <v>2.706190337604391</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489388</v>
+        <v>3.831819032489387</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.815404787789887</v>
+        <v>2.770465870658948</v>
       </c>
       <c r="D1974" t="n">
         <v>-4.55059049774608</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9948121643777079</v>
+        <v>0.9498732472467686</v>
       </c>
       <c r="F1974" t="n">
         <v>-0.2859036805060711</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.643862579486245</v>
+        <v>2.598923662355305</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397798</v>
+        <v>3.836411672397796</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.813896405829816</v>
+        <v>2.768957488698876</v>
       </c>
       <c r="D1975" t="n">
         <v>-4.474168451314153</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.023872600990407</v>
+        <v>0.978933683859468</v>
       </c>
       <c r="F1975" t="n">
         <v>-0.2859036805060711</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.642354197526173</v>
+        <v>2.597415280395234</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024966</v>
+        <v>3.836023391024964</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.813759273265252</v>
+        <v>2.768820356134313</v>
       </c>
       <c r="D1976" t="n">
         <v>-4.429795319675584</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.041484721081271</v>
+        <v>0.9965458039503317</v>
       </c>
       <c r="F1976" t="n">
         <v>-0.2415305488675025</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.668840943944751</v>
+        <v>2.623902026813811</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863226</v>
+        <v>3.821591150863224</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.813759273265252</v>
+        <v>2.768820356134313</v>
       </c>
       <c r="D1977" t="n">
         <v>-4.421841349380812</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.04466630919918</v>
+        <v>0.9997273920682406</v>
       </c>
       <c r="F1977" t="n">
         <v>-0.2415305488675025</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.668840943944751</v>
+        <v>2.623902026813811</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947585</v>
+        <v>3.833040181947583</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.820141030293057</v>
+        <v>2.775202113162117</v>
       </c>
       <c r="D1978" t="n">
         <v>-4.374185618819756</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.070110358451407</v>
+        <v>1.025171441320468</v>
       </c>
       <c r="F1978" t="n">
         <v>-0.1938748183064469</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.703816139309189</v>
+        <v>2.65887722217825</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326876</v>
+        <v>3.822707244326875</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.825033403667781</v>
+        <v>2.780094486536842</v>
       </c>
       <c r="D1979" t="n">
         <v>-4.24650130902546</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.12607645574385</v>
+        <v>1.081137538612911</v>
       </c>
       <c r="F1979" t="n">
         <v>-0.06619050851215041</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.785319098560491</v>
+        <v>2.740380181429552</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314552</v>
+        <v>3.82883791131455</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.811788076143654</v>
+        <v>2.766849159012714</v>
       </c>
       <c r="D1980" t="n">
         <v>-4.307167899427849</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.088564492058766</v>
+        <v>1.043625574927827</v>
       </c>
       <c r="F1980" t="n">
         <v>-0.1478888252306841</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.723054781005243</v>
+        <v>2.678115863874304</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690027</v>
+        <v>3.816866067690025</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.815885778754282</v>
+        <v>2.770946861623343</v>
       </c>
       <c r="D1981" t="n">
         <v>-4.262329497819451</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.110597555312755</v>
+        <v>1.065658638181815</v>
       </c>
       <c r="F1981" t="n">
         <v>-0.1433453922858146</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.729878543382794</v>
+        <v>2.684939626251854</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674311</v>
+        <v>3.817961388674309</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.82004671838536</v>
+        <v>2.775107801254421</v>
       </c>
       <c r="D1982" t="n">
         <v>-4.363088133576449</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.074455040641033</v>
+        <v>1.029516123510094</v>
       </c>
       <c r="F1982" t="n">
         <v>-0.23217096101282</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.680744141777669</v>
+        <v>2.635805224646729</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826713779163221</v>
+        <v>3.826713779163219</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.825926320913197</v>
+        <v>2.780987403782258</v>
       </c>
       <c r="D1983" t="n">
         <v>-4.318885296490548</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.098015778003231</v>
+        <v>1.053076860872291</v>
       </c>
       <c r="F1983" t="n">
         <v>-0.1879681239269196</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.713145446557046</v>
+        <v>2.668206529426107</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022905</v>
+        <v>3.838228663022903</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.824336321382445</v>
+        <v>2.779397404251505</v>
       </c>
       <c r="D1984" t="n">
         <v>-4.355864324153991</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.081634167407101</v>
+        <v>1.036695250276162</v>
       </c>
       <c r="F1984" t="n">
         <v>-0.1509942221355891</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.733739788101092</v>
+        <v>2.688800870970153</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042139</v>
+        <v>3.863924114042137</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.875584086565484</v>
+        <v>2.830645169434545</v>
       </c>
       <c r="D1985" t="n">
         <v>-4.375922403018832</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.124858701044205</v>
+        <v>1.079919783913265</v>
       </c>
       <c r="F1985" t="n">
         <v>-0.1509942221355891</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.784987553284132</v>
+        <v>2.740048636153192</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865367715078282</v>
+        <v>3.86536771507828</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.874024791159738</v>
+        <v>2.829085874028798</v>
       </c>
       <c r="D1986" t="n">
         <v>-4.335991729840941</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.139271674909614</v>
+        <v>1.094332757778675</v>
       </c>
       <c r="F1986" t="n">
         <v>-0.1110635489576987</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.807386661785118</v>
+        <v>2.762447744654179</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232399</v>
+        <v>3.864518876232397</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.868973019398008</v>
+        <v>2.824034102267068</v>
       </c>
       <c r="D1987" t="n">
         <v>-4.284959637118414</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.154632740236895</v>
+        <v>1.109693823105955</v>
       </c>
       <c r="F1987" t="n">
         <v>-0.06003145623517075</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.832954145656906</v>
+        <v>2.788015228525966</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842576394162115</v>
+        <v>3.842576394162113</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.886160423490713</v>
+        <v>2.841221506359773</v>
       </c>
       <c r="D1988" t="n">
         <v>-4.219735455991208</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.197909816780482</v>
+        <v>1.152970899649543</v>
       </c>
       <c r="F1988" t="n">
         <v>0.005192724892034872</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.889276058425934</v>
+        <v>2.844337141294994</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840090220639818</v>
+        <v>3.840090220639817</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.882121395789993</v>
+        <v>2.837182478659054</v>
       </c>
       <c r="D1989" t="n">
         <v>-4.182308435920074</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.208841597108216</v>
+        <v>1.163902679977277</v>
       </c>
       <c r="F1989" t="n">
         <v>0.01044426292121653</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.888387953542723</v>
+        <v>2.843449036411784</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845198842749923</v>
+        <v>3.845198842749921</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.883378188121233</v>
+        <v>2.838439270990294</v>
       </c>
       <c r="D1990" t="n">
         <v>-4.202420091954782</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.202053727025573</v>
+        <v>1.157114809894634</v>
       </c>
       <c r="F1990" t="n">
         <v>0.02147160791863573</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.896261152872415</v>
+        <v>2.851322235741476</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.82869047939355</v>
+        <v>3.828690479393548</v>
       </c>
       <c r="C1991" t="n">
-        <v>3.043935959142444</v>
+        <v>2.998997042011505</v>
       </c>
       <c r="D1991" t="n">
         <v>-4.148675277527578</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.384109423817666</v>
+        <v>1.339170506686726</v>
       </c>
       <c r="F1991" t="n">
         <v>0.03153491735909769</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.062856909557903</v>
+        <v>3.017917992426963</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813251854714887</v>
+        <v>3.813251854714886</v>
       </c>
       <c r="C1992" t="n">
-        <v>3.164048868360261</v>
+        <v>3.119109951229322</v>
       </c>
       <c r="D1992" t="n">
         <v>-4.124883708921436</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.51373896047794</v>
+        <v>1.468800043347</v>
       </c>
       <c r="F1992" t="n">
         <v>0.05532648596523998</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.197244759939406</v>
+        <v>3.152305842808466</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814259761756013</v>
+        <v>3.814259761756011</v>
       </c>
       <c r="C1993" t="n">
-        <v>3.15575684437412</v>
+        <v>3.110817927243181</v>
       </c>
       <c r="D1993" t="n">
         <v>-4.098799624657627</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.515880570197322</v>
+        <v>1.470941653066383</v>
       </c>
       <c r="F1993" t="n">
         <v>0.05532648596523998</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.188952735953265</v>
+        <v>3.144013818822325</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803426852654187</v>
+        <v>3.803426852654185</v>
       </c>
       <c r="C1994" t="n">
-        <v>3.1539500399579</v>
+        <v>3.10901112282696</v>
       </c>
       <c r="D1994" t="n">
         <v>-4.09446532160058</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.515807487003921</v>
+        <v>1.470868569872981</v>
       </c>
       <c r="F1994" t="n">
         <v>0.2069765892844439</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.278135993528566</v>
+        <v>3.233197076397627</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796293177717118</v>
+        <v>3.796293177717116</v>
       </c>
       <c r="C1995" t="n">
-        <v>3.171504445684691</v>
+        <v>3.126565528553752</v>
       </c>
       <c r="D1995" t="n">
         <v>-4.085572860207296</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.536918877288025</v>
+        <v>1.491979960157086</v>
       </c>
       <c r="F1995" t="n">
         <v>0.2069765892844439</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.295690399255358</v>
+        <v>3.250751482124418</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794453975702627</v>
+        <v>3.794453975702625</v>
       </c>
       <c r="C1996" t="n">
-        <v>3.163359493089275</v>
+        <v>3.118420575958336</v>
       </c>
       <c r="D1996" t="n">
         <v>-4.254048977177174</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.461383477904658</v>
+        <v>1.416444560773719</v>
       </c>
       <c r="F1996" t="n">
         <v>0.1790287535678631</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.270776745229993</v>
+        <v>3.225837828099054</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795603100539969</v>
+        <v>3.795603100539967</v>
       </c>
       <c r="C1997" t="n">
-        <v>3.144629190277137</v>
+        <v>3.099690273146197</v>
       </c>
       <c r="D1997" t="n">
         <v>-3.556249448315591</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.721772986637153</v>
+        <v>1.676834069506214</v>
       </c>
       <c r="F1997" t="n">
         <v>0.1086806941974524</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.209837606795609</v>
+        <v>3.164898689664669</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784700379389899</v>
+        <v>3.784700379389897</v>
       </c>
       <c r="C1998" t="n">
-        <v>3.135293212774041</v>
+        <v>3.090354295643102</v>
       </c>
       <c r="D1998" t="n">
         <v>-3.533528344632438</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.721525450607319</v>
+        <v>1.676586533476379</v>
       </c>
       <c r="F1998" t="n">
         <v>0.1086806941974524</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.200501629292513</v>
+        <v>3.155562712161574</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783234730534937</v>
+        <v>3.783234730534935</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.29419933862521</v>
+        <v>3.249260421494271</v>
       </c>
       <c r="D1999" t="n">
         <v>-3.673820944169631</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.824314536643611</v>
+        <v>1.779375619512672</v>
       </c>
       <c r="F1999" t="n">
         <v>-0.03161190533974023</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.275232195421367</v>
+        <v>3.230293278290427</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779962759401675</v>
+        <v>3.779962759401673</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.331277161118857</v>
+        <v>3.286338243987918</v>
       </c>
       <c r="D2000" t="n">
         <v>-3.828601950947886</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.799479956425955</v>
+        <v>1.754541039295016</v>
       </c>
       <c r="F2000" t="n">
         <v>-0.06497957939421634</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.292289413482327</v>
+        <v>3.247350496351388</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769472653557223</v>
+        <v>3.769472653557221</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.327952517108402</v>
+        <v>3.283013599977463</v>
       </c>
       <c r="D2001" t="n">
         <v>-3.895862394969803</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.769251134806734</v>
+        <v>1.724312217675794</v>
       </c>
       <c r="F2001" t="n">
         <v>-0.1322400234161334</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.248608503058722</v>
+        <v>3.203669585927783</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766702530088378</v>
+        <v>3.766702530088376</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.337958670753144</v>
+        <v>3.293019753622204</v>
       </c>
       <c r="D2002" t="n">
         <v>-3.873390860930971</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.788245902067008</v>
+        <v>1.743306984936069</v>
       </c>
       <c r="F2002" t="n">
         <v>0.003465461399837777</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.340037947593046</v>
+        <v>3.295099030462107</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.747838269009202</v>
+        <v>3.7843704125137</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.522061802898103</v>
+        <v>3.477122885767164</v>
       </c>
       <c r="D2003" t="n">
-        <v>-4.007248777609875</v>
+        <v>-4.009343868987287</v>
       </c>
       <c r="E2003" t="n">
-        <v>1.918805867540406</v>
+        <v>1.873028913858502</v>
       </c>
       <c r="F2003" t="n">
         <v>0.003465461399837777</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.524141079738006</v>
+        <v>3.479202162607067</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240623.xlsx
+++ b/tame_output/ON/bt/strategyON_20240623.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.4%</t>
+          <t>61.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.7%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>54.7%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>75.5%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>37.2%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>60.2%</t>
+          <t>60.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>-5.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>40.6%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.2%</t>
+          <t>-73.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.1%</t>
+          <t>108.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.0%</t>
+          <t>121.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-692.0%</t>
+          <t>-671.5%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.9%</t>
+          <t>-51.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.9%</t>
+          <t>-69.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.5%</t>
+          <t>89.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>459.2%</t>
+          <t>461.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-12.9%</t>
+          <t>-12.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-562.5%</t>
+          <t>-542.0%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>19.7%</t>
+          <t>22.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>49.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.5%</t>
+          <t>99.4%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-277.2%</t>
+          <t>-269.0%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-40.5%</t>
+          <t>-39.8%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-31.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>120.3%</t>
+          <t>62.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-188.9%</t>
+          <t>-176.2%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-23.0%</t>
+          <t>-20.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-300.5%</t>
+          <t>-284.7%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-33.2%</t>
+          <t>-32.2%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-16.3%</t>
+          <t>-13.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-3.6%</t>
+          <t>-1.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-171.6%</t>
+          <t>-224.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-223.6%</t>
+          <t>-207.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.2%</t>
+          <t>95.8%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-180.7%</t>
+          <t>-171.2%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.6%</t>
+          <t>-27.7%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>58.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.7%</t>
+          <t>-16.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-98.1%</t>
+          <t>-84.1%</t>
         </is>
       </c>
     </row>
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.069732473107872</v>
+        <v>-4.865028289201649</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.095822120473888</v>
+        <v>1.177703794036377</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.7716818011309712</v>
+        <v>-0.6134014309399536</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.661062453352201</v>
+        <v>2.756030675466812</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310978</v>
+        <v>3.284619513310979</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.304426467240424</v>
+        <v>-5.099722283334201</v>
       </c>
       <c r="E1860" t="n">
-        <v>0.9902292978229577</v>
+        <v>1.072110971385447</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.765345533901716</v>
+        <v>-0.6070651637106984</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.653148988691845</v>
+        <v>2.748117210806456</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,22 +44348,22 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.30584953900653</v>
+        <v>3.305849539006531</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.640089114470877</v>
+        <v>-5.435384930564654</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8545448305867418</v>
+        <v>0.9364265041492308</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.8332765193906209</v>
+        <v>-0.6749961491996033</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.610970989054468</v>
+        <v>2.705939211169078</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-6.00371535937119</v>
+        <v>-5.799011175464967</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7155818928608579</v>
+        <v>0.7974635664233469</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.9314981562577467</v>
+        <v>-0.7732177860667291</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.558525567168433</v>
+        <v>2.653493789283044</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.368842742009937</v>
+        <v>-6.164138558103714</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5687854548111906</v>
+        <v>0.6506671283736796</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.227808940556759</v>
+        <v>-1.069528570365742</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.379993611594857</v>
+        <v>2.474961833709468</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.777431519190616</v>
+        <v>-6.572727335284393</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4041114879536778</v>
+        <v>0.4859931615161672</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.636397717737438</v>
+        <v>-1.47811734754642</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.133601889301209</v>
+        <v>2.22857011141582</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.054007619506448</v>
+        <v>-6.849303435600225</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.2886664802988057</v>
+        <v>0.3705481538612947</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.636397717737438</v>
+        <v>-1.47811734754642</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.12878732177267</v>
+        <v>2.223755543887281</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.470399493793446</v>
+        <v>-7.265695309887223</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.120103781192884</v>
+        <v>0.2019854547553734</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.636397717737438</v>
+        <v>-1.47811734754642</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.126781372381547</v>
+        <v>2.221749594496158</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.714670894520515</v>
+        <v>-7.509966710614292</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.03265391157073516</v>
+        <v>0.1145355851332246</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.636397717737438</v>
+        <v>-1.47811734754642</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.137040063050226</v>
+        <v>2.232008285164837</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.919921913757276</v>
+        <v>-7.715217729851052</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.05334693097827392</v>
+        <v>0.02853474258421551</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.636397717737438</v>
+        <v>-1.47811734754642</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.133139628195922</v>
+        <v>2.228107850310532</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.083501791941659</v>
+        <v>-7.878797608035436</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1203739621970263</v>
+        <v>-0.03849228863453691</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.636397717737438</v>
+        <v>-1.47811734754642</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.131544548250923</v>
+        <v>2.226512770365533</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.380163133751857</v>
+        <v>-8.175458949845634</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2352595229918975</v>
+        <v>-0.153377849429408</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.705140853471316</v>
+        <v>-1.546860483280299</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.094077642739804</v>
+        <v>2.189045864854414</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.56688284206116</v>
+        <v>-8.362178658154937</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.3139737108500213</v>
+        <v>-0.2320920372875324</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.705140853471316</v>
+        <v>-1.546860483280299</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.0900513382054</v>
+        <v>2.185019560320011</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.949884230803791</v>
+        <v>-8.745180046897568</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.4672763676686582</v>
+        <v>-0.3853946941061688</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.705140853471316</v>
+        <v>-1.546860483280299</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.089949236883816</v>
+        <v>2.184917458998427</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.131754021788826</v>
+        <v>-8.927049837882603</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.5374527680912418</v>
+        <v>-0.4555710945287523</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.887010644456351</v>
+        <v>-1.728730274265334</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.983398878264226</v>
+        <v>2.078367100378836</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.491284344292827</v>
+        <v>-9.286580160386604</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.6759145937947921</v>
+        <v>-0.5940329202323031</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.887010644456351</v>
+        <v>-1.728730274265334</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.988749181562276</v>
+        <v>2.083717403676886</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.541633407747049</v>
+        <v>-9.336929223840826</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.6881381992193036</v>
+        <v>-0.6062565256568142</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.937359707910573</v>
+        <v>-1.779079337719556</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.96645576344692</v>
+        <v>2.061423985561531</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.639252685168445</v>
+        <v>-9.434548501262222</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.7241441595660931</v>
+        <v>-0.6422624860036037</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.03497898533197</v>
+        <v>-1.876698615140952</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.91092594761585</v>
+        <v>2.005894169730461</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.786778773174088</v>
+        <v>-9.582074589267865</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.7802610384467781</v>
+        <v>-0.6983793648842886</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.182505073337614</v>
+        <v>-2.024224703146596</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.825303851134037</v>
+        <v>1.920272073248647</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.991036948503952</v>
+        <v>-9.786332764597729</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.856451111460081</v>
+        <v>-0.774569437897592</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.310144017951603</v>
+        <v>-2.151863647760585</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.754233681484286</v>
+        <v>1.849201903598896</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.06536992476412</v>
+        <v>-9.860665740857893</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.8817017474797111</v>
+        <v>-0.7998200739172217</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.454843541886275</v>
+        <v>-2.296563171695257</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.671896521607918</v>
+        <v>1.766864743722529</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.991900093096667</v>
+        <v>-9.787195909190444</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.83694211331931</v>
+        <v>-0.755060439756821</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.381373710218827</v>
+        <v>-2.223093340027809</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.731350122101808</v>
+        <v>1.826318344216419</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.16702451048321</v>
+        <v>-9.962320326576988</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.8924366595264104</v>
+        <v>-0.8105549859639214</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.556498127605371</v>
+        <v>-2.398217757414353</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.640830692417399</v>
+        <v>1.73579891453201</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.4014766044977</v>
+        <v>-10.19677242059148</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.9934366620338024</v>
+        <v>-0.911554988471313</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.556498127605371</v>
+        <v>-2.398217757414353</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.633611527515803</v>
+        <v>1.728579749630414</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.50585133552415</v>
+        <v>-10.30114715161792</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.041858745218357</v>
+        <v>-0.9599770716558678</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.660872858631816</v>
+        <v>-2.502592488440798</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.564314498125959</v>
+        <v>1.65928272024057</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.55863749112447</v>
+        <v>-10.35393330721825</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.061857417619931</v>
+        <v>-0.9799757440574428</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.756548345214213</v>
+        <v>-2.598267975023195</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.508024996015078</v>
+        <v>1.602993218129688</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.68467428449276</v>
+        <v>-10.47997010058654</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.109578406338132</v>
+        <v>-1.027696732775644</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.731296722404471</v>
+        <v>-2.573016352213453</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.525869698330037</v>
+        <v>1.620837920444648</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.63265877052395</v>
+        <v>-10.42795458661773</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.084781865064206</v>
+        <v>-1.002900191501717</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.731296722404471</v>
+        <v>-2.573016352213453</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.529860034016438</v>
+        <v>1.624828256131049</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.77433061224807</v>
+        <v>-10.56962642834185</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.142925828652596</v>
+        <v>-1.061044155090107</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.731296722404471</v>
+        <v>-2.573016352213453</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.528384807117697</v>
+        <v>1.623353029232307</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.72473976782324</v>
+        <v>-10.52003558391701</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.10803608071779</v>
+        <v>-1.026154407155301</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.681705877979637</v>
+        <v>-2.523425507788619</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.573192723937469</v>
+        <v>1.66816094605208</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.71193237481846</v>
+        <v>-10.50722819091224</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.115964257162564</v>
+        <v>-1.034082583600074</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.730561652988538</v>
+        <v>-2.57228128279752</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.530828125285446</v>
+        <v>1.625796347400056</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.48608722209905</v>
+        <v>-10.28138303819283</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.016047123038591</v>
+        <v>-0.9341654494761022</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.688634977401374</v>
+        <v>-2.530354607210357</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.565563203673952</v>
+        <v>1.660531425788563</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.36150856576146</v>
+        <v>-10.15680438185524</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.9650765159474957</v>
+        <v>-0.8831948423850062</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.688634977401374</v>
+        <v>-2.530354607210357</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.566702348230011</v>
+        <v>1.661670570344622</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.41440385380575</v>
+        <v>-10.20969966989952</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.9836008570031023</v>
+        <v>-0.9017191834406129</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.683679631312928</v>
+        <v>-2.52539926112191</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.572309330045187</v>
+        <v>1.667277552159797</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.34227067851787</v>
+        <v>-10.13756649461164</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.9490138826493135</v>
+        <v>-0.8671322090868241</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.683679631312928</v>
+        <v>-2.52539926112191</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.578043034283823</v>
+        <v>1.673011256398434</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.27090428590822</v>
+        <v>-10.06620010200199</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.9302045879993202</v>
+        <v>-0.8483229144368307</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.61231323870328</v>
+        <v>-2.454032868512262</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.611125607455747</v>
+        <v>1.706093829570358</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.17744525192299</v>
+        <v>-9.97274106801677</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.9027044557181374</v>
+        <v>-0.8208227821556484</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.61231323870328</v>
+        <v>-2.454032868512262</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.601242126142839</v>
+        <v>1.69621034825745</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.910203451054596</v>
+        <v>-9.705499267148372</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7976422958701521</v>
+        <v>-0.7157606223076631</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.61231323870328</v>
+        <v>-2.454032868512262</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.599407565643466</v>
+        <v>1.694375787758076</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.812296412378105</v>
+        <v>-9.607592228471882</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.7587797953730169</v>
+        <v>-0.6768981218105274</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.544327488842724</v>
+        <v>-2.386047118651706</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.639898700586339</v>
+        <v>1.734866922700949</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.788342871402147</v>
+        <v>-9.583638687495924</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.7485298728371399</v>
+        <v>-0.6666481992746509</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.520373947866766</v>
+        <v>-2.362093577675748</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.654939331317407</v>
+        <v>1.749907553432017</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.52428293307935</v>
+        <v>-9.319578749173127</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6561662136697732</v>
+        <v>-0.5742845401072842</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.25631400954397</v>
+        <v>-2.098033639352952</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.800114978149332</v>
+        <v>1.895083200263943</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.817203309574513</v>
+        <v>-8.61249912566829</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3761213979281393</v>
+        <v>-0.2942397243656503</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.25631400954397</v>
+        <v>-2.098033639352952</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.797327944489031</v>
+        <v>1.892296166603642</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.777019011208322</v>
+        <v>-8.572314827302099</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3597040546938217</v>
+        <v>-0.2778223811313327</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.216129711177779</v>
+        <v>-2.057849340986762</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.821782147396587</v>
+        <v>1.916750369511198</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.613619140268959</v>
+        <v>-8.408914956362736</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2949772850973194</v>
+        <v>-0.2130956115348304</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.052729840238417</v>
+        <v>-1.894449470047399</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.919188891180962</v>
+        <v>2.014157113295572</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.38013791803936</v>
+        <v>-8.175433734133136</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1936603673676274</v>
+        <v>-0.1117786938051379</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.819248618008818</v>
+        <v>-1.660968247817801</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.067202053356573</v>
+        <v>2.162170275471184</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.230471527031845</v>
+        <v>-8.025767343125622</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1366860212775807</v>
+        <v>-0.05480434771509168</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.726345126766282</v>
+        <v>-1.568064756575265</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.120051937789135</v>
+        <v>2.215020159903746</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.098196053400958</v>
+        <v>-7.893491869494736</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.08840834507819872</v>
+        <v>-0.006526671515710181</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.594069653135396</v>
+        <v>-1.435789282944378</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.194784708714694</v>
+        <v>2.289752930829305</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.942457720841216</v>
+        <v>-7.737753536934994</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.02329795136666535</v>
+        <v>0.05858372219582364</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.438331320575654</v>
+        <v>-1.280050950384636</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.291042768938176</v>
+        <v>2.386010991052787</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.693457922157635</v>
+        <v>-7.488753738251413</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.08920830933042589</v>
+        <v>0.1710899828929144</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.438331320575654</v>
+        <v>-1.280050950384636</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.303949110161835</v>
+        <v>2.398917332276445</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.79904791193074</v>
+        <v>-7.594343728024517</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.08100361617803475</v>
+        <v>0.0008780573844542339</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.543921310348759</v>
+        <v>-1.385640940157741</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.112619186698754</v>
+        <v>2.207587408813364</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.817782814049337</v>
+        <v>-7.613078630143114</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.03995323514838711</v>
+        <v>0.04192843841410188</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.54951732000889</v>
+        <v>-1.391236949817872</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.157805922779761</v>
+        <v>2.252774144894372</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.669842772641737</v>
+        <v>-7.465138588735515</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.100656141273515</v>
+        <v>-0.01877446771102598</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.529196404100332</v>
+        <v>-1.370916033909314</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.050119549636728</v>
+        <v>2.145087771751339</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.616873250387749</v>
+        <v>-7.412169066481527</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.08818231862539783</v>
+        <v>-0.006300645062908838</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.476226881846344</v>
+        <v>-1.317946511655326</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.073187276735643</v>
+        <v>2.168155498850254</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.573324843617058</v>
+        <v>-7.368620659710836</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.07772356801221481</v>
+        <v>0.004158105550274183</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.476226881846344</v>
+        <v>-1.317946511655326</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.06622666464055</v>
+        <v>2.161194886755161</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.3311764501632</v>
+        <v>-7.126472266256978</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.03359814375047154</v>
+        <v>0.1154798173129605</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.476226881846344</v>
+        <v>-1.317946511655326</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.080689019021693</v>
+        <v>2.175657241136304</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.222917313040679</v>
+        <v>-7.018213129134456</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.07143391905867524</v>
+        <v>0.1533155926211642</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.476226881846344</v>
+        <v>-1.317946511655326</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.075221139480888</v>
+        <v>2.170189361595499</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.099626178223548</v>
+        <v>-6.894921994317325</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1182484669961044</v>
+        <v>0.2001301405585934</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.352935747029213</v>
+        <v>-1.194655376838195</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.146693914381743</v>
+        <v>2.241662136496354</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.078476979320104</v>
+        <v>-6.873772795413882</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1344091247948072</v>
+        <v>0.2162907983572957</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.33178654812577</v>
+        <v>-1.173506177934752</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.167084411961135</v>
+        <v>2.262052634075745</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.83471153733666</v>
+        <v>-6.630007353430438</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2276960099352352</v>
+        <v>0.3095776834977242</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.33178654812577</v>
+        <v>-1.173506177934752</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.162865120308185</v>
+        <v>2.257833342422796</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.732948717059365</v>
+        <v>-6.528244533153143</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2705254519661695</v>
+        <v>0.352407125528658</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.318567479733341</v>
+        <v>-1.160287109542323</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.172920875263658</v>
+        <v>2.267889097378269</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.483098323110291</v>
+        <v>-6.278394139204068</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3632076845295011</v>
+        <v>0.4450893580919901</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.318567479733341</v>
+        <v>-1.160287109542323</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.165662950247361</v>
+        <v>2.260631172361971</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.307206230642858</v>
+        <v>-6.102502046736635</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4371636450371228</v>
+        <v>0.5190453185996122</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.318567479733341</v>
+        <v>-1.160287109542323</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.169262073768009</v>
+        <v>2.26423029588262</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.135759767620395</v>
+        <v>-5.931055583714172</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5190697363006618</v>
+        <v>0.6009514098631512</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.147121016710878</v>
+        <v>-0.9888406465198601</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.285457457636041</v>
+        <v>2.380425679750652</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.061470201882056</v>
+        <v>-5.856766017975833</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5478060402122944</v>
+        <v>0.6296877137747838</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.072831450972539</v>
+        <v>-0.9145510807815209</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.329051674695342</v>
+        <v>2.424019896809952</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883074</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.997834459648121</v>
+        <v>-5.793130275741898</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5779551381601857</v>
+        <v>0.6598368117226752</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.009195708738604</v>
+        <v>-0.8509153385475864</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.37192792109002</v>
+        <v>2.46689614320463</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074783</v>
+        <v>3.798814771074785</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.886407700322201</v>
+        <v>-5.681703516415978</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6037201006743493</v>
+        <v>0.6856017742368388</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.009195708738604</v>
+        <v>-0.8509153385475864</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.353122179873815</v>
+        <v>2.448090401988426</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242294</v>
+        <v>3.797694884242296</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.645977203517341</v>
+        <v>-5.441273019611118</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7016353760211711</v>
+        <v>0.7835170495836601</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.7687652119337436</v>
+        <v>-0.6104848417427261</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.499123554581609</v>
+        <v>2.594091776696219</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367685</v>
+        <v>3.821593509367687</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.573734635346146</v>
+        <v>-5.369030451439923</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7344617171244692</v>
+        <v>0.8163433906869582</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.7687652119337436</v>
+        <v>-0.6104848417427261</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.503052868416429</v>
+        <v>2.598021090531039</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879967</v>
+        <v>3.822326997879968</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.520736313064758</v>
+        <v>-5.316032129158535</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7563396299543643</v>
+        <v>0.8382213035168533</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.7134289529318047</v>
+        <v>-0.5551485827407873</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.536933207734932</v>
+        <v>2.631901429849543</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.84861662650234</v>
+        <v>3.848616626502341</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.411931427585031</v>
+        <v>-5.207227243678808</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7968596553662484</v>
+        <v>0.8787413289287378</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.7134289529318047</v>
+        <v>-0.5551485827407873</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.533931278954926</v>
+        <v>2.628899501069536</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675941</v>
+        <v>3.818668951675943</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.191910629548021</v>
+        <v>-4.987206445641798</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8864470115916667</v>
+        <v>0.9683286851541562</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.5722091078638245</v>
+        <v>-0.413928737672807</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.620242223006328</v>
+        <v>2.715210445120939</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539952</v>
+        <v>3.843274527539954</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.059042940484743</v>
+        <v>-4.85433875657852</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.955488270018801</v>
+        <v>1.03736994358129</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.5722091078638245</v>
+        <v>-0.413928737672807</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.636136405808151</v>
+        <v>2.731104627922762</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496261</v>
+        <v>3.845047386496263</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.938869857120245</v>
+        <v>-4.734165673214021</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.004703347804903</v>
+        <v>1.086585021367392</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.4520360244993256</v>
+        <v>-0.2937556543083081</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.709386100267153</v>
+        <v>2.804354322381763</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576998</v>
+        <v>3.791273551577</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.794197712020507</v>
+        <v>-4.589493528114284</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.072660308406237</v>
+        <v>1.154541981968727</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.3073638793995881</v>
+        <v>-0.1490835092085707</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.806277489888435</v>
+        <v>2.901245712003045</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942104</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.854072539378199</v>
+        <v>-4.649368355471976</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.034747868864586</v>
+        <v>1.116629542427076</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.3672387067572803</v>
+        <v>-0.2089583365662628</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.756390084875245</v>
+        <v>2.851358306989856</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674514</v>
+        <v>3.762647477674516</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.767273041599191</v>
+        <v>-4.562568857692968</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.091868161298756</v>
+        <v>1.173749834861245</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.3672387067572803</v>
+        <v>-0.2089583365662628</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.778790578197811</v>
+        <v>2.873758800312422</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430695</v>
+        <v>3.729146398430697</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.769742748060997</v>
+        <v>-4.565038564154774</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.090952680087445</v>
+        <v>1.172834353649935</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.3697084132190864</v>
+        <v>-0.2114280430280689</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.77738115569414</v>
+        <v>2.87234937780875</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003602</v>
+        <v>3.743220196003604</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.838112934385007</v>
+        <v>-4.633408750478784</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.074611528032543</v>
+        <v>1.156493201595033</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.3604327141828715</v>
+        <v>-0.202152343991854</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.793953497590571</v>
+        <v>2.888921719705182</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.71417913950837</v>
+        <v>3.714179139508372</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.851900987232054</v>
+        <v>-4.647196803325831</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.059533015525616</v>
+        <v>1.141414689088105</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.3604327141828715</v>
+        <v>-0.202152343991854</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.784390206222462</v>
+        <v>2.879358428337073</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417705</v>
+        <v>3.710906731417706</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.882894146560759</v>
+        <v>-4.678189962654536</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8718453168345206</v>
+        <v>0.9537269903970098</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.3604327141828715</v>
+        <v>-0.202152343991854</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.609099771262849</v>
+        <v>2.70406799337746</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205901</v>
+        <v>3.746042526205903</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.707419886768291</v>
+        <v>-4.502715702862067</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.946602252743296</v>
+        <v>1.028483926305785</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.3604327141828715</v>
+        <v>-0.202152343991854</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.613667003254637</v>
+        <v>2.708635225369247</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225446</v>
+        <v>3.765024323225448</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.81835613940954</v>
+        <v>-4.613651955503316</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8779697804480033</v>
+        <v>0.9598514540104928</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.3604327141828715</v>
+        <v>-0.202152343991854</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.589409032015844</v>
+        <v>2.684377254130454</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111295</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.784692593937257</v>
+        <v>-4.579988410031034</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8945665838568218</v>
+        <v>0.9764482574193112</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.3267691687105896</v>
+        <v>-0.1684887985195722</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.612738544519118</v>
+        <v>2.707706766633729</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.724839974733534</v>
+        <v>-4.520135790827311</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9286800179704435</v>
+        <v>1.010561691532933</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.3267691687105896</v>
+        <v>-0.1684887985195722</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.622910930951251</v>
+        <v>2.717879153065861</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742299</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.638596511707156</v>
+        <v>-4.433892327800933</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9581236737548549</v>
+        <v>1.040005347317344</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.3267691687105896</v>
+        <v>-0.1684887985195722</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.617857201525111</v>
+        <v>2.712825423639722</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316046</v>
+        <v>3.752027499316048</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.683903331106136</v>
+        <v>-4.479199147199913</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9317767214397885</v>
+        <v>1.013658395002278</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.3675793317198204</v>
+        <v>-0.209298961528803</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.585146879164098</v>
+        <v>2.680115101278709</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.712936435808437</v>
+        <v>-4.508232251902214</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9207153525919696</v>
+        <v>1.002597026154459</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.3675793317198204</v>
+        <v>-0.209298961528803</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.5856987521972</v>
+        <v>2.68066697431181</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809497</v>
+        <v>3.733390600809499</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.620125954357578</v>
+        <v>-4.415421770451355</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.887112237063679</v>
+        <v>0.9689939106261685</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.2747688502689611</v>
+        <v>-0.1164884800779436</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.570657732959081</v>
+        <v>2.665625955073692</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560425</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.664515423687005</v>
+        <v>-4.459811239780782</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.871229925256509</v>
+        <v>0.9531115988189982</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.3191583195983888</v>
+        <v>-0.1608779494073713</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.545897527286025</v>
+        <v>2.640865749400636</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472738</v>
+        <v>3.72107719547274</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.551844205450755</v>
+        <v>-4.347140021544532</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.911374121062732</v>
+        <v>0.9932557946252212</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.2064871013621385</v>
+        <v>-0.04820673117112106</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.608575966739498</v>
+        <v>2.703544188854109</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798539</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.439467204268082</v>
+        <v>-4.234763020361859</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9618162173664684</v>
+        <v>1.043697890928958</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.2064871013621385</v>
+        <v>-0.04820673117112106</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.614067262570166</v>
+        <v>2.709035484684776</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498865</v>
+        <v>3.689597840498867</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.467247602169435</v>
+        <v>-4.262543418263212</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9622012599744665</v>
+        <v>1.044082933536956</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.2342674992634916</v>
+        <v>-0.07598712907247412</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.608896225597893</v>
+        <v>2.703864447712503</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705325</v>
+        <v>3.643069621705327</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.550248883194714</v>
+        <v>-4.345544699288491</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7673564675650082</v>
+        <v>0.8492381411274974</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.2528383837906654</v>
+        <v>-0.09455801359964788</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.436109414882242</v>
+        <v>2.531077636996852</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.68271631072927</v>
+        <v>3.682716310729271</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.658862961638045</v>
+        <v>-4.454158777731822</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8440604969068812</v>
+        <v>0.9259421704693707</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.2528383837906654</v>
+        <v>-0.09455801359964788</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.556259075601448</v>
+        <v>2.651227297716058</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190769</v>
+        <v>3.733012441190771</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.623453923389902</v>
+        <v>-4.418749739483679</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8727371383084614</v>
+        <v>0.9546188118709507</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.2528383837906654</v>
+        <v>-0.09455801359964788</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.570772101703771</v>
+        <v>2.665740323818381</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913426</v>
+        <v>3.741174069913428</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.585070260831751</v>
+        <v>-4.380366076925528</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8855100446740907</v>
+        <v>0.9673917182365799</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.2144547212325142</v>
+        <v>-0.05617435104149671</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.59122174058103</v>
+        <v>2.68618996269564</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532487</v>
+        <v>3.751147197532489</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.407953930796585</v>
+        <v>-4.203249746890362</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9530856055334589</v>
+        <v>1.034967279095948</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.2144547212325142</v>
+        <v>-0.05617435104149671</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.587950769426332</v>
+        <v>2.682918991540942</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793904</v>
+        <v>3.741328448793906</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.45304617563013</v>
+        <v>-4.248341991723907</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9357320993619538</v>
+        <v>1.017613772924443</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.276350764401904</v>
+        <v>-0.1180703942108865</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.551496535286611</v>
+        <v>2.646464757401222</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011237</v>
+        <v>3.750729377011239</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.273670754391363</v>
+        <v>-4.06896657048514</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.001269243163875</v>
+        <v>1.083150916726364</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.1195740062311853</v>
+        <v>0.03870636395983218</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.639349565495456</v>
+        <v>2.734317787610067</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982231</v>
+        <v>3.716991718982233</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.318684967911969</v>
+        <v>-4.113980784005745</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9640710130872225</v>
+        <v>1.045952686649712</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.1499229015457899</v>
+        <v>0.008357468645227573</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.601947683638284</v>
+        <v>2.696915905752894</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509541</v>
+        <v>3.737026608509542</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.585689478184404</v>
+        <v>-4.38098529427818</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8629607713171943</v>
+        <v>0.9448424448796837</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.3442859395887385</v>
+        <v>-0.186005569397721</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.49102142315146</v>
+        <v>2.585989645266071</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760811</v>
+        <v>3.702309454760813</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.686887259621576</v>
+        <v>-4.482183075715353</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8216855806388268</v>
+        <v>0.903567254201316</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.4126947531340577</v>
+        <v>-0.2544143829430402</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.44918005692077</v>
+        <v>2.54414827903538</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815456</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.654411673450804</v>
+        <v>-4.449707489544581</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8322757766614524</v>
+        <v>0.9141574502239416</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.4126947531340577</v>
+        <v>-0.2544143829430402</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.446780018475087</v>
+        <v>2.541748240589697</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.7095104433781</v>
+        <v>3.709510443378102</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.635373545743507</v>
+        <v>-4.430669361837284</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8364157469526161</v>
+        <v>0.9182974205151053</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.4708783644652522</v>
+        <v>-0.3125979942742347</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.408394570884615</v>
+        <v>2.503362792999225</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.731064473131253</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.666500176894125</v>
+        <v>-4.461795992987902</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.001546963431049</v>
+        <v>1.083428636993539</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.4708783644652522</v>
+        <v>-0.3125979942742347</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.585976439823296</v>
+        <v>2.680944661937906</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067867</v>
+        <v>3.722447362067869</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.680366938228043</v>
+        <v>-4.47566275432182</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9968335878836156</v>
+        <v>1.078715261446105</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.5087362811990752</v>
+        <v>-0.3504559110080577</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.564095018769136</v>
+        <v>2.659063240883746</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789123</v>
+        <v>3.787425580789125</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.635562766688113</v>
+        <v>-4.43085858278189</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.020763786896514</v>
+        <v>1.102645460459003</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.5087362811990752</v>
+        <v>-0.3504559110080577</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.570103549166062</v>
+        <v>2.665071771280672</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.78150125051991</v>
+        <v>3.781501250519912</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.909559048546589</v>
+        <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.487819796453111</v>
+        <v>-4.283115612546887</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.114074705651597</v>
+        <v>1.240895296345026</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.3409289239641921</v>
+        <v>-0.1826485537731745</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.705001694168074</v>
+        <v>2.844908833413624</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181172</v>
+        <v>3.802245929181174</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.91235267007807</v>
+        <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.589834478984332</v>
+        <v>-4.385130295078109</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.07606245417059</v>
+        <v>1.202883044864018</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.3409289239641921</v>
+        <v>-0.1826485537731745</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.707795315699555</v>
+        <v>2.847702454945105</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394732</v>
+        <v>3.805608985394734</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.913015018469728</v>
+        <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.583681772931548</v>
+        <v>-4.378977589025324</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.079185884983362</v>
+        <v>1.20600647567679</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.3347762179114078</v>
+        <v>-0.1764958477203902</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.712149287722884</v>
+        <v>2.852056426968434</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890611</v>
+        <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.912095495209838</v>
+        <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.600491071082049</v>
+        <v>-4.395786887175826</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.071542642463271</v>
+        <v>1.1983632331567</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.3515855160619094</v>
+        <v>-0.1933051458708919</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.701144185572693</v>
+        <v>2.841051324818243</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798428</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.978431049006659</v>
+        <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.538193072305927</v>
+        <v>-4.333488888399704</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.162797395770541</v>
+        <v>1.28961798646397</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.3515855160619094</v>
+        <v>-0.1933051458708919</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.767479739369514</v>
+        <v>2.907386878615064</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992193</v>
+        <v>3.848729139992195</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.687011921396057</v>
+        <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.336402874640769</v>
+        <v>-4.131698690734546</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9520943472260024</v>
+        <v>1.078914937919431</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.153567323892755</v>
+        <v>0.004713046298262524</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.594871527060405</v>
+        <v>2.734778666305954</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852423</v>
+        <v>3.841444817852425</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.757302153718233</v>
+        <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.276512192998176</v>
+        <v>-4.071808009091953</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.046340852205215</v>
+        <v>1.173161442898643</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.09367664225016153</v>
+        <v>0.064603727940856</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.701096168368136</v>
+        <v>2.841003307613686</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319548</v>
+        <v>3.81906330031955</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.771929889834276</v>
+        <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.37425273762315</v>
+        <v>-4.169548553716927</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.021872370471269</v>
+        <v>1.148692961164697</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.1095659203831417</v>
+        <v>0.04871444980787581</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.706190337604391</v>
+        <v>2.846097476849941</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489387</v>
+        <v>3.831819032489388</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.770465870658948</v>
+        <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.55059049774608</v>
+        <v>-4.345886313839856</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9498732472467686</v>
+        <v>1.076693837940197</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.2859036805060711</v>
+        <v>-0.1276233103150536</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.598923662355305</v>
+        <v>2.738830801600855</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397796</v>
+        <v>3.836411672397798</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.768957488698876</v>
+        <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.474168451314153</v>
+        <v>-4.26946426740793</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.978933683859468</v>
+        <v>1.105754274552897</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.2859036805060711</v>
+        <v>-0.1276233103150536</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.597415280395234</v>
+        <v>2.737322419640784</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024964</v>
+        <v>3.836023391024966</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.768820356134313</v>
+        <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.429795319675584</v>
+        <v>-4.225091135769361</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9965458039503317</v>
+        <v>1.12336639464376</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.2415305488675025</v>
+        <v>-0.08325017867648499</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.623902026813811</v>
+        <v>2.763809166059361</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863224</v>
+        <v>3.821591150863226</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.768820356134313</v>
+        <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.421841349380812</v>
+        <v>-4.217137165474589</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9997273920682406</v>
+        <v>1.126547982761669</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.2415305488675025</v>
+        <v>-0.08325017867648499</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.623902026813811</v>
+        <v>2.763809166059361</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947583</v>
+        <v>3.833040181947585</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.775202113162117</v>
+        <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.374185618819756</v>
+        <v>-4.169481434913533</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.025171441320468</v>
+        <v>1.151992032013896</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.1938748183064469</v>
+        <v>-0.03559444811542933</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.65887722217825</v>
+        <v>2.798784361423799</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326875</v>
+        <v>3.822707244326876</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.780094486536842</v>
+        <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.24650130902546</v>
+        <v>-4.041797125119237</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.081137538612911</v>
+        <v>1.20795812930634</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.06619050851215041</v>
+        <v>0.09208986167886712</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.740380181429552</v>
+        <v>2.880287320675102</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.82883791131455</v>
+        <v>3.828837911314552</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.766849159012714</v>
+        <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.307167899427849</v>
+        <v>-4.102463715521626</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.043625574927827</v>
+        <v>1.170446165621256</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.1478888252306841</v>
+        <v>0.01039154496033345</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.678115863874304</v>
+        <v>2.818023003119854</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690025</v>
+        <v>3.816866067690027</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.770946861623343</v>
+        <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.262329497819451</v>
+        <v>-4.057625313913228</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.065658638181815</v>
+        <v>1.192479228875244</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.1433453922858146</v>
+        <v>0.01493497790520293</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.684939626251854</v>
+        <v>2.824846765497404</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674309</v>
+        <v>3.817961388674311</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.775107801254421</v>
+        <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.363088133576449</v>
+        <v>-4.158383949670226</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.029516123510094</v>
+        <v>1.156336714203523</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.23217096101282</v>
+        <v>-0.07389059082180249</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.635805224646729</v>
+        <v>2.775712363892279</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826713779163219</v>
+        <v>3.826713779163221</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.780987403782258</v>
+        <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.318885296490548</v>
+        <v>-4.114181112584325</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.053076860872291</v>
+        <v>1.17989745156572</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.1879681239269196</v>
+        <v>-0.02968775373590204</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.668206529426107</v>
+        <v>2.808113668671656</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022903</v>
+        <v>3.838228663022905</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.779397404251505</v>
+        <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.355864324153991</v>
+        <v>-4.151160140247768</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.036695250276162</v>
+        <v>1.16351584096959</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.1509942221355891</v>
+        <v>0.007286148055428487</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.688800870970153</v>
+        <v>2.828708010215702</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042137</v>
+        <v>3.863924114042139</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.830645169434545</v>
+        <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.375922403018832</v>
+        <v>-4.171218219112609</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.079919783913265</v>
+        <v>1.206740374606694</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.1509942221355891</v>
+        <v>0.007286148055428487</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.740048636153192</v>
+        <v>2.879955775398742</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86536771507828</v>
+        <v>3.865367715078282</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.829085874028798</v>
+        <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.335991729840941</v>
+        <v>-4.131287545934718</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.094332757778675</v>
+        <v>1.221153348472103</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.1110635489576987</v>
+        <v>0.04721682123331883</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.762447744654179</v>
+        <v>2.902354883899729</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232397</v>
+        <v>3.864518876232399</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.824034102267068</v>
+        <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.284959637118414</v>
+        <v>-4.080255453212191</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.109693823105955</v>
+        <v>1.236514413799384</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.06003145623517075</v>
+        <v>0.09824891395584678</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.788015228525966</v>
+        <v>2.927922367771516</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842576394162113</v>
+        <v>3.842576394162115</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.841221506359773</v>
+        <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.219735455991208</v>
+        <v>-4.015031272084985</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.152970899649543</v>
+        <v>1.279791490342971</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.005192724892034872</v>
+        <v>0.1634730950830524</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.844337141294994</v>
+        <v>2.984244280540544</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840090220639817</v>
+        <v>3.840090220639818</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.837182478659054</v>
+        <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.182308435920074</v>
+        <v>-3.977604252013851</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.163902679977277</v>
+        <v>1.290723270670705</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.01044426292121653</v>
+        <v>0.1687246331122341</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.843449036411784</v>
+        <v>2.983356175657334</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845198842749921</v>
+        <v>3.845198842749923</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.838439270990294</v>
+        <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.202420091954782</v>
+        <v>-3.99771590804856</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.157114809894634</v>
+        <v>1.283935400588062</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.02147160791863573</v>
+        <v>0.1797519781096533</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.851322235741476</v>
+        <v>2.991229374987026</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828690479393548</v>
+        <v>3.82869047939355</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.998997042011505</v>
+        <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.148675277527578</v>
+        <v>-3.943971093621355</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.339170506686726</v>
+        <v>1.465991097380155</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.03153491735909769</v>
+        <v>0.1898152875501152</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.017917992426963</v>
+        <v>3.157825131672513</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813251854714886</v>
+        <v>3.813251854714887</v>
       </c>
       <c r="C1992" t="n">
-        <v>3.119109951229322</v>
+        <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.124883708921436</v>
+        <v>-3.920179525015213</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.468800043347</v>
+        <v>1.595620634040429</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.05532648596523998</v>
+        <v>0.2136068561562575</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.152305842808466</v>
+        <v>3.292212982054016</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814259761756011</v>
+        <v>3.814259761756013</v>
       </c>
       <c r="C1993" t="n">
-        <v>3.110817927243181</v>
+        <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.098799624657627</v>
+        <v>-3.894095440751405</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.470941653066383</v>
+        <v>1.597762243759811</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.05532648596523998</v>
+        <v>0.2136068561562575</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.144013818822325</v>
+        <v>3.283920958067875</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803426852654185</v>
+        <v>3.803426852654187</v>
       </c>
       <c r="C1994" t="n">
-        <v>3.10901112282696</v>
+        <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-4.09446532160058</v>
+        <v>-3.889761137694356</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.470868569872981</v>
+        <v>1.59768916056641</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.2069765892844439</v>
+        <v>0.3652569594754614</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.233197076397627</v>
+        <v>3.373104215643177</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796293177717116</v>
+        <v>3.796293177717118</v>
       </c>
       <c r="C1995" t="n">
-        <v>3.126565528553752</v>
+        <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-4.085572860207296</v>
+        <v>-3.880868676301073</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.491979960157086</v>
+        <v>1.618800550850514</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.2069765892844439</v>
+        <v>0.3652569594754614</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.250751482124418</v>
+        <v>3.390658621369968</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794453975702625</v>
+        <v>3.794453975702627</v>
       </c>
       <c r="C1996" t="n">
-        <v>3.118420575958336</v>
+        <v>3.163359493089275</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.254048977177174</v>
+        <v>-4.049344793270951</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.416444560773719</v>
+        <v>1.543265151467147</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.1790287535678631</v>
+        <v>0.3373091237588807</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.225837828099054</v>
+        <v>3.365744967344604</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795603100539967</v>
+        <v>3.795603100539969</v>
       </c>
       <c r="C1997" t="n">
-        <v>3.099690273146197</v>
+        <v>3.144629190277137</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.556249448315591</v>
+        <v>-3.351545264409368</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.676834069506214</v>
+        <v>1.803654660199643</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.1086806941974524</v>
+        <v>0.2669610643884699</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.164898689664669</v>
+        <v>3.304805828910219</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784700379389897</v>
+        <v>3.784700379389899</v>
       </c>
       <c r="C1998" t="n">
-        <v>3.090354295643102</v>
+        <v>3.135293212774041</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.533528344632438</v>
+        <v>-3.328824160726215</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.676586533476379</v>
+        <v>1.803407124169808</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.1086806941974524</v>
+        <v>0.2669610643884699</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.155562712161574</v>
+        <v>3.295469851407124</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783234730534935</v>
+        <v>3.783234730534937</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.249260421494271</v>
+        <v>3.29419933862521</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.673820944169631</v>
+        <v>-3.469116760263407</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.779375619512672</v>
+        <v>1.9061962102061</v>
       </c>
       <c r="F1999" t="n">
-        <v>-0.03161190533974023</v>
+        <v>0.1266684648512773</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.230293278290427</v>
+        <v>3.370200417535977</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779962759401673</v>
+        <v>3.779962759401675</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.286338243987918</v>
+        <v>3.331277161118857</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.828601950947886</v>
+        <v>-3.623897767041663</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.754541039295016</v>
+        <v>1.881361629988445</v>
       </c>
       <c r="F2000" t="n">
-        <v>-0.06497957939421634</v>
+        <v>0.0933007907968012</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.247350496351388</v>
+        <v>3.387257635596938</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769472653557221</v>
+        <v>3.769472653557223</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.283013599977463</v>
+        <v>3.327952517108402</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.895862394969803</v>
+        <v>-3.69115821106358</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.724312217675794</v>
+        <v>1.851132808369223</v>
       </c>
       <c r="F2001" t="n">
-        <v>-0.1322400234161334</v>
+        <v>0.02604034677488409</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.203669585927783</v>
+        <v>3.343576725173333</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766702530088376</v>
+        <v>3.766702530088378</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.293019753622204</v>
+        <v>3.337958670753144</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.873390860930971</v>
+        <v>-3.668686677024748</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.743306984936069</v>
+        <v>1.870127575629497</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.003465461399837777</v>
+        <v>0.1617458315908553</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.295099030462107</v>
+        <v>3.435006169707657</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.7843704125137</v>
+        <v>3.827613531393259</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.477122885767164</v>
+        <v>3.522061802898103</v>
       </c>
       <c r="D2003" t="n">
-        <v>-4.009343868987287</v>
+        <v>-3.804639685081064</v>
       </c>
       <c r="E2003" t="n">
-        <v>1.873028913858502</v>
+        <v>1.999849504551931</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.003465461399837777</v>
+        <v>0.1617458315908553</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.479202162607067</v>
+        <v>3.619109301852617</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240623.xlsx
+++ b/tame_output/ON/bt/strategyON_20240623.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61.6%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>46.7%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>79.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>60.9%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>30.5%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.3%</t>
+          <t>-6.9%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>50.3%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-73.8%</t>
+          <t>-74.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.0%</t>
+          <t>109.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>121.9%</t>
+          <t>123.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-671.5%</t>
+          <t>-692.0%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.1%</t>
+          <t>-51.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-69.0%</t>
+          <t>-70.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.6%</t>
+          <t>90.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>461.0%</t>
+          <t>459.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-12.2%</t>
+          <t>-12.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-542.0%</t>
+          <t>-549.0%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>22.7%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,22 +1102,22 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.2%</t>
+          <t>49.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.4%</t>
+          <t>99.5%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-269.0%</t>
+          <t>-277.2%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-39.8%</t>
+          <t>-40.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-31.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>120.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-176.2%</t>
+          <t>-179.0%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-20.6%</t>
+          <t>-23.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-284.7%</t>
+          <t>-300.5%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-32.2%</t>
+          <t>-33.2%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-13.5%</t>
+          <t>-16.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-1.2%</t>
+          <t>-3.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-224.6%</t>
+          <t>-171.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-207.8%</t>
+          <t>-223.6%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>53.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,22 +1418,22 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>95.8%</t>
+          <t>96.2%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-171.2%</t>
+          <t>-180.7%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-27.7%</t>
+          <t>-28.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>58.4%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.4%</t>
+          <t>-17.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-84.1%</t>
+          <t>-84.8%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2003"/>
+  <dimension ref="A1:G2004"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178242</v>
+        <v>3.31588437417824</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,22 +44302,22 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.30531679820781</v>
+        <v>3.305316798207809</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.865028289201649</v>
+        <v>-5.069732473107872</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.177703794036377</v>
+        <v>1.095822120473888</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.6134014309399536</v>
+        <v>-0.7716818011309712</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.756030675466812</v>
+        <v>2.661062453352201</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310979</v>
+        <v>3.284619513310977</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.099722283334201</v>
+        <v>-5.304426467240424</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.072110971385447</v>
+        <v>0.9902292978229577</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.6070651637106984</v>
+        <v>-0.765345533901716</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.748117210806456</v>
+        <v>2.653148988691845</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,22 +44348,22 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006531</v>
+        <v>3.305849539006529</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.435384930564654</v>
+        <v>-5.640089114470877</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.9364265041492308</v>
+        <v>0.8545448305867418</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.6749961491996033</v>
+        <v>-0.8332765193906209</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.705939211169078</v>
+        <v>2.610970989054468</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309422</v>
+        <v>3.31108639130942</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.799011175464967</v>
+        <v>-6.00371535937119</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7974635664233469</v>
+        <v>0.7155818928608579</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.7732177860667291</v>
+        <v>-0.9314981562577467</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.653493789283044</v>
+        <v>2.558525567168433</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970903</v>
+        <v>3.304715716970901</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.164138558103714</v>
+        <v>-6.368842742009937</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.6506671283736796</v>
+        <v>0.5687854548111906</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.069528570365742</v>
+        <v>-1.227808940556759</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.474961833709468</v>
+        <v>2.379993611594857</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330521</v>
+        <v>3.300815818330519</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.572727335284393</v>
+        <v>-6.777431519190616</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4859931615161672</v>
+        <v>0.4041114879536778</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.47811734754642</v>
+        <v>-1.636397717737438</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.22857011141582</v>
+        <v>2.133601889301209</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191735</v>
+        <v>3.302618194191733</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.849303435600225</v>
+        <v>-7.054007619506448</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3705481538612947</v>
+        <v>0.2886664802988057</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.47811734754642</v>
+        <v>-1.636397717737438</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.223755543887281</v>
+        <v>2.12878732177267</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108638</v>
+        <v>3.305023265108634</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.265695309887223</v>
+        <v>-7.470399493793446</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.2019854547553734</v>
+        <v>0.120103781192884</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.47811734754642</v>
+        <v>-1.636397717737438</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.221749594496158</v>
+        <v>2.126781372381547</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.34137872309782</v>
+        <v>3.341378723097816</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.509966710614292</v>
+        <v>-7.714670894520515</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.1145355851332246</v>
+        <v>0.03265391157073516</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.47811734754642</v>
+        <v>-1.636397717737438</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.232008285164837</v>
+        <v>2.137040063050226</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094115</v>
+        <v>3.374439043094112</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.715217729851052</v>
+        <v>-7.919921913757276</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.02853474258421551</v>
+        <v>-0.05334693097827392</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.47811734754642</v>
+        <v>-1.636397717737438</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.228107850310532</v>
+        <v>2.133139628195922</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199284</v>
+        <v>3.405960511199281</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.878797608035436</v>
+        <v>-8.083501791941659</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.03849228863453691</v>
+        <v>-0.1203739621970263</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.47811734754642</v>
+        <v>-1.636397717737438</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.226512770365533</v>
+        <v>2.131544548250923</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969592</v>
+        <v>3.424633354969589</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.175458949845634</v>
+        <v>-8.380163133751857</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.153377849429408</v>
+        <v>-0.2352595229918975</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.546860483280299</v>
+        <v>-1.705140853471316</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.189045864854414</v>
+        <v>2.094077642739804</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923085</v>
+        <v>3.419979433923082</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.362178658154937</v>
+        <v>-8.56688284206116</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.2320920372875324</v>
+        <v>-0.3139737108500213</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.546860483280299</v>
+        <v>-1.705140853471316</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.185019560320011</v>
+        <v>2.0900513382054</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297748</v>
+        <v>3.458100091297744</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.745180046897568</v>
+        <v>-8.949884230803791</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.3853946941061688</v>
+        <v>-0.4672763676686582</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.546860483280299</v>
+        <v>-1.705140853471316</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.184917458998427</v>
+        <v>2.089949236883816</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317616</v>
+        <v>3.447750501317612</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-8.927049837882603</v>
+        <v>-9.131754021788826</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.4555710945287523</v>
+        <v>-0.5374527680912418</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.728730274265334</v>
+        <v>-1.887010644456351</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.078367100378836</v>
+        <v>1.983398878264226</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.50351550673717</v>
+        <v>3.503515506737166</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.286580160386604</v>
+        <v>-9.491284344292827</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.5940329202323031</v>
+        <v>-0.6759145937947921</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.728730274265334</v>
+        <v>-1.887010644456351</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.083717403676886</v>
+        <v>1.988749181562276</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341313</v>
+        <v>3.503170282341309</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.336929223840826</v>
+        <v>-9.541633407747049</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.6062565256568142</v>
+        <v>-0.6881381992193036</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.779079337719556</v>
+        <v>-1.937359707910573</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.061423985561531</v>
+        <v>1.96645576344692</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539463</v>
+        <v>3.50105255853946</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.434548501262222</v>
+        <v>-9.639252685168445</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.6422624860036037</v>
+        <v>-0.7241441595660931</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.876698615140952</v>
+        <v>-2.03497898533197</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.005894169730461</v>
+        <v>1.91092594761585</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937497</v>
+        <v>3.492448711937496</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.582074589267865</v>
+        <v>-9.786778773174088</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.6983793648842886</v>
+        <v>-0.7802610384467781</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.024224703146596</v>
+        <v>-2.182505073337614</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.920272073248647</v>
+        <v>1.825303851134037</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.5027903991417</v>
+        <v>3.502790399141698</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.786332764597729</v>
+        <v>-9.991036948503952</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.774569437897592</v>
+        <v>-0.856451111460081</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.151863647760585</v>
+        <v>-2.310144017951603</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.849201903598896</v>
+        <v>1.754233681484286</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49685190472989</v>
+        <v>3.496851904729889</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.860665740857893</v>
+        <v>-10.06536992476412</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.7998200739172217</v>
+        <v>-0.8817017474797111</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.296563171695257</v>
+        <v>-2.454843541886275</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.766864743722529</v>
+        <v>1.671896521607918</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440633</v>
+        <v>3.499971739440631</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.787195909190444</v>
+        <v>-9.991900093096667</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.755060439756821</v>
+        <v>-0.83694211331931</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.223093340027809</v>
+        <v>-2.381373710218827</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.826318344216419</v>
+        <v>1.731350122101808</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608599</v>
+        <v>3.490059241608598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-9.962320326576988</v>
+        <v>-10.16702451048321</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.8105549859639214</v>
+        <v>-0.8924366595264104</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.398217757414353</v>
+        <v>-2.556498127605371</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.73579891453201</v>
+        <v>1.640830692417399</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410271</v>
+        <v>3.485878594410269</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.19677242059148</v>
+        <v>-10.4014766044977</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.911554988471313</v>
+        <v>-0.9934366620338024</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.398217757414353</v>
+        <v>-2.556498127605371</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.728579749630414</v>
+        <v>1.633611527515803</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764396</v>
+        <v>3.480692492764394</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.30114715161792</v>
+        <v>-10.50585133552415</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.9599770716558678</v>
+        <v>-1.041858745218357</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.502592488440798</v>
+        <v>-2.660872858631816</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.65928272024057</v>
+        <v>1.564314498125959</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390585</v>
+        <v>3.493716014390583</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.35393330721825</v>
+        <v>-10.55863749112447</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.9799757440574428</v>
+        <v>-1.061857417619931</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.598267975023195</v>
+        <v>-2.756548345214213</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.602993218129688</v>
+        <v>1.508024996015078</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297398</v>
+        <v>3.492101641297396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.47997010058654</v>
+        <v>-10.68467428449276</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.027696732775644</v>
+        <v>-1.109578406338132</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.573016352213453</v>
+        <v>-2.731296722404471</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.620837920444648</v>
+        <v>1.525869698330037</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322543</v>
+        <v>3.573674025322541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.42795458661773</v>
+        <v>-10.63265877052395</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.002900191501717</v>
+        <v>-1.084781865064206</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.573016352213453</v>
+        <v>-2.731296722404471</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.624828256131049</v>
+        <v>1.529860034016438</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158921</v>
+        <v>3.600038265158919</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.56962642834185</v>
+        <v>-10.77433061224807</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.061044155090107</v>
+        <v>-1.142925828652596</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.573016352213453</v>
+        <v>-2.731296722404471</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.623353029232307</v>
+        <v>1.528384807117697</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940719</v>
+        <v>3.691571733940718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.52003558391701</v>
+        <v>-10.72473976782324</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.026154407155301</v>
+        <v>-1.10803608071779</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.523425507788619</v>
+        <v>-2.681705877979637</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.66816094605208</v>
+        <v>1.573192723937469</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.67684154977058</v>
+        <v>3.676841549770578</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.50722819091224</v>
+        <v>-10.71193237481846</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.034082583600074</v>
+        <v>-1.115964257162564</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.57228128279752</v>
+        <v>-2.730561652988538</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.625796347400056</v>
+        <v>1.530828125285446</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615283</v>
+        <v>3.685161381615281</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.28138303819283</v>
+        <v>-10.48608722209905</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.9341654494761022</v>
+        <v>-1.016047123038591</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.530354607210357</v>
+        <v>-2.688634977401374</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.660531425788563</v>
+        <v>1.565563203673952</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812102</v>
+        <v>3.6848438238121</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.15680438185524</v>
+        <v>-10.36150856576146</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.8831948423850062</v>
+        <v>-0.9650765159474957</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.530354607210357</v>
+        <v>-2.688634977401374</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.661670570344622</v>
+        <v>1.566702348230011</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646216</v>
+        <v>3.710935533646214</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.20969966989952</v>
+        <v>-10.41440385380575</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.9017191834406129</v>
+        <v>-0.9836008570031023</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.52539926112191</v>
+        <v>-2.683679631312928</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.667277552159797</v>
+        <v>1.572309330045187</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611568</v>
+        <v>3.768951674611564</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.13756649461164</v>
+        <v>-10.34227067851787</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.8671322090868241</v>
+        <v>-0.9490138826493135</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.52539926112191</v>
+        <v>-2.683679631312928</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.673011256398434</v>
+        <v>1.578043034283823</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955327</v>
+        <v>3.728577929955323</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.06620010200199</v>
+        <v>-10.27090428590822</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.8483229144368307</v>
+        <v>-0.9302045879993202</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.454032868512262</v>
+        <v>-2.61231323870328</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.706093829570358</v>
+        <v>1.611125607455747</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232412</v>
+        <v>3.747702660232409</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.97274106801677</v>
+        <v>-10.17744525192299</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.8208227821556484</v>
+        <v>-0.9027044557181374</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.454032868512262</v>
+        <v>-2.61231323870328</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.69621034825745</v>
+        <v>1.601242126142839</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436228</v>
+        <v>3.766317079436225</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.705499267148372</v>
+        <v>-9.910203451054596</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7157606223076631</v>
+        <v>-0.7976422958701521</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.454032868512262</v>
+        <v>-2.61231323870328</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.694375787758076</v>
+        <v>1.599407565643466</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311949</v>
+        <v>3.784684521311944</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.607592228471882</v>
+        <v>-9.812296412378105</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.6768981218105274</v>
+        <v>-0.7587797953730169</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.386047118651706</v>
+        <v>-2.544327488842724</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.734866922700949</v>
+        <v>1.639898700586339</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097244</v>
+        <v>3.800829354097239</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.583638687495924</v>
+        <v>-9.788342871402147</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.6666481992746509</v>
+        <v>-0.7485298728371399</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.362093577675748</v>
+        <v>-2.520373947866766</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.749907553432017</v>
+        <v>1.654939331317407</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017772</v>
+        <v>3.789311112017767</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.319578749173127</v>
+        <v>-9.52428293307935</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.5742845401072842</v>
+        <v>-0.6561662136697732</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.098033639352952</v>
+        <v>-2.25631400954397</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.895083200263943</v>
+        <v>1.800114978149332</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839726</v>
+        <v>3.833252747839721</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.61249912566829</v>
+        <v>-8.817203309574513</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.2942397243656503</v>
+        <v>-0.3761213979281393</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.098033639352952</v>
+        <v>-2.25631400954397</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.892296166603642</v>
+        <v>1.797327944489031</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.83937444738873</v>
+        <v>3.839374447388725</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.572314827302099</v>
+        <v>-8.777019011208322</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.2778223811313327</v>
+        <v>-0.3597040546938217</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.057849340986762</v>
+        <v>-2.216129711177779</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.916750369511198</v>
+        <v>1.821782147396587</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626476</v>
+        <v>3.85616175162647</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.408914956362736</v>
+        <v>-8.613619140268959</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2130956115348304</v>
+        <v>-0.2949772850973194</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.894449470047399</v>
+        <v>-2.052729840238417</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.014157113295572</v>
+        <v>1.919188891180962</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291811</v>
+        <v>3.787330429291807</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.175433734133136</v>
+        <v>-8.38013791803936</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1117786938051379</v>
+        <v>-0.1936603673676274</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.660968247817801</v>
+        <v>-1.819248618008818</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.162170275471184</v>
+        <v>2.067202053356573</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785788</v>
+        <v>3.801637122785785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.025767343125622</v>
+        <v>-8.230471527031845</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.05480434771509168</v>
+        <v>-0.1366860212775807</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.568064756575265</v>
+        <v>-1.726345126766282</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.215020159903746</v>
+        <v>2.120051937789135</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390428</v>
+        <v>3.763182248390424</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.893491869494736</v>
+        <v>-8.098196053400958</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.006526671515710181</v>
+        <v>-0.08840834507819872</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.435789282944378</v>
+        <v>-1.594069653135396</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.289752930829305</v>
+        <v>2.194784708714694</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105952</v>
+        <v>3.784718794105949</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.737753536934994</v>
+        <v>-7.942457720841216</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.05858372219582364</v>
+        <v>-0.02329795136666535</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.280050950384636</v>
+        <v>-1.438331320575654</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.386010991052787</v>
+        <v>2.291042768938176</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960987</v>
+        <v>3.753882571960983</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.488753738251413</v>
+        <v>-7.693457922157635</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1710899828929144</v>
+        <v>0.08920830933042589</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.280050950384636</v>
+        <v>-1.438331320575654</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.398917332276445</v>
+        <v>2.303949110161835</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607646</v>
+        <v>3.692931855607642</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.594343728024517</v>
+        <v>-7.79904791193074</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.0008780573844542339</v>
+        <v>-0.08100361617803475</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.385640940157741</v>
+        <v>-1.543921310348759</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.207587408813364</v>
+        <v>2.112619186698754</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987903</v>
+        <v>3.7704225839879</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.613078630143114</v>
+        <v>-7.817782814049337</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.04192843841410188</v>
+        <v>-0.03995323514838711</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.391236949817872</v>
+        <v>-1.54951732000889</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.252774144894372</v>
+        <v>2.157805922779761</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710812</v>
+        <v>3.760333686710808</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.465138588735515</v>
+        <v>-7.669842772641737</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.01877446771102598</v>
+        <v>-0.100656141273515</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.370916033909314</v>
+        <v>-1.529196404100332</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.145087771751339</v>
+        <v>2.050119549636728</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409205</v>
+        <v>3.723566229409202</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.412169066481527</v>
+        <v>-7.616873250387749</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.006300645062908838</v>
+        <v>-0.08818231862539783</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.317946511655326</v>
+        <v>-1.476226881846344</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.168155498850254</v>
+        <v>2.073187276735643</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098109</v>
+        <v>3.729969716098106</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.368620659710836</v>
+        <v>-7.573324843617058</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.004158105550274183</v>
+        <v>-0.07772356801221481</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.317946511655326</v>
+        <v>-1.476226881846344</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.161194886755161</v>
+        <v>2.06622666464055</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493419</v>
+        <v>3.782922533493416</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.126472266256978</v>
+        <v>-7.3311764501632</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.1154798173129605</v>
+        <v>0.03359814375047154</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.317946511655326</v>
+        <v>-1.476226881846344</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.175657241136304</v>
+        <v>2.080689019021693</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722816</v>
+        <v>3.828551486722812</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.018213129134456</v>
+        <v>-7.222917313040679</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1533155926211642</v>
+        <v>0.07143391905867524</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.317946511655326</v>
+        <v>-1.476226881846344</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.170189361595499</v>
+        <v>2.075221139480888</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792046</v>
+        <v>3.828052928792042</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.894921994317325</v>
+        <v>-7.099626178223548</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.2001301405585934</v>
+        <v>0.1182484669961044</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.194655376838195</v>
+        <v>-1.352935747029213</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.241662136496354</v>
+        <v>2.146693914381743</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.812453678919903</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.873772795413882</v>
+        <v>-7.078476979320104</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.2162907983572957</v>
+        <v>0.1344091247948072</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.173506177934752</v>
+        <v>-1.33178654812577</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.262052634075745</v>
+        <v>2.167084411961135</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318093</v>
+        <v>3.748328408318089</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.630007353430438</v>
+        <v>-6.83471153733666</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.3095776834977242</v>
+        <v>0.2276960099352352</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.173506177934752</v>
+        <v>-1.33178654812577</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.257833342422796</v>
+        <v>2.162865120308185</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057526</v>
+        <v>3.824311233057522</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.528244533153143</v>
+        <v>-6.732948717059365</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.352407125528658</v>
+        <v>0.2705254519661695</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.160287109542323</v>
+        <v>-1.318567479733341</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.267889097378269</v>
+        <v>2.172920875263658</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279186</v>
+        <v>3.826354974279182</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.278394139204068</v>
+        <v>-6.483098323110291</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4450893580919901</v>
+        <v>0.3632076845295011</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.160287109542323</v>
+        <v>-1.318567479733341</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.260631172361971</v>
+        <v>2.165662950247361</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011499</v>
+        <v>3.835957987011495</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.102502046736635</v>
+        <v>-6.307206230642858</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5190453185996122</v>
+        <v>0.4371636450371228</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.160287109542323</v>
+        <v>-1.318567479733341</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.26423029588262</v>
+        <v>2.169262073768009</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392987</v>
+        <v>3.780933911392983</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.931055583714172</v>
+        <v>-6.135759767620395</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.6009514098631512</v>
+        <v>0.5190697363006618</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.9888406465198601</v>
+        <v>-1.147121016710878</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.380425679750652</v>
+        <v>2.285457457636041</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632782</v>
+        <v>3.773765222632777</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.856766017975833</v>
+        <v>-6.061470201882056</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6296877137747838</v>
+        <v>0.5478060402122944</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.9145510807815209</v>
+        <v>-1.072831450972539</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.424019896809952</v>
+        <v>2.329051674695342</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883074</v>
+        <v>3.764617879883069</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.793130275741898</v>
+        <v>-5.997834459648121</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6598368117226752</v>
+        <v>0.5779551381601857</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.8509153385475864</v>
+        <v>-1.009195708738604</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.46689614320463</v>
+        <v>2.37192792109002</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074785</v>
+        <v>3.798814771074778</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.681703516415978</v>
+        <v>-5.886407700322201</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6856017742368388</v>
+        <v>0.6037201006743493</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.8509153385475864</v>
+        <v>-1.009195708738604</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.448090401988426</v>
+        <v>2.353122179873815</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242296</v>
+        <v>3.797694884242289</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.441273019611118</v>
+        <v>-5.645977203517341</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7835170495836601</v>
+        <v>0.7016353760211711</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.6104848417427261</v>
+        <v>-0.7687652119337436</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.594091776696219</v>
+        <v>2.499123554581609</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367687</v>
+        <v>3.82159350936768</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.369030451439923</v>
+        <v>-5.573734635346146</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8163433906869582</v>
+        <v>0.7344617171244692</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.6104848417427261</v>
+        <v>-0.7687652119337436</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.598021090531039</v>
+        <v>2.503052868416429</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879968</v>
+        <v>3.822326997879961</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.316032129158535</v>
+        <v>-5.520736313064758</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8382213035168533</v>
+        <v>0.7563396299543643</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.5551485827407873</v>
+        <v>-0.7134289529318047</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.631901429849543</v>
+        <v>2.536933207734932</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502341</v>
+        <v>3.848616626502334</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.207227243678808</v>
+        <v>-5.411931427585031</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8787413289287378</v>
+        <v>0.7968596553662484</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.5551485827407873</v>
+        <v>-0.7134289529318047</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.628899501069536</v>
+        <v>2.533931278954926</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675943</v>
+        <v>3.818668951675935</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.987206445641798</v>
+        <v>-5.191910629548021</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9683286851541562</v>
+        <v>0.8864470115916667</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.413928737672807</v>
+        <v>-0.5722091078638245</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.715210445120939</v>
+        <v>2.620242223006328</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539954</v>
+        <v>3.843274527539946</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.85433875657852</v>
+        <v>-5.059042940484743</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.03736994358129</v>
+        <v>0.955488270018801</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.413928737672807</v>
+        <v>-0.5722091078638245</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.731104627922762</v>
+        <v>2.636136405808151</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496263</v>
+        <v>3.845047386496257</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.734165673214021</v>
+        <v>-4.938869857120245</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.086585021367392</v>
+        <v>1.004703347804903</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.2937556543083081</v>
+        <v>-0.4520360244993256</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.804354322381763</v>
+        <v>2.709386100267153</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577</v>
+        <v>3.791273551576994</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.589493528114284</v>
+        <v>-4.794197712020507</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.154541981968727</v>
+        <v>1.072660308406237</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.1490835092085707</v>
+        <v>-0.3073638793995881</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.901245712003045</v>
+        <v>2.806277489888435</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942104</v>
+        <v>3.735839222942099</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.649368355471976</v>
+        <v>-4.854072539378199</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.116629542427076</v>
+        <v>1.034747868864586</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.2089583365662628</v>
+        <v>-0.3672387067572803</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.851358306989856</v>
+        <v>2.756390084875245</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674516</v>
+        <v>3.762647477674511</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.562568857692968</v>
+        <v>-4.767273041599191</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.173749834861245</v>
+        <v>1.091868161298756</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.2089583365662628</v>
+        <v>-0.3672387067572803</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.873758800312422</v>
+        <v>2.778790578197811</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430697</v>
+        <v>3.729146398430691</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.565038564154774</v>
+        <v>-4.769742748060997</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.172834353649935</v>
+        <v>1.090952680087445</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.2114280430280689</v>
+        <v>-0.3697084132190864</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.87234937780875</v>
+        <v>2.77738115569414</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003604</v>
+        <v>3.743220196003598</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.633408750478784</v>
+        <v>-4.838112934385007</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.156493201595033</v>
+        <v>1.074611528032543</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.202152343991854</v>
+        <v>-0.3604327141828715</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.888921719705182</v>
+        <v>2.793953497590571</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508372</v>
+        <v>3.714179139508365</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.647196803325831</v>
+        <v>-4.851900987232054</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.141414689088105</v>
+        <v>1.059533015525616</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.202152343991854</v>
+        <v>-0.3604327141828715</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.879358428337073</v>
+        <v>2.784390206222462</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417706</v>
+        <v>3.710906731417699</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.678189962654536</v>
+        <v>-4.882894146560759</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9537269903970098</v>
+        <v>0.8718453168345206</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.202152343991854</v>
+        <v>-0.3604327141828715</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.70406799337746</v>
+        <v>2.609099771262849</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205903</v>
+        <v>3.746042526205896</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.502715702862067</v>
+        <v>-4.707419886768291</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.028483926305785</v>
+        <v>0.946602252743296</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.202152343991854</v>
+        <v>-0.3604327141828715</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.708635225369247</v>
+        <v>2.613667003254637</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225448</v>
+        <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.613651955503316</v>
+        <v>-4.81835613940954</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9598514540104928</v>
+        <v>0.8779697804480033</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.202152343991854</v>
+        <v>-0.3604327141828715</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.684377254130454</v>
+        <v>2.589409032015844</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111295</v>
+        <v>3.773210297111291</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.579988410031034</v>
+        <v>-4.784692593937257</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9764482574193112</v>
+        <v>0.8945665838568218</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.1684887985195722</v>
+        <v>-0.3267691687105896</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.707706766633729</v>
+        <v>2.612738544519118</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264164</v>
+        <v>3.784343952264161</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.520135790827311</v>
+        <v>-4.724839974733534</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.010561691532933</v>
+        <v>0.9286800179704435</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.1684887985195722</v>
+        <v>-0.3267691687105896</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.717879153065861</v>
+        <v>2.622910930951251</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742297</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.433892327800933</v>
+        <v>-4.638596511707156</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.040005347317344</v>
+        <v>0.9581236737548549</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.1684887985195722</v>
+        <v>-0.3267691687105896</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.712825423639722</v>
+        <v>2.617857201525111</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316048</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.479199147199913</v>
+        <v>-4.683903331106136</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.013658395002278</v>
+        <v>0.9317767214397885</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.209298961528803</v>
+        <v>-0.3675793317198204</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.680115101278709</v>
+        <v>2.585146879164098</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803192</v>
+        <v>3.753571165803189</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.508232251902214</v>
+        <v>-4.712936435808437</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.002597026154459</v>
+        <v>0.9207153525919696</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.209298961528803</v>
+        <v>-0.3675793317198204</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.68066697431181</v>
+        <v>2.5856987521972</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809499</v>
+        <v>3.733390600809495</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.415421770451355</v>
+        <v>-4.620125954357578</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9689939106261685</v>
+        <v>0.887112237063679</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.1164884800779436</v>
+        <v>-0.2747688502689611</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.665625955073692</v>
+        <v>2.570657732959081</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560423</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.459811239780782</v>
+        <v>-4.664515423687005</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9531115988189982</v>
+        <v>0.871229925256509</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.1608779494073713</v>
+        <v>-0.3191583195983888</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.640865749400636</v>
+        <v>2.545897527286025</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.72107719547274</v>
+        <v>3.721077195472736</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.347140021544532</v>
+        <v>-4.551844205450755</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9932557946252212</v>
+        <v>0.911374121062732</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.04820673117112106</v>
+        <v>-0.2064871013621385</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.703544188854109</v>
+        <v>2.608575966739498</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798539</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.234763020361859</v>
+        <v>-4.439467204268082</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.043697890928958</v>
+        <v>0.9618162173664684</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.04820673117112106</v>
+        <v>-0.2064871013621385</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.709035484684776</v>
+        <v>2.614067262570166</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498867</v>
+        <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.262543418263212</v>
+        <v>-4.467247602169435</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.044082933536956</v>
+        <v>0.9622012599744665</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.07598712907247412</v>
+        <v>-0.2342674992634916</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.703864447712503</v>
+        <v>2.608896225597893</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705327</v>
+        <v>3.643069621705323</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.345544699288491</v>
+        <v>-4.550248883194714</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8492381411274974</v>
+        <v>0.7673564675650082</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.09455801359964788</v>
+        <v>-0.2528383837906654</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.531077636996852</v>
+        <v>2.436109414882242</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729271</v>
+        <v>3.682716310729268</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.454158777731822</v>
+        <v>-4.658862961638045</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9259421704693707</v>
+        <v>0.8440604969068812</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.09455801359964788</v>
+        <v>-0.2528383837906654</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.651227297716058</v>
+        <v>2.556259075601448</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190771</v>
+        <v>3.733012441190765</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.418749739483679</v>
+        <v>-4.623453923389902</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9546188118709507</v>
+        <v>0.8727371383084614</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.09455801359964788</v>
+        <v>-0.2528383837906654</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.665740323818381</v>
+        <v>2.570772101703771</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913428</v>
+        <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.380366076925528</v>
+        <v>-4.585070260831751</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9673917182365799</v>
+        <v>0.8855100446740907</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.05617435104149671</v>
+        <v>-0.2144547212325142</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.68618996269564</v>
+        <v>2.59122174058103</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532489</v>
+        <v>3.751147197532482</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.203249746890362</v>
+        <v>-4.407953930796585</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.034967279095948</v>
+        <v>0.9530856055334589</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.05617435104149671</v>
+        <v>-0.2144547212325142</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.682918991540942</v>
+        <v>2.587950769426332</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793906</v>
+        <v>3.7413284487939</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.248341991723907</v>
+        <v>-4.45304617563013</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.017613772924443</v>
+        <v>0.9357320993619538</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.1180703942108865</v>
+        <v>-0.276350764401904</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.646464757401222</v>
+        <v>2.551496535286611</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011239</v>
+        <v>3.750729377011233</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.06896657048514</v>
+        <v>-4.273670754391363</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.083150916726364</v>
+        <v>1.001269243163875</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.03870636395983218</v>
+        <v>-0.1195740062311853</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.734317787610067</v>
+        <v>2.639349565495456</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982233</v>
+        <v>3.716991718982227</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.113980784005745</v>
+        <v>-4.318684967911969</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.045952686649712</v>
+        <v>0.9640710130872225</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.008357468645227573</v>
+        <v>-0.1499229015457899</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.696915905752894</v>
+        <v>2.601947683638284</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509542</v>
+        <v>3.737026608509535</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.38098529427818</v>
+        <v>-4.585689478184404</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9448424448796837</v>
+        <v>0.8629607713171943</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.186005569397721</v>
+        <v>-0.3442859395887385</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.585989645266071</v>
+        <v>2.49102142315146</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760813</v>
+        <v>3.702309454760808</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.482183075715353</v>
+        <v>-4.686887259621576</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.903567254201316</v>
+        <v>0.8216855806388268</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.2544143829430402</v>
+        <v>-0.4126947531340577</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.54414827903538</v>
+        <v>2.44918005692077</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815453</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.449707489544581</v>
+        <v>-4.654411673450804</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9141574502239416</v>
+        <v>0.8322757766614524</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.2544143829430402</v>
+        <v>-0.4126947531340577</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.541748240589697</v>
+        <v>2.446780018475087</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378102</v>
+        <v>3.709510443378098</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.430669361837284</v>
+        <v>-4.635373545743507</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9182974205151053</v>
+        <v>0.8364157469526161</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.3125979942742347</v>
+        <v>-0.4708783644652522</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.503362792999225</v>
+        <v>2.408394570884615</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131253</v>
+        <v>3.731064473131248</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.461795992987902</v>
+        <v>-4.666500176894125</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.083428636993539</v>
+        <v>1.001546963431049</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.3125979942742347</v>
+        <v>-0.4708783644652522</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.680944661937906</v>
+        <v>2.585976439823296</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067869</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.47566275432182</v>
+        <v>-4.680366938228043</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.078715261446105</v>
+        <v>0.9968335878836156</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.3504559110080577</v>
+        <v>-0.5087362811990752</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.659063240883746</v>
+        <v>2.564095018769136</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789125</v>
+        <v>3.787425580789119</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.43085858278189</v>
+        <v>-4.635562766688113</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.102645460459003</v>
+        <v>1.020763786896514</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.3504559110080577</v>
+        <v>-0.5087362811990752</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.665071771280672</v>
+        <v>2.570103549166062</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519912</v>
+        <v>3.781501250519905</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.283115612546887</v>
+        <v>-4.487819796453111</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.240895296345026</v>
+        <v>1.159013622782537</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.1826485537731745</v>
+        <v>-0.3409289239641921</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.844908833413624</v>
+        <v>2.749940611299013</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181174</v>
+        <v>3.802245929181167</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.385130295078109</v>
+        <v>-4.589834478984332</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.202883044864018</v>
+        <v>1.121001371301529</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.1826485537731745</v>
+        <v>-0.3409289239641921</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.847702454945105</v>
+        <v>2.752734232830494</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394734</v>
+        <v>3.805608985394726</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.378977589025324</v>
+        <v>-4.583681772931548</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.20600647567679</v>
+        <v>1.124124802114301</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.1764958477203902</v>
+        <v>-0.3347762179114078</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.852056426968434</v>
+        <v>2.757088204853823</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.798239794890607</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.395786887175826</v>
+        <v>-4.600491071082049</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.1983632331567</v>
+        <v>1.116481559594211</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.1933051458708919</v>
+        <v>-0.3515855160619094</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.841051324818243</v>
+        <v>2.746083102703632</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798428</v>
+        <v>3.867362636798423</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.333488888399704</v>
+        <v>-4.538193072305927</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.28961798646397</v>
+        <v>1.20773631290148</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.1933051458708919</v>
+        <v>-0.3515855160619094</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.907386878615064</v>
+        <v>2.812418656500453</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992195</v>
+        <v>3.848729139992187</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.131698690734546</v>
+        <v>-4.336402874640769</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.078914937919431</v>
+        <v>0.9970332643569417</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.004713046298262524</v>
+        <v>-0.153567323892755</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.734778666305954</v>
+        <v>2.639810444191344</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852425</v>
+        <v>3.84144481785242</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.071808009091953</v>
+        <v>-4.276512192998176</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.173161442898643</v>
+        <v>1.091279769336154</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.064603727940856</v>
+        <v>-0.09367664225016153</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.841003307613686</v>
+        <v>2.746035085499075</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.81906330031955</v>
+        <v>3.819063300319542</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.169548553716927</v>
+        <v>-4.37425273762315</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.148692961164697</v>
+        <v>1.066811287602208</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.04871444980787581</v>
+        <v>-0.1095659203831417</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.846097476849941</v>
+        <v>2.751129254735331</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489388</v>
+        <v>3.831819032489381</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.345886313839856</v>
+        <v>-4.55059049774608</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.076693837940197</v>
+        <v>0.9948121643777079</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.1276233103150536</v>
+        <v>-0.2859036805060711</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.738830801600855</v>
+        <v>2.643862579486245</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397798</v>
+        <v>3.836411672397791</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.26946426740793</v>
+        <v>-4.474168451314153</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.105754274552897</v>
+        <v>1.023872600990407</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.1276233103150536</v>
+        <v>-0.2859036805060711</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.737322419640784</v>
+        <v>2.642354197526173</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024966</v>
+        <v>3.836023391024959</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.225091135769361</v>
+        <v>-4.429795319675584</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.12336639464376</v>
+        <v>1.041484721081271</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.08325017867648499</v>
+        <v>-0.2415305488675025</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.763809166059361</v>
+        <v>2.668840943944751</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863226</v>
+        <v>3.82159115086322</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.217137165474589</v>
+        <v>-4.421841349380812</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.126547982761669</v>
+        <v>1.04466630919918</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.08325017867648499</v>
+        <v>-0.2415305488675025</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.763809166059361</v>
+        <v>2.668840943944751</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947585</v>
+        <v>3.833040181947579</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.169481434913533</v>
+        <v>-4.374185618819756</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.151992032013896</v>
+        <v>1.070110358451407</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.03559444811542933</v>
+        <v>-0.1938748183064469</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.798784361423799</v>
+        <v>2.703816139309189</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326876</v>
+        <v>3.822707244326871</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.041797125119237</v>
+        <v>-4.24650130902546</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.20795812930634</v>
+        <v>1.12607645574385</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.09208986167886712</v>
+        <v>-0.06619050851215041</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.880287320675102</v>
+        <v>2.785319098560491</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314552</v>
+        <v>3.828837911314547</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.102463715521626</v>
+        <v>-4.307167899427849</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.170446165621256</v>
+        <v>1.088564492058766</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.01039154496033345</v>
+        <v>-0.1478888252306841</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.818023003119854</v>
+        <v>2.723054781005243</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690027</v>
+        <v>3.816866067690022</v>
       </c>
       <c r="C1981" t="n">
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.057625313913228</v>
+        <v>-4.262329497819451</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.192479228875244</v>
+        <v>1.110597555312755</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.01493497790520293</v>
+        <v>-0.1433453922858146</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.824846765497404</v>
+        <v>2.729878543382794</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674311</v>
+        <v>3.817961388674306</v>
       </c>
       <c r="C1982" t="n">
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.158383949670226</v>
+        <v>-4.363088133576449</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.156336714203523</v>
+        <v>1.074455040641033</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.07389059082180249</v>
+        <v>-0.23217096101282</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.775712363892279</v>
+        <v>2.680744141777669</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826713779163221</v>
+        <v>3.826713779163216</v>
       </c>
       <c r="C1983" t="n">
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.114181112584325</v>
+        <v>-4.318885296490548</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.17989745156572</v>
+        <v>1.098015778003231</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.02968775373590204</v>
+        <v>-0.1879681239269196</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.808113668671656</v>
+        <v>2.713145446557046</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022905</v>
+        <v>3.8382286630229</v>
       </c>
       <c r="C1984" t="n">
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.151160140247768</v>
+        <v>-4.355864324153991</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.16351584096959</v>
+        <v>1.081634167407101</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.007286148055428487</v>
+        <v>-0.1509942221355891</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.828708010215702</v>
+        <v>2.733739788101092</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042139</v>
+        <v>3.863924114042133</v>
       </c>
       <c r="C1985" t="n">
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.171218219112609</v>
+        <v>-4.375922403018832</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.206740374606694</v>
+        <v>1.124858701044205</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.007286148055428487</v>
+        <v>-0.1509942221355891</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.879955775398742</v>
+        <v>2.784987553284132</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865367715078282</v>
+        <v>3.865367715078275</v>
       </c>
       <c r="C1986" t="n">
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.131287545934718</v>
+        <v>-4.335991729840941</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.221153348472103</v>
+        <v>1.139271674909614</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.04721682123331883</v>
+        <v>-0.1110635489576987</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.902354883899729</v>
+        <v>2.807386661785118</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232399</v>
+        <v>3.864518876232392</v>
       </c>
       <c r="C1987" t="n">
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.080255453212191</v>
+        <v>-4.284959637118414</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.236514413799384</v>
+        <v>1.154632740236895</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.09824891395584678</v>
+        <v>-0.06003145623517075</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.927922367771516</v>
+        <v>2.832954145656906</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842576394162115</v>
+        <v>3.842576394162107</v>
       </c>
       <c r="C1988" t="n">
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.015031272084985</v>
+        <v>-4.219735455991208</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.279791490342971</v>
+        <v>1.197909816780482</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.1634730950830524</v>
+        <v>0.005192724892034872</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.984244280540544</v>
+        <v>2.889276058425934</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840090220639818</v>
+        <v>3.840090220639811</v>
       </c>
       <c r="C1989" t="n">
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.977604252013851</v>
+        <v>-4.182308435920074</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.290723270670705</v>
+        <v>1.208841597108216</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.1687246331122341</v>
+        <v>0.01044426292121653</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.983356175657334</v>
+        <v>2.888387953542723</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845198842749923</v>
+        <v>3.845198842749916</v>
       </c>
       <c r="C1990" t="n">
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.99771590804856</v>
+        <v>-4.202420091954782</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.283935400588062</v>
+        <v>1.202053727025573</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.1797519781096533</v>
+        <v>0.02147160791863573</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.991229374987026</v>
+        <v>2.896261152872415</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.82869047939355</v>
+        <v>3.828690479393541</v>
       </c>
       <c r="C1991" t="n">
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.943971093621355</v>
+        <v>-4.148675277527578</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.465991097380155</v>
+        <v>1.384109423817666</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.1898152875501152</v>
+        <v>0.03153491735909769</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.157825131672513</v>
+        <v>3.062856909557903</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813251854714887</v>
+        <v>3.813251854714879</v>
       </c>
       <c r="C1992" t="n">
         <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.920179525015213</v>
+        <v>-4.124883708921436</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.595620634040429</v>
+        <v>1.51373896047794</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.2136068561562575</v>
+        <v>0.05532648596523998</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.292212982054016</v>
+        <v>3.197244759939406</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814259761756013</v>
+        <v>3.814259761756007</v>
       </c>
       <c r="C1993" t="n">
         <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.894095440751405</v>
+        <v>-4.098799624657627</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.597762243759811</v>
+        <v>1.515880570197322</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.2136068561562575</v>
+        <v>0.05532648596523998</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.283920958067875</v>
+        <v>3.188952735953265</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803426852654187</v>
+        <v>3.803426852654182</v>
       </c>
       <c r="C1994" t="n">
         <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.889761137694356</v>
+        <v>-4.09446532160058</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.59768916056641</v>
+        <v>1.515807487003921</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.3652569594754614</v>
+        <v>0.2069765892844439</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.373104215643177</v>
+        <v>3.278135993528566</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796293177717118</v>
+        <v>3.796293177717112</v>
       </c>
       <c r="C1995" t="n">
         <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.880868676301073</v>
+        <v>-4.085572860207296</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.618800550850514</v>
+        <v>1.536918877288025</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.3652569594754614</v>
+        <v>0.2069765892844439</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.390658621369968</v>
+        <v>3.295690399255358</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794453975702627</v>
+        <v>3.794453975702622</v>
       </c>
       <c r="C1996" t="n">
         <v>3.163359493089275</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.049344793270951</v>
+        <v>-4.254048977177174</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.543265151467147</v>
+        <v>1.461383477904658</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.3373091237588807</v>
+        <v>0.1790287535678631</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.365744967344604</v>
+        <v>3.270776745229993</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795603100539969</v>
+        <v>3.795603100539963</v>
       </c>
       <c r="C1997" t="n">
         <v>3.144629190277137</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.351545264409368</v>
+        <v>-3.556249448315591</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.803654660199643</v>
+        <v>1.721772986637153</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.2669610643884699</v>
+        <v>0.1086806941974524</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.304805828910219</v>
+        <v>3.209837606795609</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784700379389899</v>
+        <v>3.784700379389891</v>
       </c>
       <c r="C1998" t="n">
         <v>3.135293212774041</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.328824160726215</v>
+        <v>-3.533528344632438</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.803407124169808</v>
+        <v>1.721525450607319</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.2669610643884699</v>
+        <v>0.1086806941974524</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.295469851407124</v>
+        <v>3.200501629292513</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783234730534937</v>
+        <v>3.78323473053493</v>
       </c>
       <c r="C1999" t="n">
         <v>3.29419933862521</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.469116760263407</v>
+        <v>-3.673820944169631</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.9061962102061</v>
+        <v>1.824314536643611</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.1266684648512773</v>
+        <v>-0.03161190533974023</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.370200417535977</v>
+        <v>3.275232195421367</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779962759401675</v>
+        <v>3.779962759401668</v>
       </c>
       <c r="C2000" t="n">
         <v>3.331277161118857</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.623897767041663</v>
+        <v>-3.828601950947886</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.881361629988445</v>
+        <v>1.799479956425955</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.0933007907968012</v>
+        <v>-0.06497957939421634</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.387257635596938</v>
+        <v>3.292289413482327</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769472653557223</v>
+        <v>3.769472653557218</v>
       </c>
       <c r="C2001" t="n">
         <v>3.327952517108402</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.69115821106358</v>
+        <v>-3.895862394969803</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.851132808369223</v>
+        <v>1.769251134806734</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.02604034677488409</v>
+        <v>-0.1322400234161334</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.343576725173333</v>
+        <v>3.248608503058722</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766702530088378</v>
+        <v>3.766702530088374</v>
       </c>
       <c r="C2002" t="n">
         <v>3.337958670753144</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.668686677024748</v>
+        <v>-3.873390860930971</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.870127575629497</v>
+        <v>1.788245902067008</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.1617458315908553</v>
+        <v>0.003465461399837777</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.435006169707657</v>
+        <v>3.340037947593046</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,45 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.827613531393259</v>
+        <v>3.76808110154137</v>
       </c>
       <c r="C2003" t="n">
         <v>3.522061802898103</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.804639685081064</v>
+        <v>-3.874335788345376</v>
       </c>
       <c r="E2003" t="n">
-        <v>1.999849504551931</v>
+        <v>1.971971063246206</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.1617458315908553</v>
+        <v>0.003465461399837777</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.619109301852617</v>
+        <v>3.524141079738006</v>
+      </c>
+    </row>
+    <row r="2004">
+      <c r="A2004" s="2" t="n">
+        <v>45466</v>
+      </c>
+      <c r="B2004" t="n">
+        <v>3.747866136782537</v>
+      </c>
+      <c r="C2004" t="n">
+        <v>3.619143054518755</v>
+      </c>
+      <c r="D2004" t="n">
+        <v>-3.874335788345376</v>
+      </c>
+      <c r="E2004" t="n">
+        <v>1.971971063246206</v>
+      </c>
+      <c r="F2004" t="n">
+        <v>0.003465461399837777</v>
+      </c>
+      <c r="G2004" t="n">
+        <v>3.612206851505123</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240623.xlsx
+++ b/tame_output/ON/bt/strategyON_20240623.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,12 +610,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>54.7%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>79.8%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>37.7%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>63.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-6.9%</t>
+          <t>-5.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>50.3%</t>
+          <t>51.2%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-74.5%</t>
+          <t>-73.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.0%</t>
+          <t>108.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.6%</t>
+          <t>121.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-692.0%</t>
+          <t>-671.4%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>23.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.9%</t>
+          <t>-51.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.1%</t>
+          <t>-69.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.4%</t>
+          <t>89.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>459.2%</t>
+          <t>461.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-12.9%</t>
+          <t>-12.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-549.0%</t>
+          <t>-541.9%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.7%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.5%</t>
+          <t>99.4%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-277.2%</t>
+          <t>-269.0%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-40.5%</t>
+          <t>-39.8%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-31.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>120.7%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-179.0%</t>
+          <t>-180.7%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-23.0%</t>
+          <t>-20.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-300.5%</t>
+          <t>-284.5%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-33.2%</t>
+          <t>-32.2%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-16.3%</t>
+          <t>-13.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-3.6%</t>
+          <t>-2.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-171.6%</t>
+          <t>-227.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-223.6%</t>
+          <t>-207.7%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.9%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.2%</t>
+          <t>95.8%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-180.7%</t>
+          <t>-171.1%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.6%</t>
+          <t>-27.7%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.9%</t>
+          <t>-16.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-84.8%</t>
+          <t>-83.9%</t>
         </is>
       </c>
     </row>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.31588437417824</v>
+        <v>3.315884374178241</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.069732473107872</v>
+        <v>-4.863803359533784</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.095822120473888</v>
+        <v>1.178193765903523</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.7716818011309712</v>
+        <v>-0.6118274807080977</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.661062453352201</v>
+        <v>2.756975045605925</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310977</v>
+        <v>3.284619513310978</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.304426467240424</v>
+        <v>-5.098497353666336</v>
       </c>
       <c r="E1860" t="n">
-        <v>0.9902292978229577</v>
+        <v>1.072600943252593</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.765345533901716</v>
+        <v>-0.6054912134788425</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.653148988691845</v>
+        <v>2.749061580945569</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,22 +44348,22 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006529</v>
+        <v>3.30584953900653</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.640089114470877</v>
+        <v>-5.434160000896789</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8545448305867418</v>
+        <v>0.9369164760163771</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.8332765193906209</v>
+        <v>-0.6734221989677474</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.610970989054468</v>
+        <v>2.706883581308191</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.31108639130942</v>
+        <v>3.311086391309421</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-6.00371535937119</v>
+        <v>-5.797786245797102</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7155818928608579</v>
+        <v>0.7979535382904932</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.9314981562577467</v>
+        <v>-0.7716438358348732</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.558525567168433</v>
+        <v>2.654438159422158</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970901</v>
+        <v>3.304715716970902</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.368842742009937</v>
+        <v>-6.162913628435849</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5687854548111906</v>
+        <v>0.6511571002408258</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.227808940556759</v>
+        <v>-1.067954620133886</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.379993611594857</v>
+        <v>2.475906203848582</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.777431519190616</v>
+        <v>-6.571502405616528</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4041114879536778</v>
+        <v>0.4864831333833131</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.636397717737438</v>
+        <v>-1.476543397314564</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.133601889301209</v>
+        <v>2.229514481554934</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191733</v>
+        <v>3.302618194191734</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.054007619506448</v>
+        <v>-6.84807850593236</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.2886664802988057</v>
+        <v>0.371038125728441</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.636397717737438</v>
+        <v>-1.476543397314564</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.12878732177267</v>
+        <v>2.224699914026394</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108634</v>
+        <v>3.305023265108635</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.470399493793446</v>
+        <v>-7.264470380219358</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.120103781192884</v>
+        <v>0.2024754266225193</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.636397717737438</v>
+        <v>-1.476543397314564</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.126781372381547</v>
+        <v>2.222693964635272</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097816</v>
+        <v>3.341378723097817</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.714670894520515</v>
+        <v>-7.508741780946427</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.03265391157073516</v>
+        <v>0.1150255570003704</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.636397717737438</v>
+        <v>-1.476543397314564</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.137040063050226</v>
+        <v>2.232952655303951</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094112</v>
+        <v>3.374439043094113</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.919921913757276</v>
+        <v>-7.713992800183187</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.05334693097827392</v>
+        <v>0.02902471445136134</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.636397717737438</v>
+        <v>-1.476543397314564</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.133139628195922</v>
+        <v>2.229052220449645</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199281</v>
+        <v>3.405960511199282</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.083501791941659</v>
+        <v>-7.877572678367571</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1203739621970263</v>
+        <v>-0.03800231676739108</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.636397717737438</v>
+        <v>-1.476543397314564</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.131544548250923</v>
+        <v>2.227457140504646</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969589</v>
+        <v>3.42463335496959</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.380163133751857</v>
+        <v>-8.174234020177769</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2352595229918975</v>
+        <v>-0.1528878775622622</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.705140853471316</v>
+        <v>-1.545286533048443</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.094077642739804</v>
+        <v>2.189990234993528</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923082</v>
+        <v>3.419979433923083</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.56688284206116</v>
+        <v>-8.360953728487072</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.3139737108500213</v>
+        <v>-0.2316020654203861</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.705140853471316</v>
+        <v>-1.545286533048443</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.0900513382054</v>
+        <v>2.185963930459125</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297744</v>
+        <v>3.458100091297745</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.949884230803791</v>
+        <v>-8.743955117229703</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.4672763676686582</v>
+        <v>-0.3849047222390229</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.705140853471316</v>
+        <v>-1.545286533048443</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.089949236883816</v>
+        <v>2.18586182913754</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317612</v>
+        <v>3.447750501317613</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.131754021788826</v>
+        <v>-8.925824908214738</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.5374527680912418</v>
+        <v>-0.4550811226616065</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.887010644456351</v>
+        <v>-1.727156324033478</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.983398878264226</v>
+        <v>2.07931147051795</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737166</v>
+        <v>3.503515506737167</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.491284344292827</v>
+        <v>-9.285355230718739</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.6759145937947921</v>
+        <v>-0.5935429483651569</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.887010644456351</v>
+        <v>-1.727156324033478</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.988749181562276</v>
+        <v>2.084661773816</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341309</v>
+        <v>3.50317028234131</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.541633407747049</v>
+        <v>-9.335704294172961</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.6881381992193036</v>
+        <v>-0.6057665537896684</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.937359707910573</v>
+        <v>-1.7775053874877</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.96645576344692</v>
+        <v>2.062368355700644</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50105255853946</v>
+        <v>3.501052558539461</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.639252685168445</v>
+        <v>-9.433323571594357</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.7241441595660931</v>
+        <v>-0.6417725141364579</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.03497898533197</v>
+        <v>-1.875124664909096</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.91092594761585</v>
+        <v>2.006838539869575</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937496</v>
+        <v>3.492448711937497</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.786778773174088</v>
+        <v>-9.5808496596</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.7802610384467781</v>
+        <v>-0.6978893930171428</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.182505073337614</v>
+        <v>-2.02265075291474</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.825303851134037</v>
+        <v>1.921216443387761</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141698</v>
+        <v>3.502790399141699</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.991036948503952</v>
+        <v>-9.785107834929864</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.856451111460081</v>
+        <v>-0.7740794660304458</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.310144017951603</v>
+        <v>-2.150289697528729</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.754233681484286</v>
+        <v>1.85014627373801</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729889</v>
+        <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.06536992476412</v>
+        <v>-9.859440811190028</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.8817017474797111</v>
+        <v>-0.7993301020500758</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.454843541886275</v>
+        <v>-2.294989221463402</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.671896521607918</v>
+        <v>1.767809113861642</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440631</v>
+        <v>3.499971739440632</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.991900093096667</v>
+        <v>-9.785970979522579</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.83694211331931</v>
+        <v>-0.7545704678896747</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.381373710218827</v>
+        <v>-2.221519389795953</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.731350122101808</v>
+        <v>1.827262714355533</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.16702451048321</v>
+        <v>-9.961095396909123</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.8924366595264104</v>
+        <v>-0.8100650140967756</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.556498127605371</v>
+        <v>-2.396643807182497</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.640830692417399</v>
+        <v>1.736743284671123</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410269</v>
+        <v>3.48587859441027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.4014766044977</v>
+        <v>-10.19554749092361</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.9934366620338024</v>
+        <v>-0.9110650166041672</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.556498127605371</v>
+        <v>-2.396643807182497</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.633611527515803</v>
+        <v>1.729524119769527</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764394</v>
+        <v>3.480692492764395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.50585133552415</v>
+        <v>-10.29992222195006</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.041858745218357</v>
+        <v>-0.9594870997887219</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.660872858631816</v>
+        <v>-2.501018538208943</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.564314498125959</v>
+        <v>1.660227090379683</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390583</v>
+        <v>3.493716014390584</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.55863749112447</v>
+        <v>-10.35270837755039</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.061857417619931</v>
+        <v>-0.9794857721902961</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.756548345214213</v>
+        <v>-2.59669402479134</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.508024996015078</v>
+        <v>1.603937588268801</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297396</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.68467428449276</v>
+        <v>-10.47874517091867</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.109578406338132</v>
+        <v>-1.027206760908497</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.731296722404471</v>
+        <v>-2.571442401981598</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.525869698330037</v>
+        <v>1.621782290583762</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322541</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.63265877052395</v>
+        <v>-10.42672965694986</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.084781865064206</v>
+        <v>-1.002410219634571</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.731296722404471</v>
+        <v>-2.571442401981598</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.529860034016438</v>
+        <v>1.625772626270162</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158919</v>
+        <v>3.60003826515892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.77433061224807</v>
+        <v>-10.56840149867398</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.142925828652596</v>
+        <v>-1.060554183222961</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.731296722404471</v>
+        <v>-2.571442401981598</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.528384807117697</v>
+        <v>1.624297399371421</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940718</v>
+        <v>3.691571733940719</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.72473976782324</v>
+        <v>-10.51881065424915</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.10803608071779</v>
+        <v>-1.025664435288155</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.681705877979637</v>
+        <v>-2.521851557556764</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.573192723937469</v>
+        <v>1.669105316191193</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770578</v>
+        <v>3.676841549770579</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.71193237481846</v>
+        <v>-10.50600326124437</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.115964257162564</v>
+        <v>-1.033592611732928</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.730561652988538</v>
+        <v>-2.570707332565665</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.530828125285446</v>
+        <v>1.626740717539169</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615281</v>
+        <v>3.685161381615282</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.48608722209905</v>
+        <v>-10.28015810852496</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.016047123038591</v>
+        <v>-0.9336754776089555</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.688634977401374</v>
+        <v>-2.528780656978501</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.565563203673952</v>
+        <v>1.661475795927676</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848438238121</v>
+        <v>3.684843823812101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.36150856576146</v>
+        <v>-10.15557945218737</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.9650765159474957</v>
+        <v>-0.8827048705178595</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.688634977401374</v>
+        <v>-2.528780656978501</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.566702348230011</v>
+        <v>1.662614940483735</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646214</v>
+        <v>3.710935533646215</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.41440385380575</v>
+        <v>-10.20847474023166</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.9836008570031023</v>
+        <v>-0.9012292115734661</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.683679631312928</v>
+        <v>-2.523825310890055</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.572309330045187</v>
+        <v>1.668221922298911</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611564</v>
+        <v>3.768951674611566</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.34227067851787</v>
+        <v>-10.13634156494378</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.9490138826493135</v>
+        <v>-0.8666422372196774</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.683679631312928</v>
+        <v>-2.523825310890055</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.578043034283823</v>
+        <v>1.673955626537547</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955323</v>
+        <v>3.728577929955326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.27090428590822</v>
+        <v>-10.06497517233413</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.9302045879993202</v>
+        <v>-0.847832942569684</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.61231323870328</v>
+        <v>-2.452458918280407</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.611125607455747</v>
+        <v>1.707038199709471</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232409</v>
+        <v>3.747702660232411</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.17744525192299</v>
+        <v>-9.971516138348903</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.9027044557181374</v>
+        <v>-0.8203328102885017</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.61231323870328</v>
+        <v>-2.452458918280407</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.601242126142839</v>
+        <v>1.697154718396563</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436225</v>
+        <v>3.766317079436227</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.910203451054596</v>
+        <v>-9.704274337480506</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7976422958701521</v>
+        <v>-0.7152706504405164</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.61231323870328</v>
+        <v>-2.452458918280407</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.599407565643466</v>
+        <v>1.695320157897189</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311944</v>
+        <v>3.784684521311947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.812296412378105</v>
+        <v>-9.606367298804015</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.7587797953730169</v>
+        <v>-0.6764081499433807</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.544327488842724</v>
+        <v>-2.38447316841985</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.639898700586339</v>
+        <v>1.735811292840063</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097239</v>
+        <v>3.800829354097242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.788342871402147</v>
+        <v>-9.582413757828057</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.7485298728371399</v>
+        <v>-0.6661582274075042</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.520373947866766</v>
+        <v>-2.360519627443893</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.654939331317407</v>
+        <v>1.750851923571131</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017767</v>
+        <v>3.789311112017771</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.52428293307935</v>
+        <v>-9.31835381950526</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6561662136697732</v>
+        <v>-0.5737945682401375</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.25631400954397</v>
+        <v>-2.096459689121097</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.800114978149332</v>
+        <v>1.896027570403056</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839721</v>
+        <v>3.833252747839724</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.817203309574513</v>
+        <v>-8.611274196000423</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3761213979281393</v>
+        <v>-0.2937497524985035</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.25631400954397</v>
+        <v>-2.096459689121097</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.797327944489031</v>
+        <v>1.893240536742755</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388725</v>
+        <v>3.839374447388728</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.777019011208322</v>
+        <v>-8.571089897634232</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3597040546938217</v>
+        <v>-0.277332409264186</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.216129711177779</v>
+        <v>-2.056275390754906</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.821782147396587</v>
+        <v>1.917694739650311</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.85616175162647</v>
+        <v>3.856161751626473</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.613619140268959</v>
+        <v>-8.407690026694869</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2949772850973194</v>
+        <v>-0.2126056396676836</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.052729840238417</v>
+        <v>-1.892875519815544</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.919188891180962</v>
+        <v>2.015101483434686</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291807</v>
+        <v>3.787330429291811</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.38013791803936</v>
+        <v>-8.17420880446527</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1936603673676274</v>
+        <v>-0.1112887219379912</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.819248618008818</v>
+        <v>-1.659394297585945</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.067202053356573</v>
+        <v>2.163114645610297</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785785</v>
+        <v>3.801637122785788</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.230471527031845</v>
+        <v>-8.024542413457755</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1366860212775807</v>
+        <v>-0.05431437584794496</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.726345126766282</v>
+        <v>-1.566490806343409</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.120051937789135</v>
+        <v>2.215964530042859</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390424</v>
+        <v>3.763182248390428</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.098196053400958</v>
+        <v>-7.892266939826869</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.08840834507819872</v>
+        <v>-0.006036699648563459</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.594069653135396</v>
+        <v>-1.434215332712522</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.194784708714694</v>
+        <v>2.290697300968418</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105949</v>
+        <v>3.784718794105952</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.942457720841216</v>
+        <v>-7.736528607267127</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.02329795136666535</v>
+        <v>0.05907369406297036</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.438331320575654</v>
+        <v>-1.278477000152781</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.291042768938176</v>
+        <v>2.3869553611919</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960983</v>
+        <v>3.753882571960987</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.693457922157635</v>
+        <v>-7.487528808583546</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.08920830933042589</v>
+        <v>0.1715799547600612</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.438331320575654</v>
+        <v>-1.278477000152781</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.303949110161835</v>
+        <v>2.399861702415559</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607642</v>
+        <v>3.692931855607646</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.79904791193074</v>
+        <v>-7.593118798356651</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.08100361617803475</v>
+        <v>0.001368029251600955</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.543921310348759</v>
+        <v>-1.384066989925885</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.112619186698754</v>
+        <v>2.208531778952477</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.7704225839879</v>
+        <v>3.770422583987903</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.817782814049337</v>
+        <v>-7.611853700475248</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.03995323514838711</v>
+        <v>0.0424184102812486</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.54951732000889</v>
+        <v>-1.389662999586017</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.157805922779761</v>
+        <v>2.253718515033485</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710808</v>
+        <v>3.760333686710812</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.669842772641737</v>
+        <v>-7.463913659067648</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.100656141273515</v>
+        <v>-0.01828449584387926</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.529196404100332</v>
+        <v>-1.369342083677459</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.050119549636728</v>
+        <v>2.146032141890452</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409202</v>
+        <v>3.723566229409205</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.616873250387749</v>
+        <v>-7.41094413681366</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.08818231862539783</v>
+        <v>-0.005810673195762117</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.476226881846344</v>
+        <v>-1.31637256142347</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.073187276735643</v>
+        <v>2.169099868989367</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098106</v>
+        <v>3.729969716098109</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.573324843617058</v>
+        <v>-7.367395730042969</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.07772356801221481</v>
+        <v>0.004648077417420904</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.476226881846344</v>
+        <v>-1.31637256142347</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.06622666464055</v>
+        <v>2.162139256894274</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493416</v>
+        <v>3.782922533493419</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.3311764501632</v>
+        <v>-7.125247336589111</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.03359814375047154</v>
+        <v>0.1159697891801073</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.476226881846344</v>
+        <v>-1.31637256142347</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.080689019021693</v>
+        <v>2.176601611275417</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722812</v>
+        <v>3.828551486722816</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.222917313040679</v>
+        <v>-7.016988199466589</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.07143391905867524</v>
+        <v>0.153805564488311</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.476226881846344</v>
+        <v>-1.31637256142347</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.075221139480888</v>
+        <v>2.171133731734612</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792042</v>
+        <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.099626178223548</v>
+        <v>-6.893697064649459</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1182484669961044</v>
+        <v>0.2006201124257401</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.352935747029213</v>
+        <v>-1.19308142660634</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.146693914381743</v>
+        <v>2.242606506635467</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919903</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.078476979320104</v>
+        <v>-6.872547865746015</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1344091247948072</v>
+        <v>0.2167807702244424</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.33178654812577</v>
+        <v>-1.171932227702897</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.167084411961135</v>
+        <v>2.262997004214859</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318089</v>
+        <v>3.748328408318093</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.83471153733666</v>
+        <v>-6.628782423762571</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2276960099352352</v>
+        <v>0.3100676553648709</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.33178654812577</v>
+        <v>-1.171932227702897</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.162865120308185</v>
+        <v>2.258777712561909</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057522</v>
+        <v>3.824311233057526</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.732948717059365</v>
+        <v>-6.527019603485276</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2705254519661695</v>
+        <v>0.3528970973958048</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.318567479733341</v>
+        <v>-1.158713159310468</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.172920875263658</v>
+        <v>2.268833467517382</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279182</v>
+        <v>3.826354974279186</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.483098323110291</v>
+        <v>-6.277169209536201</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3632076845295011</v>
+        <v>0.4455793299591368</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.318567479733341</v>
+        <v>-1.158713159310468</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.165662950247361</v>
+        <v>2.261575542501085</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011495</v>
+        <v>3.835957987011499</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.307206230642858</v>
+        <v>-6.101277117068769</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4371636450371228</v>
+        <v>0.5195352904667589</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.318567479733341</v>
+        <v>-1.158713159310468</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.169262073768009</v>
+        <v>2.265174666021733</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392983</v>
+        <v>3.780933911392987</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.135759767620395</v>
+        <v>-5.929830654046305</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5190697363006618</v>
+        <v>0.6014413817302979</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.147121016710878</v>
+        <v>-0.9872666962880047</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.285457457636041</v>
+        <v>2.381370049889765</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632777</v>
+        <v>3.773765222632781</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.061470201882056</v>
+        <v>-5.855541088307966</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5478060402122944</v>
+        <v>0.6301776856419306</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.072831450972539</v>
+        <v>-0.9129771305496654</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.329051674695342</v>
+        <v>2.424964266949065</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883069</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.997834459648121</v>
+        <v>-5.791905346074032</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5779551381601857</v>
+        <v>0.6603267835898219</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.009195708738604</v>
+        <v>-0.8493413883157309</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.37192792109002</v>
+        <v>2.467840513343743</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074778</v>
+        <v>3.798814771074782</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.886407700322201</v>
+        <v>-5.680478586748111</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6037201006743493</v>
+        <v>0.6860917461039855</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.009195708738604</v>
+        <v>-0.8493413883157309</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.353122179873815</v>
+        <v>2.449034772127539</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242289</v>
+        <v>3.797694884242292</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.645977203517341</v>
+        <v>-5.440048089943251</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7016353760211711</v>
+        <v>0.7840070214508068</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.7687652119337436</v>
+        <v>-0.6089108915108706</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.499123554581609</v>
+        <v>2.595036146835333</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82159350936768</v>
+        <v>3.821593509367682</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.573734635346146</v>
+        <v>-5.367805521772056</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7344617171244692</v>
+        <v>0.8168333625541049</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.7687652119337436</v>
+        <v>-0.6089108915108706</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.503052868416429</v>
+        <v>2.598965460670153</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879961</v>
+        <v>3.822326997879964</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.520736313064758</v>
+        <v>-5.314807199490668</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7563396299543643</v>
+        <v>0.838711275384</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.7134289529318047</v>
+        <v>-0.5535746325089318</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.536933207734932</v>
+        <v>2.632845799988656</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502334</v>
+        <v>3.848616626502337</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.411931427585031</v>
+        <v>-5.206002314010941</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7968596553662484</v>
+        <v>0.8792313007958845</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.7134289529318047</v>
+        <v>-0.5535746325089318</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.533931278954926</v>
+        <v>2.629843871208649</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675935</v>
+        <v>3.818668951675938</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.191910629548021</v>
+        <v>-4.985981515973931</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8864470115916667</v>
+        <v>0.9688186570213029</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.5722091078638245</v>
+        <v>-0.4123547874409516</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.620242223006328</v>
+        <v>2.716154815260052</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539946</v>
+        <v>3.843274527539949</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.059042940484743</v>
+        <v>-4.853113826910653</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.955488270018801</v>
+        <v>1.037859915448437</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.5722091078638245</v>
+        <v>-0.4123547874409516</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.636136405808151</v>
+        <v>2.732048998061875</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496257</v>
+        <v>3.84504738649626</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.938869857120245</v>
+        <v>-4.732940743546155</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.004703347804903</v>
+        <v>1.087074993234538</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.4520360244993256</v>
+        <v>-0.2921817040764526</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.709386100267153</v>
+        <v>2.805298692520876</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576994</v>
+        <v>3.791273551576996</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.794197712020507</v>
+        <v>-4.588268598446417</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.072660308406237</v>
+        <v>1.155031953835873</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.3073638793995881</v>
+        <v>-0.1475095589767152</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.806277489888435</v>
+        <v>2.902190082142158</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942099</v>
+        <v>3.735839222942101</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.854072539378199</v>
+        <v>-4.648143425804109</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.034747868864586</v>
+        <v>1.117119514294222</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.3672387067572803</v>
+        <v>-0.2073843863344073</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.756390084875245</v>
+        <v>2.852302677128969</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674511</v>
+        <v>3.762647477674513</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.767273041599191</v>
+        <v>-4.561343928025101</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.091868161298756</v>
+        <v>1.174239806728392</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.3672387067572803</v>
+        <v>-0.2073843863344073</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.778790578197811</v>
+        <v>2.874703170451535</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430691</v>
+        <v>3.729146398430693</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.769742748060997</v>
+        <v>-4.563813634486907</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.090952680087445</v>
+        <v>1.173324325517081</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.3697084132190864</v>
+        <v>-0.2098540927962135</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.77738115569414</v>
+        <v>2.873293747947864</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003598</v>
+        <v>3.7432201960036</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.838112934385007</v>
+        <v>-4.632183820810917</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.074611528032543</v>
+        <v>1.156983173462179</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.3604327141828715</v>
+        <v>-0.2005783937599985</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.793953497590571</v>
+        <v>2.889866089844295</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508365</v>
+        <v>3.714179139508367</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.851900987232054</v>
+        <v>-4.645971873657964</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.059533015525616</v>
+        <v>1.141904660955252</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.3604327141828715</v>
+        <v>-0.2005783937599985</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.784390206222462</v>
+        <v>2.880302798476186</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417699</v>
+        <v>3.710906731417701</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.882894146560759</v>
+        <v>-4.676965032986669</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8718453168345206</v>
+        <v>0.9542169622641565</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.3604327141828715</v>
+        <v>-0.2005783937599985</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.609099771262849</v>
+        <v>2.705012363516573</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205896</v>
+        <v>3.746042526205898</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.707419886768291</v>
+        <v>-4.501490773194201</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.946602252743296</v>
+        <v>1.028973898172932</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.3604327141828715</v>
+        <v>-0.2005783937599985</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.613667003254637</v>
+        <v>2.709579595508361</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225441</v>
+        <v>3.765024323225442</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.81835613940954</v>
+        <v>-4.61242702583545</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8779697804480033</v>
+        <v>0.9603414258776395</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.3604327141828715</v>
+        <v>-0.2005783937599985</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.589409032015844</v>
+        <v>2.685321624269568</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111291</v>
+        <v>3.773210297111293</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.784692593937257</v>
+        <v>-4.578763480363167</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8945665838568218</v>
+        <v>0.9769382292864579</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.3267691687105896</v>
+        <v>-0.1669148482877167</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.612738544519118</v>
+        <v>2.708651136772842</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264161</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.724839974733534</v>
+        <v>-4.518910861159444</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9286800179704435</v>
+        <v>1.011051663400079</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.3267691687105896</v>
+        <v>-0.1669148482877167</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.622910930951251</v>
+        <v>2.718823523204974</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742297</v>
+        <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.638596511707156</v>
+        <v>-4.432667398133066</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9581236737548549</v>
+        <v>1.040495319184491</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.3267691687105896</v>
+        <v>-0.1669148482877167</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.617857201525111</v>
+        <v>2.713769793778835</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.683903331106136</v>
+        <v>-4.477974217532046</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9317767214397885</v>
+        <v>1.014148366869424</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.3675793317198204</v>
+        <v>-0.2077250112969475</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.585146879164098</v>
+        <v>2.681059471417822</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803189</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.712936435808437</v>
+        <v>-4.507007322234347</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9207153525919696</v>
+        <v>1.003086998021606</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.3675793317198204</v>
+        <v>-0.2077250112969475</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.5856987521972</v>
+        <v>2.681611344450924</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809495</v>
+        <v>3.733390600809497</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.620125954357578</v>
+        <v>-4.414196840783488</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.887112237063679</v>
+        <v>0.9694838824933152</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.2747688502689611</v>
+        <v>-0.1149145298460881</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.570657732959081</v>
+        <v>2.666570325212805</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560423</v>
+        <v>3.748285816560425</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.664515423687005</v>
+        <v>-4.458586310112915</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.871229925256509</v>
+        <v>0.9536015706861449</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.3191583195983888</v>
+        <v>-0.1593039991755158</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.545897527286025</v>
+        <v>2.641810119539749</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472736</v>
+        <v>3.721077195472738</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.551844205450755</v>
+        <v>-4.345915091876665</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.911374121062732</v>
+        <v>0.9937457664923679</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.2064871013621385</v>
+        <v>-0.04663278093926559</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.608575966739498</v>
+        <v>2.704488558993222</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.439467204268082</v>
+        <v>-4.233538090693992</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9618162173664684</v>
+        <v>1.044187862796104</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.2064871013621385</v>
+        <v>-0.04663278093926559</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.614067262570166</v>
+        <v>2.70997985482389</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498863</v>
+        <v>3.689597840498865</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.467247602169435</v>
+        <v>-4.261318488595345</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9622012599744665</v>
+        <v>1.044572905404102</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.2342674992634916</v>
+        <v>-0.07441317884061865</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.608896225597893</v>
+        <v>2.704808817851617</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705323</v>
+        <v>3.643069621705325</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.550248883194714</v>
+        <v>-4.344319769620624</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7673564675650082</v>
+        <v>0.8497281129946441</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.2528383837906654</v>
+        <v>-0.09298406336779241</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.436109414882242</v>
+        <v>2.532022007135966</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729268</v>
+        <v>3.68271631072927</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.658862961638045</v>
+        <v>-4.452933848063955</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8440604969068812</v>
+        <v>0.9264321423365174</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.2528383837906654</v>
+        <v>-0.09298406336779241</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.556259075601448</v>
+        <v>2.652171667855171</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190765</v>
+        <v>3.733012441190768</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.623453923389902</v>
+        <v>-4.417524809815812</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8727371383084614</v>
+        <v>0.9551087837380974</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.2528383837906654</v>
+        <v>-0.09298406336779241</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.570772101703771</v>
+        <v>2.666684693957494</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913423</v>
+        <v>3.741174069913425</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.585070260831751</v>
+        <v>-4.379141147257661</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8855100446740907</v>
+        <v>0.9678816901037266</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.2144547212325142</v>
+        <v>-0.05460040080964124</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.59122174058103</v>
+        <v>2.687134332834754</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532482</v>
+        <v>3.751147197532485</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.407953930796585</v>
+        <v>-4.202024817222495</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9530856055334589</v>
+        <v>1.035457250963095</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.2144547212325142</v>
+        <v>-0.05460040080964124</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.587950769426332</v>
+        <v>2.683863361680056</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.7413284487939</v>
+        <v>3.741328448793902</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.45304617563013</v>
+        <v>-4.247117062056041</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9357320993619538</v>
+        <v>1.01810374479159</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.276350764401904</v>
+        <v>-0.116496443979031</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.551496535286611</v>
+        <v>2.647409127540335</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011233</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.273670754391363</v>
+        <v>-4.067741640817273</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.001269243163875</v>
+        <v>1.083640888593511</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.1195740062311853</v>
+        <v>0.04028031419168765</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.639349565495456</v>
+        <v>2.73526215774918</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982227</v>
+        <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.318684967911969</v>
+        <v>-4.112755854337879</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9640710130872225</v>
+        <v>1.046442658516859</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.1499229015457899</v>
+        <v>0.009931418877083042</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.601947683638284</v>
+        <v>2.697860275892007</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509535</v>
+        <v>3.737026608509537</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.585689478184404</v>
+        <v>-4.379760364610314</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8629607713171943</v>
+        <v>0.9453324167468304</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.3442859395887385</v>
+        <v>-0.1844316191658655</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.49102142315146</v>
+        <v>2.586934015405184</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760808</v>
+        <v>3.70230945476081</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.686887259621576</v>
+        <v>-4.480958146047486</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8216855806388268</v>
+        <v>0.9040572260684627</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.4126947531340577</v>
+        <v>-0.2528404327111847</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.44918005692077</v>
+        <v>2.545092649174494</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815453</v>
+        <v>3.705571661815455</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.654411673450804</v>
+        <v>-4.448482559876714</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8322757766614524</v>
+        <v>0.9146474220910883</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.4126947531340577</v>
+        <v>-0.2528404327111847</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.446780018475087</v>
+        <v>2.542692610728811</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378098</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.635373545743507</v>
+        <v>-4.429444432169417</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8364157469526161</v>
+        <v>0.918787392382252</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.4708783644652522</v>
+        <v>-0.3110240440423793</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.408394570884615</v>
+        <v>2.504307163138339</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131248</v>
+        <v>3.73106447313125</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.666500176894125</v>
+        <v>-4.460571063320035</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.001546963431049</v>
+        <v>1.083918608860685</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.4708783644652522</v>
+        <v>-0.3110240440423793</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.585976439823296</v>
+        <v>2.681889032077019</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067865</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.680366938228043</v>
+        <v>-4.474437824653953</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9968335878836156</v>
+        <v>1.079205233313252</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.5087362811990752</v>
+        <v>-0.3488819607762022</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.564095018769136</v>
+        <v>2.660007611022859</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789119</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.635562766688113</v>
+        <v>-4.429633653114023</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.020763786896514</v>
+        <v>1.10313543232615</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.5087362811990752</v>
+        <v>-0.3488819607762022</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.570103549166062</v>
+        <v>2.666016141419785</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519905</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.954497965677528</v>
+        <v>2.909559048546589</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.487819796453111</v>
+        <v>-4.281890682879021</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.159013622782537</v>
+        <v>1.196446351081233</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.3409289239641921</v>
+        <v>-0.181074603541319</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.749940611299013</v>
+        <v>2.800914286421798</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181167</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.957291587209009</v>
+        <v>2.91235267007807</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.589834478984332</v>
+        <v>-4.383905365410242</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.121001371301529</v>
+        <v>1.158434099600226</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.3409289239641921</v>
+        <v>-0.181074603541319</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.752734232830494</v>
+        <v>2.803707907953279</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394726</v>
+        <v>3.805608985394728</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.957953935600667</v>
+        <v>2.913015018469728</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.583681772931548</v>
+        <v>-4.377752659357458</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.124124802114301</v>
+        <v>1.161557530412998</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.3347762179114078</v>
+        <v>-0.1749218974885348</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.757088204853823</v>
+        <v>2.808061879976607</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890607</v>
+        <v>3.798239794890609</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.957034412340778</v>
+        <v>2.912095495209838</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.600491071082049</v>
+        <v>-4.39456195750796</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.116481559594211</v>
+        <v>1.153914287892907</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.3515855160619094</v>
+        <v>-0.1917311956390364</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.746083102703632</v>
+        <v>2.797056777826417</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798423</v>
+        <v>3.867362636798425</v>
       </c>
       <c r="C1970" t="n">
-        <v>3.023369966137599</v>
+        <v>2.978431049006659</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.538193072305927</v>
+        <v>-4.332263958731837</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.20773631290148</v>
+        <v>1.245169041200177</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.3515855160619094</v>
+        <v>-0.1917311956390364</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.812418656500453</v>
+        <v>2.863392331623237</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992187</v>
+        <v>3.848729139992189</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.731950838526997</v>
+        <v>2.687011921396057</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.336402874640769</v>
+        <v>-4.130473761066679</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9970332643569417</v>
+        <v>1.034465992655638</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.153567323892755</v>
+        <v>0.006286996530117994</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.639810444191344</v>
+        <v>2.690784119314128</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.84144481785242</v>
+        <v>3.841444817852421</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.802241070849172</v>
+        <v>2.757302153718233</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.276512192998176</v>
+        <v>-4.070583079424086</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.091279769336154</v>
+        <v>1.128712497634851</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.09367664225016153</v>
+        <v>0.06617767817271147</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.746035085499075</v>
+        <v>2.79700876062186</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319542</v>
+        <v>3.819063300319544</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.816868806965215</v>
+        <v>2.771929889834276</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.37425273762315</v>
+        <v>-4.16832362404906</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.066811287602208</v>
+        <v>1.104244015900905</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.1095659203831417</v>
+        <v>0.05028840003973128</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.751129254735331</v>
+        <v>2.802102929858115</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489381</v>
+        <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.815404787789887</v>
+        <v>2.770465870658948</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.55059049774608</v>
+        <v>-4.34466138417199</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9948121643777079</v>
+        <v>1.032244892676405</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.2859036805060711</v>
+        <v>-0.1260493600831981</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.643862579486245</v>
+        <v>2.694836254609029</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397791</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.813896405829816</v>
+        <v>2.768957488698876</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.474168451314153</v>
+        <v>-4.268239337740063</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.023872600990407</v>
+        <v>1.061305329289104</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.2859036805060711</v>
+        <v>-0.1260493600831981</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.642354197526173</v>
+        <v>2.693327872648958</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024959</v>
+        <v>3.836023391024961</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.813759273265252</v>
+        <v>2.768820356134313</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.429795319675584</v>
+        <v>-4.223866206101494</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.041484721081271</v>
+        <v>1.078917449379968</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.2415305488675025</v>
+        <v>-0.08167622844462952</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.668840943944751</v>
+        <v>2.719814619067535</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.82159115086322</v>
+        <v>3.821591150863222</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.813759273265252</v>
+        <v>2.768820356134313</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.421841349380812</v>
+        <v>-4.215912235806722</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.04466630919918</v>
+        <v>1.082099037497877</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.2415305488675025</v>
+        <v>-0.08167622844462952</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.668840943944751</v>
+        <v>2.719814619067535</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947579</v>
+        <v>3.833040181947581</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.820141030293057</v>
+        <v>2.775202113162117</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.374185618819756</v>
+        <v>-4.168256505245666</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.070110358451407</v>
+        <v>1.107543086750103</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.1938748183064469</v>
+        <v>-0.03402049788357386</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.703816139309189</v>
+        <v>2.754789814431973</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326871</v>
+        <v>3.822707244326873</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.825033403667781</v>
+        <v>2.780094486536842</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.24650130902546</v>
+        <v>-4.04057219545137</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.12607645574385</v>
+        <v>1.163509184042547</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.06619050851215041</v>
+        <v>0.09366381191072259</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.785319098560491</v>
+        <v>2.836292773683276</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314547</v>
+        <v>3.828837911314548</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.811788076143654</v>
+        <v>2.766849159012714</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.307167899427849</v>
+        <v>-4.101238785853759</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.088564492058766</v>
+        <v>1.125997220357463</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.1478888252306841</v>
+        <v>0.01196549519218892</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.723054781005243</v>
+        <v>2.774028456128028</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690022</v>
+        <v>3.816866067690023</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.815885778754282</v>
+        <v>2.770946861623343</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.262329497819451</v>
+        <v>-4.056400384245361</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.110597555312755</v>
+        <v>1.148030283611451</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.1433453922858146</v>
+        <v>0.0165089281370584</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.729878543382794</v>
+        <v>2.780852218505578</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674306</v>
+        <v>3.817961388674307</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.82004671838536</v>
+        <v>2.775107801254421</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.363088133576449</v>
+        <v>-4.157159020002359</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.074455040641033</v>
+        <v>1.11188776893973</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.23217096101282</v>
+        <v>-0.07231664058994702</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.680744141777669</v>
+        <v>2.731717816900453</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826713779163216</v>
+        <v>3.826713779163217</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.825926320913197</v>
+        <v>2.780987403782258</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.318885296490548</v>
+        <v>-4.112956182916458</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.098015778003231</v>
+        <v>1.135448506301927</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.1879681239269196</v>
+        <v>-0.02811380350404658</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.713145446557046</v>
+        <v>2.76411912167983</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.8382286630229</v>
+        <v>3.838228663022901</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.824336321382445</v>
+        <v>2.779397404251505</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.355864324153991</v>
+        <v>-4.149935210579901</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.081634167407101</v>
+        <v>1.119066895705798</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.1509942221355891</v>
+        <v>0.008860098287283957</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.733739788101092</v>
+        <v>2.784713463223876</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042133</v>
+        <v>3.863924114042136</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.875584086565484</v>
+        <v>2.830645169434545</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.375922403018832</v>
+        <v>-4.169993289444742</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.124858701044205</v>
+        <v>1.162291429342901</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.1509942221355891</v>
+        <v>0.008860098287283957</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.784987553284132</v>
+        <v>2.835961228406916</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865367715078275</v>
+        <v>3.865367715078277</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.874024791159738</v>
+        <v>2.829085874028798</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.335991729840941</v>
+        <v>-4.130062616266851</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.139271674909614</v>
+        <v>1.17670440320831</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.1110635489576987</v>
+        <v>0.0487907714651743</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.807386661785118</v>
+        <v>2.858360336907903</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232392</v>
+        <v>3.864518876232394</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.868973019398008</v>
+        <v>2.824034102267068</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.284959637118414</v>
+        <v>-4.079030523544324</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.154632740236895</v>
+        <v>1.192065468535592</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.06003145623517075</v>
+        <v>0.09982286418770225</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.832954145656906</v>
+        <v>2.88392782077969</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842576394162107</v>
+        <v>3.842576394162108</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.886160423490713</v>
+        <v>2.841221506359773</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.219735455991208</v>
+        <v>-4.013806342417118</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.197909816780482</v>
+        <v>1.235342545079179</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.005192724892034872</v>
+        <v>0.1650470453149079</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.889276058425934</v>
+        <v>2.940249733548718</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840090220639811</v>
+        <v>3.840090220639813</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.882121395789993</v>
+        <v>2.837182478659054</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.182308435920074</v>
+        <v>-3.976379322345985</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.208841597108216</v>
+        <v>1.246274325406912</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.01044426292121653</v>
+        <v>0.1702985833440895</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.888387953542723</v>
+        <v>2.939361628665508</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845198842749916</v>
+        <v>3.845198842749918</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.883378188121233</v>
+        <v>2.838439270990294</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.202420091954782</v>
+        <v>-3.996490978380693</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.202053727025573</v>
+        <v>1.239486455324269</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.02147160791863573</v>
+        <v>0.1813259283415087</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.896261152872415</v>
+        <v>2.947234827995199</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828690479393541</v>
+        <v>3.828690479393543</v>
       </c>
       <c r="C1991" t="n">
-        <v>3.043935959142444</v>
+        <v>2.998997042011505</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.148675277527578</v>
+        <v>-3.942746163953488</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.384109423817666</v>
+        <v>1.421542152116362</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.03153491735909769</v>
+        <v>0.1913892377819707</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.062856909557903</v>
+        <v>3.113830584680688</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813251854714879</v>
+        <v>3.813251854714881</v>
       </c>
       <c r="C1992" t="n">
-        <v>3.164048868360261</v>
+        <v>3.119109951229322</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.124883708921436</v>
+        <v>-3.918954595347346</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.51373896047794</v>
+        <v>1.551171688776636</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.05532648596523998</v>
+        <v>0.215180806388113</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.197244759939406</v>
+        <v>3.24821843506219</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814259761756007</v>
+        <v>3.814259761756009</v>
       </c>
       <c r="C1993" t="n">
-        <v>3.15575684437412</v>
+        <v>3.110817927243181</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.098799624657627</v>
+        <v>-3.892870511083538</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.515880570197322</v>
+        <v>1.553313298496018</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.05532648596523998</v>
+        <v>0.215180806388113</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.188952735953265</v>
+        <v>3.239926411076049</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803426852654182</v>
+        <v>3.803426852654184</v>
       </c>
       <c r="C1994" t="n">
-        <v>3.1539500399579</v>
+        <v>3.10901112282696</v>
       </c>
       <c r="D1994" t="n">
-        <v>-4.09446532160058</v>
+        <v>-3.88853620802649</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.515807487003921</v>
+        <v>1.553240215302617</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.2069765892844439</v>
+        <v>0.3668309097073169</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.278135993528566</v>
+        <v>3.329109668651351</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796293177717112</v>
+        <v>3.796293177717114</v>
       </c>
       <c r="C1995" t="n">
-        <v>3.171504445684691</v>
+        <v>3.126565528553752</v>
       </c>
       <c r="D1995" t="n">
-        <v>-4.085572860207296</v>
+        <v>-3.879643746633207</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.536918877288025</v>
+        <v>1.574351605586722</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.2069765892844439</v>
+        <v>0.3668309097073169</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.295690399255358</v>
+        <v>3.346664074378142</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794453975702622</v>
+        <v>3.794453975702623</v>
       </c>
       <c r="C1996" t="n">
-        <v>3.163359493089275</v>
+        <v>3.118420575958336</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.254048977177174</v>
+        <v>-4.048119863603084</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.461383477904658</v>
+        <v>1.498816206203355</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.1790287535678631</v>
+        <v>0.3388830739907361</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.270776745229993</v>
+        <v>3.321750420352778</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795603100539963</v>
+        <v>3.795603100539965</v>
       </c>
       <c r="C1997" t="n">
-        <v>3.144629190277137</v>
+        <v>3.099690273146197</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.556249448315591</v>
+        <v>-3.350320334741501</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.721772986637153</v>
+        <v>1.75920571493585</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.1086806941974524</v>
+        <v>0.2685350146203254</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.209837606795609</v>
+        <v>3.260811281918393</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784700379389891</v>
+        <v>3.784700379389893</v>
       </c>
       <c r="C1998" t="n">
-        <v>3.135293212774041</v>
+        <v>3.090354295643102</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.533528344632438</v>
+        <v>-3.327599231058348</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.721525450607319</v>
+        <v>1.758958178906016</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.1086806941974524</v>
+        <v>0.2685350146203254</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.200501629292513</v>
+        <v>3.251475304415298</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.78323473053493</v>
+        <v>3.783234730534931</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.29419933862521</v>
+        <v>3.249260421494271</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.673820944169631</v>
+        <v>-3.467891830595541</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.824314536643611</v>
+        <v>1.861747264942307</v>
       </c>
       <c r="F1999" t="n">
-        <v>-0.03161190533974023</v>
+        <v>0.1282424150831328</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.275232195421367</v>
+        <v>3.326205870544151</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779962759401668</v>
+        <v>3.77996275940167</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.331277161118857</v>
+        <v>3.286338243987918</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.828601950947886</v>
+        <v>-3.622672837373796</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.799479956425955</v>
+        <v>1.836912684724652</v>
       </c>
       <c r="F2000" t="n">
-        <v>-0.06497957939421634</v>
+        <v>0.09487474102865667</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.292289413482327</v>
+        <v>3.343263088605112</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769472653557218</v>
+        <v>3.76947265355722</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.327952517108402</v>
+        <v>3.283013599977463</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.895862394969803</v>
+        <v>-3.689933281395713</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.769251134806734</v>
+        <v>1.80668386310543</v>
       </c>
       <c r="F2001" t="n">
-        <v>-0.1322400234161334</v>
+        <v>0.02761429700673956</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.248608503058722</v>
+        <v>3.299582178181507</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766702530088374</v>
+        <v>3.766702530088375</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.337958670753144</v>
+        <v>3.293019753622204</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.873390860930971</v>
+        <v>-3.667461747356881</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.788245902067008</v>
+        <v>1.825678630365705</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.003465461399837777</v>
+        <v>0.1633197818227108</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.340037947593046</v>
+        <v>3.391011622715831</v>
       </c>
     </row>
     <row r="2003">
@@ -47617,19 +47617,19 @@
         <v>3.76808110154137</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.522061802898103</v>
+        <v>3.477122885767164</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.874335788345376</v>
+        <v>-3.803414755413197</v>
       </c>
       <c r="E2003" t="n">
-        <v>1.971971063246206</v>
+        <v>1.955400559288138</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.003465461399837777</v>
+        <v>0.1633197818227108</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.524141079738006</v>
+        <v>3.575114754860791</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.747866136782537</v>
+        <v>3.827531574668135</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.619143054518755</v>
+        <v>3.628519621976041</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.874335788345376</v>
+        <v>-3.803414755413197</v>
       </c>
       <c r="E2004" t="n">
-        <v>1.971971063246206</v>
+        <v>1.955400559288138</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.003465461399837777</v>
+        <v>0.1633197818227108</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.612206851505123</v>
+        <v>3.621583418962409</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240623.xlsx
+++ b/tame_output/ON/bt/strategyON_20240623.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,12 +610,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>47.7%</t>
         </is>
       </c>
     </row>
@@ -758,12 +758,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>79.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>37.7%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>63.9%</t>
+          <t>64.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.3%</t>
+          <t>-6.9%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>51.2%</t>
+          <t>48.8%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-73.7%</t>
+          <t>-74.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.0%</t>
+          <t>109.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>121.8%</t>
+          <t>124.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>93.8%</t>
+          <t>93.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-671.4%</t>
+          <t>-692.0%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.1%</t>
+          <t>-51.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-69.1%</t>
+          <t>-70.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.6%</t>
+          <t>90.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>461.0%</t>
+          <t>458.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-12.2%</t>
+          <t>-13.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-541.9%</t>
+          <t>-551.8%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>64.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>49.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.4%</t>
+          <t>99.5%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-269.0%</t>
+          <t>-277.2%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-39.8%</t>
+          <t>-40.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-31.8%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>120.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-180.7%</t>
+          <t>-180.1%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-20.5%</t>
+          <t>-23.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-284.5%</t>
+          <t>-300.5%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-32.2%</t>
+          <t>-33.2%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-13.5%</t>
+          <t>-16.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>-3.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-227.7%</t>
+          <t>-171.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-207.7%</t>
+          <t>-223.6%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>95.8%</t>
+          <t>96.2%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-171.1%</t>
+          <t>-180.7%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-27.7%</t>
+          <t>-28.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>58.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>-17.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-83.9%</t>
+          <t>-86.3%</t>
         </is>
       </c>
     </row>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178241</v>
+        <v>3.315884374178242</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,22 +44302,22 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207809</v>
+        <v>3.30531679820781</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.863803359533784</v>
+        <v>-5.069732473107872</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.178193765903523</v>
+        <v>1.095822120473888</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.6118274807080977</v>
+        <v>-0.7716818011309712</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.756975045605925</v>
+        <v>2.661062453352201</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.098497353666336</v>
+        <v>-5.304426467240424</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.072600943252593</v>
+        <v>0.9902292978229577</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.6054912134788425</v>
+        <v>-0.765345533901716</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.749061580945569</v>
+        <v>2.653148988691845</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.434160000896789</v>
+        <v>-5.640089114470877</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.9369164760163771</v>
+        <v>0.8545448305867418</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.6734221989677474</v>
+        <v>-0.8332765193906209</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.706883581308191</v>
+        <v>2.610970989054468</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309421</v>
+        <v>3.311086391309422</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.797786245797102</v>
+        <v>-6.00371535937119</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7979535382904932</v>
+        <v>0.7155818928608579</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.7716438358348732</v>
+        <v>-0.9314981562577467</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.654438159422158</v>
+        <v>2.558525567168433</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.162913628435849</v>
+        <v>-6.368842742009937</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.6511571002408258</v>
+        <v>0.5687854548111906</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.067954620133886</v>
+        <v>-1.227808940556759</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.475906203848582</v>
+        <v>2.379993611594857</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330519</v>
+        <v>3.30081581833052</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.571502405616528</v>
+        <v>-6.777431519190616</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4864831333833131</v>
+        <v>0.4041114879536778</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.476543397314564</v>
+        <v>-1.636397717737438</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.229514481554934</v>
+        <v>2.133601889301209</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191734</v>
+        <v>3.302618194191735</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.84807850593236</v>
+        <v>-7.054007619506448</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.371038125728441</v>
+        <v>0.2886664802988057</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.476543397314564</v>
+        <v>-1.636397717737438</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.224699914026394</v>
+        <v>2.12878732177267</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108635</v>
+        <v>3.305023265108636</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.264470380219358</v>
+        <v>-7.470399493793446</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.2024754266225193</v>
+        <v>0.120103781192884</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.476543397314564</v>
+        <v>-1.636397717737438</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.222693964635272</v>
+        <v>2.126781372381547</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097817</v>
+        <v>3.341378723097818</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.508741780946427</v>
+        <v>-7.714670894520515</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.1150255570003704</v>
+        <v>0.03265391157073516</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.476543397314564</v>
+        <v>-1.636397717737438</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.232952655303951</v>
+        <v>2.137040063050226</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094113</v>
+        <v>3.374439043094114</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.713992800183187</v>
+        <v>-7.919921913757276</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.02902471445136134</v>
+        <v>-0.05334693097827392</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.476543397314564</v>
+        <v>-1.636397717737438</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.229052220449645</v>
+        <v>2.133139628195922</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199282</v>
+        <v>3.405960511199283</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.877572678367571</v>
+        <v>-8.083501791941659</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.03800231676739108</v>
+        <v>-0.1203739621970263</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.476543397314564</v>
+        <v>-1.636397717737438</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.227457140504646</v>
+        <v>2.131544548250923</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.42463335496959</v>
+        <v>3.424633354969591</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.174234020177769</v>
+        <v>-8.380163133751857</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.1528878775622622</v>
+        <v>-0.2352595229918975</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.545286533048443</v>
+        <v>-1.705140853471316</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.189990234993528</v>
+        <v>2.094077642739804</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923083</v>
+        <v>3.419979433923084</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.360953728487072</v>
+        <v>-8.56688284206116</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.2316020654203861</v>
+        <v>-0.3139737108500213</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.545286533048443</v>
+        <v>-1.705140853471316</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.185963930459125</v>
+        <v>2.0900513382054</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297745</v>
+        <v>3.458100091297747</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.743955117229703</v>
+        <v>-8.949884230803791</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.3849047222390229</v>
+        <v>-0.4672763676686582</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.545286533048443</v>
+        <v>-1.705140853471316</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.18586182913754</v>
+        <v>2.089949236883816</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317613</v>
+        <v>3.447750501317615</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-8.925824908214738</v>
+        <v>-9.131754021788826</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.4550811226616065</v>
+        <v>-0.5374527680912418</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.727156324033478</v>
+        <v>-1.887010644456351</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.07931147051795</v>
+        <v>1.983398878264226</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737167</v>
+        <v>3.503515506737169</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.285355230718739</v>
+        <v>-9.491284344292827</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.5935429483651569</v>
+        <v>-0.6759145937947921</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.727156324033478</v>
+        <v>-1.887010644456351</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.084661773816</v>
+        <v>1.988749181562276</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.50317028234131</v>
+        <v>3.503170282341312</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.335704294172961</v>
+        <v>-9.541633407747049</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.6057665537896684</v>
+        <v>-0.6881381992193036</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.7775053874877</v>
+        <v>-1.937359707910573</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.062368355700644</v>
+        <v>1.96645576344692</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539461</v>
+        <v>3.501052558539462</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.433323571594357</v>
+        <v>-9.639252685168445</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.6417725141364579</v>
+        <v>-0.7241441595660931</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.875124664909096</v>
+        <v>-2.03497898533197</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.006838539869575</v>
+        <v>1.91092594761585</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.5808496596</v>
+        <v>-9.786778773174088</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.6978893930171428</v>
+        <v>-0.7802610384467781</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.02265075291474</v>
+        <v>-2.182505073337614</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.921216443387761</v>
+        <v>1.825303851134037</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.785107834929864</v>
+        <v>-9.991036948503952</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.7740794660304458</v>
+        <v>-0.856451111460081</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.150289697528729</v>
+        <v>-2.310144017951603</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.85014627373801</v>
+        <v>1.754233681484286</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.859440811190028</v>
+        <v>-10.06536992476412</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.7993301020500758</v>
+        <v>-0.8817017474797111</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.294989221463402</v>
+        <v>-2.454843541886275</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.767809113861642</v>
+        <v>1.671896521607918</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.785970979522579</v>
+        <v>-9.991900093096667</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.7545704678896747</v>
+        <v>-0.83694211331931</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.221519389795953</v>
+        <v>-2.381373710218827</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.827262714355533</v>
+        <v>1.731350122101808</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-9.961095396909123</v>
+        <v>-10.16702451048321</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.8100650140967756</v>
+        <v>-0.8924366595264104</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.396643807182497</v>
+        <v>-2.556498127605371</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.736743284671123</v>
+        <v>1.640830692417399</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.19554749092361</v>
+        <v>-10.4014766044977</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.9110650166041672</v>
+        <v>-0.9934366620338024</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.396643807182497</v>
+        <v>-2.556498127605371</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.729524119769527</v>
+        <v>1.633611527515803</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.29992222195006</v>
+        <v>-10.50585133552415</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.9594870997887219</v>
+        <v>-1.041858745218357</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.501018538208943</v>
+        <v>-2.660872858631816</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.660227090379683</v>
+        <v>1.564314498125959</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.35270837755039</v>
+        <v>-10.55863749112447</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.9794857721902961</v>
+        <v>-1.061857417619931</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.59669402479134</v>
+        <v>-2.756548345214213</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.603937588268801</v>
+        <v>1.508024996015078</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.47874517091867</v>
+        <v>-10.68467428449276</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.027206760908497</v>
+        <v>-1.109578406338132</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.571442401981598</v>
+        <v>-2.731296722404471</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.621782290583762</v>
+        <v>1.525869698330037</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.42672965694986</v>
+        <v>-10.63265877052395</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.002410219634571</v>
+        <v>-1.084781865064206</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.571442401981598</v>
+        <v>-2.731296722404471</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.625772626270162</v>
+        <v>1.529860034016438</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.56840149867398</v>
+        <v>-10.77433061224807</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.060554183222961</v>
+        <v>-1.142925828652596</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.571442401981598</v>
+        <v>-2.731296722404471</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.624297399371421</v>
+        <v>1.528384807117697</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.51881065424915</v>
+        <v>-10.72473976782324</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.025664435288155</v>
+        <v>-1.10803608071779</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.521851557556764</v>
+        <v>-2.681705877979637</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.669105316191193</v>
+        <v>1.573192723937469</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.50600326124437</v>
+        <v>-10.71193237481846</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.033592611732928</v>
+        <v>-1.115964257162564</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.570707332565665</v>
+        <v>-2.730561652988538</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.626740717539169</v>
+        <v>1.530828125285446</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.28015810852496</v>
+        <v>-10.48608722209905</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.9336754776089555</v>
+        <v>-1.016047123038591</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.528780656978501</v>
+        <v>-2.688634977401374</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.661475795927676</v>
+        <v>1.565563203673952</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.15557945218737</v>
+        <v>-10.36150856576146</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.8827048705178595</v>
+        <v>-0.9650765159474957</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.528780656978501</v>
+        <v>-2.688634977401374</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.662614940483735</v>
+        <v>1.566702348230011</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.20847474023166</v>
+        <v>-10.41440385380575</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.9012292115734661</v>
+        <v>-0.9836008570031023</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.523825310890055</v>
+        <v>-2.683679631312928</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.668221922298911</v>
+        <v>1.572309330045187</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611566</v>
+        <v>3.768951674611567</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.13634156494378</v>
+        <v>-10.34227067851787</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.8666422372196774</v>
+        <v>-0.9490138826493135</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.523825310890055</v>
+        <v>-2.683679631312928</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.673955626537547</v>
+        <v>1.578043034283823</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.06497517233413</v>
+        <v>-10.27090428590822</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.847832942569684</v>
+        <v>-0.9302045879993202</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.452458918280407</v>
+        <v>-2.61231323870328</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.707038199709471</v>
+        <v>1.611125607455747</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.971516138348903</v>
+        <v>-10.17744525192299</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.8203328102885017</v>
+        <v>-0.9027044557181374</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.452458918280407</v>
+        <v>-2.61231323870328</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.697154718396563</v>
+        <v>1.601242126142839</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.704274337480506</v>
+        <v>-9.910203451054596</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7152706504405164</v>
+        <v>-0.7976422958701521</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.452458918280407</v>
+        <v>-2.61231323870328</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.695320157897189</v>
+        <v>1.599407565643466</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311947</v>
+        <v>3.784684521311948</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.606367298804015</v>
+        <v>-9.812296412378105</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.6764081499433807</v>
+        <v>-0.7587797953730169</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.38447316841985</v>
+        <v>-2.544327488842724</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.735811292840063</v>
+        <v>1.639898700586339</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097242</v>
+        <v>3.800829354097243</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.582413757828057</v>
+        <v>-9.788342871402147</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.6661582274075042</v>
+        <v>-0.7485298728371399</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.360519627443893</v>
+        <v>-2.520373947866766</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.750851923571131</v>
+        <v>1.654939331317407</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017771</v>
+        <v>3.789311112017772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.31835381950526</v>
+        <v>-9.52428293307935</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.5737945682401375</v>
+        <v>-0.6561662136697732</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.096459689121097</v>
+        <v>-2.25631400954397</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.896027570403056</v>
+        <v>1.800114978149332</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839724</v>
+        <v>3.833252747839725</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.611274196000423</v>
+        <v>-8.817203309574513</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.2937497524985035</v>
+        <v>-0.3761213979281393</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.096459689121097</v>
+        <v>-2.25631400954397</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.893240536742755</v>
+        <v>1.797327944489031</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388728</v>
+        <v>3.83937444738873</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.571089897634232</v>
+        <v>-8.777019011208322</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.277332409264186</v>
+        <v>-0.3597040546938217</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.056275390754906</v>
+        <v>-2.216129711177779</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.917694739650311</v>
+        <v>1.821782147396587</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626473</v>
+        <v>3.856161751626476</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.407690026694869</v>
+        <v>-8.613619140268959</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2126056396676836</v>
+        <v>-0.2949772850973194</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.892875519815544</v>
+        <v>-2.052729840238417</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.015101483434686</v>
+        <v>1.919188891180962</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291811</v>
+        <v>3.787330429291812</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.17420880446527</v>
+        <v>-8.38013791803936</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1112887219379912</v>
+        <v>-0.1936603673676274</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.659394297585945</v>
+        <v>-1.819248618008818</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.163114645610297</v>
+        <v>2.067202053356573</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.024542413457755</v>
+        <v>-8.230471527031845</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.05431437584794496</v>
+        <v>-0.1366860212775807</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.566490806343409</v>
+        <v>-1.726345126766282</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.215964530042859</v>
+        <v>2.120051937789135</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.892266939826869</v>
+        <v>-8.098196053400958</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.006036699648563459</v>
+        <v>-0.08840834507819872</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.434215332712522</v>
+        <v>-1.594069653135396</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.290697300968418</v>
+        <v>2.194784708714694</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.736528607267127</v>
+        <v>-7.942457720841216</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.05907369406297036</v>
+        <v>-0.02329795136666535</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.278477000152781</v>
+        <v>-1.438331320575654</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.3869553611919</v>
+        <v>2.291042768938176</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.487528808583546</v>
+        <v>-7.693457922157635</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1715799547600612</v>
+        <v>0.08920830933042589</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.278477000152781</v>
+        <v>-1.438331320575654</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.399861702415559</v>
+        <v>2.303949110161835</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.593118798356651</v>
+        <v>-7.79904791193074</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.001368029251600955</v>
+        <v>-0.08100361617803475</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.384066989925885</v>
+        <v>-1.543921310348759</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.208531778952477</v>
+        <v>2.112619186698754</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.611853700475248</v>
+        <v>-7.817782814049337</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.0424184102812486</v>
+        <v>-0.03995323514838711</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.389662999586017</v>
+        <v>-1.54951732000889</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.253718515033485</v>
+        <v>2.157805922779761</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.463913659067648</v>
+        <v>-7.669842772641737</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.01828449584387926</v>
+        <v>-0.100656141273515</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.369342083677459</v>
+        <v>-1.529196404100332</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.146032141890452</v>
+        <v>2.050119549636728</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.41094413681366</v>
+        <v>-7.616873250387749</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.005810673195762117</v>
+        <v>-0.08818231862539783</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.31637256142347</v>
+        <v>-1.476226881846344</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.169099868989367</v>
+        <v>2.073187276735643</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.367395730042969</v>
+        <v>-7.573324843617058</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.004648077417420904</v>
+        <v>-0.07772356801221481</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.31637256142347</v>
+        <v>-1.476226881846344</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.162139256894274</v>
+        <v>2.06622666464055</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.125247336589111</v>
+        <v>-7.3311764501632</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.1159697891801073</v>
+        <v>0.03359814375047154</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.31637256142347</v>
+        <v>-1.476226881846344</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.176601611275417</v>
+        <v>2.080689019021693</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.016988199466589</v>
+        <v>-7.222917313040679</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.153805564488311</v>
+        <v>0.07143391905867524</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.31637256142347</v>
+        <v>-1.476226881846344</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.171133731734612</v>
+        <v>2.075221139480888</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.893697064649459</v>
+        <v>-7.099626178223548</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.2006201124257401</v>
+        <v>0.1182484669961044</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.19308142660634</v>
+        <v>-1.352935747029213</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.242606506635467</v>
+        <v>2.146693914381743</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.872547865746015</v>
+        <v>-7.078476979320104</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.2167807702244424</v>
+        <v>0.1344091247948072</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.171932227702897</v>
+        <v>-1.33178654812577</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.262997004214859</v>
+        <v>2.167084411961135</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.628782423762571</v>
+        <v>-6.83471153733666</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.3100676553648709</v>
+        <v>0.2276960099352352</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.171932227702897</v>
+        <v>-1.33178654812577</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.258777712561909</v>
+        <v>2.162865120308185</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.527019603485276</v>
+        <v>-6.732948717059365</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3528970973958048</v>
+        <v>0.2705254519661695</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.158713159310468</v>
+        <v>-1.318567479733341</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.268833467517382</v>
+        <v>2.172920875263658</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.277169209536201</v>
+        <v>-6.483098323110291</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4455793299591368</v>
+        <v>0.3632076845295011</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.158713159310468</v>
+        <v>-1.318567479733341</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.261575542501085</v>
+        <v>2.165662950247361</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.101277117068769</v>
+        <v>-6.307206230642858</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5195352904667589</v>
+        <v>0.4371636450371228</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.158713159310468</v>
+        <v>-1.318567479733341</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.265174666021733</v>
+        <v>2.169262073768009</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.929830654046305</v>
+        <v>-6.135759767620395</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.6014413817302979</v>
+        <v>0.5190697363006618</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.9872666962880047</v>
+        <v>-1.147121016710878</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.381370049889765</v>
+        <v>2.285457457636041</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632781</v>
+        <v>3.773765222632782</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.855541088307966</v>
+        <v>-6.061470201882056</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6301776856419306</v>
+        <v>0.5478060402122944</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.9129771305496654</v>
+        <v>-1.072831450972539</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.424964266949065</v>
+        <v>2.329051674695342</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.791905346074032</v>
+        <v>-5.997834459648121</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6603267835898219</v>
+        <v>0.5779551381601857</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.8493413883157309</v>
+        <v>-1.009195708738604</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.467840513343743</v>
+        <v>2.37192792109002</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074782</v>
+        <v>3.798814771074783</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.680478586748111</v>
+        <v>-5.886407700322201</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6860917461039855</v>
+        <v>0.6037201006743493</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.8493413883157309</v>
+        <v>-1.009195708738604</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.449034772127539</v>
+        <v>2.353122179873815</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242292</v>
+        <v>3.797694884242294</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.440048089943251</v>
+        <v>-5.645977203517341</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7840070214508068</v>
+        <v>0.7016353760211711</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.6089108915108706</v>
+        <v>-0.7687652119337436</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.595036146835333</v>
+        <v>2.499123554581609</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367682</v>
+        <v>3.821593509367685</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.367805521772056</v>
+        <v>-5.573734635346146</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8168333625541049</v>
+        <v>0.7344617171244692</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.6089108915108706</v>
+        <v>-0.7687652119337436</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.598965460670153</v>
+        <v>2.503052868416429</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879964</v>
+        <v>3.822326997879967</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.314807199490668</v>
+        <v>-5.520736313064758</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.838711275384</v>
+        <v>0.7563396299543643</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.5535746325089318</v>
+        <v>-0.7134289529318047</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.632845799988656</v>
+        <v>2.536933207734932</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502337</v>
+        <v>3.848616626502339</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.206002314010941</v>
+        <v>-5.411931427585031</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8792313007958845</v>
+        <v>0.7968596553662484</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.5535746325089318</v>
+        <v>-0.7134289529318047</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.629843871208649</v>
+        <v>2.533931278954926</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675938</v>
+        <v>3.81866895167594</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.985981515973931</v>
+        <v>-5.191910629548021</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9688186570213029</v>
+        <v>0.8864470115916667</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.4123547874409516</v>
+        <v>-0.5722091078638245</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.716154815260052</v>
+        <v>2.620242223006328</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539949</v>
+        <v>3.843274527539951</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.853113826910653</v>
+        <v>-5.059042940484743</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.037859915448437</v>
+        <v>0.955488270018801</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.4123547874409516</v>
+        <v>-0.5722091078638245</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.732048998061875</v>
+        <v>2.636136405808151</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504738649626</v>
+        <v>3.845047386496261</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.732940743546155</v>
+        <v>-4.938869857120245</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.087074993234538</v>
+        <v>1.004703347804903</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.2921817040764526</v>
+        <v>-0.4520360244993256</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.805298692520876</v>
+        <v>2.709386100267153</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576996</v>
+        <v>3.791273551576998</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.588268598446417</v>
+        <v>-4.794197712020507</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.155031953835873</v>
+        <v>1.072660308406237</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.1475095589767152</v>
+        <v>-0.3073638793995881</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.902190082142158</v>
+        <v>2.806277489888435</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942101</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.648143425804109</v>
+        <v>-4.854072539378199</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.117119514294222</v>
+        <v>1.034747868864586</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.2073843863344073</v>
+        <v>-0.3672387067572803</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.852302677128969</v>
+        <v>2.756390084875245</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674513</v>
+        <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.561343928025101</v>
+        <v>-4.767273041599191</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.174239806728392</v>
+        <v>1.091868161298756</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.2073843863344073</v>
+        <v>-0.3672387067572803</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.874703170451535</v>
+        <v>2.778790578197811</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430693</v>
+        <v>3.729146398430695</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.563813634486907</v>
+        <v>-4.769742748060997</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.173324325517081</v>
+        <v>1.090952680087445</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.2098540927962135</v>
+        <v>-0.3697084132190864</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.873293747947864</v>
+        <v>2.77738115569414</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.7432201960036</v>
+        <v>3.743220196003602</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.632183820810917</v>
+        <v>-4.838112934385007</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.156983173462179</v>
+        <v>1.074611528032543</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.2005783937599985</v>
+        <v>-0.3604327141828715</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.889866089844295</v>
+        <v>2.793953497590571</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508367</v>
+        <v>3.71417913950837</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.645971873657964</v>
+        <v>-4.851900987232054</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.141904660955252</v>
+        <v>1.059533015525616</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.2005783937599985</v>
+        <v>-0.3604327141828715</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.880302798476186</v>
+        <v>2.784390206222462</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417701</v>
+        <v>3.710906731417704</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.676965032986669</v>
+        <v>-4.775735440199632</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9542169622641565</v>
+        <v>0.9147087993789715</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.2005783937599985</v>
+        <v>-0.3604327141828715</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.705012363516573</v>
+        <v>2.609099771262849</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205898</v>
+        <v>3.7460425262059</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.501490773194201</v>
+        <v>-4.600261180407163</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.028973898172932</v>
+        <v>0.9894657352877472</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.2005783937599985</v>
+        <v>-0.3604327141828715</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.709579595508361</v>
+        <v>2.613667003254637</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225442</v>
+        <v>3.765024323225445</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.61242702583545</v>
+        <v>-4.711197433048412</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9603414258776395</v>
+        <v>0.9208332629924545</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.2005783937599985</v>
+        <v>-0.3604327141828715</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.685321624269568</v>
+        <v>2.589409032015844</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.578763480363167</v>
+        <v>-4.677533887576129</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9769382292864579</v>
+        <v>0.9374300664012729</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.1669148482877167</v>
+        <v>-0.3267691687105896</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.708651136772842</v>
+        <v>2.612738544519118</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.518910861159444</v>
+        <v>-4.617681268372406</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.011051663400079</v>
+        <v>0.9715435005148947</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.1669148482877167</v>
+        <v>-0.3267691687105896</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.718823523204974</v>
+        <v>2.622910930951251</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.432667398133066</v>
+        <v>-4.531437805346028</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.040495319184491</v>
+        <v>1.000987156299306</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.1669148482877167</v>
+        <v>-0.3267691687105896</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.713769793778835</v>
+        <v>2.617857201525111</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.477974217532046</v>
+        <v>-4.576744624745008</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.014148366869424</v>
+        <v>0.9746402039842397</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.2077250112969475</v>
+        <v>-0.3675793317198204</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.681059471417822</v>
+        <v>2.585146879164098</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.507007322234347</v>
+        <v>-4.605777729447309</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.003086998021606</v>
+        <v>0.9635788351364207</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.2077250112969475</v>
+        <v>-0.3675793317198204</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.681611344450924</v>
+        <v>2.5856987521972</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.414196840783488</v>
+        <v>-4.51296724799645</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9694838824933152</v>
+        <v>0.9299757196081302</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.1149145298460881</v>
+        <v>-0.2747688502689611</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.666570325212805</v>
+        <v>2.570657732959081</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.458586310112915</v>
+        <v>-4.557356717325877</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9536015706861449</v>
+        <v>0.9140934078009602</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.1593039991755158</v>
+        <v>-0.3191583195983888</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.641810119539749</v>
+        <v>2.545897527286025</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.345915091876665</v>
+        <v>-4.444685499089627</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9937457664923679</v>
+        <v>0.9542376036071831</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.04663278093926559</v>
+        <v>-0.2064871013621385</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.704488558993222</v>
+        <v>2.608575966739498</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.233538090693992</v>
+        <v>-4.332308497906954</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.044187862796104</v>
+        <v>1.00467969991092</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.04663278093926559</v>
+        <v>-0.2064871013621385</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.70997985482389</v>
+        <v>2.614067262570166</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.261318488595345</v>
+        <v>-4.360088895808307</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.044572905404102</v>
+        <v>1.005064742518918</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.07441317884061865</v>
+        <v>-0.2342674992634916</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.704808817851617</v>
+        <v>2.608896225597893</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.344319769620624</v>
+        <v>-4.443090176833586</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8497281129946441</v>
+        <v>0.8102199501094594</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.09298406336779241</v>
+        <v>-0.2528383837906654</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.532022007135966</v>
+        <v>2.436109414882242</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.452933848063955</v>
+        <v>-4.551704255276917</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9264321423365174</v>
+        <v>0.8869239794513324</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.09298406336779241</v>
+        <v>-0.2528383837906654</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.652171667855171</v>
+        <v>2.556259075601448</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190768</v>
+        <v>3.733012441190769</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.417524809815812</v>
+        <v>-4.516295217028774</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9551087837380974</v>
+        <v>0.9156006208529126</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.09298406336779241</v>
+        <v>-0.2528383837906654</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.666684693957494</v>
+        <v>2.570772101703771</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.379141147257661</v>
+        <v>-4.477911554470623</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9678816901037266</v>
+        <v>0.9283735272185418</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.05460040080964124</v>
+        <v>-0.2144547212325142</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.687134332834754</v>
+        <v>2.59122174058103</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532485</v>
+        <v>3.751147197532486</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.202024817222495</v>
+        <v>-4.300795224435457</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.035457250963095</v>
+        <v>0.99594908807791</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.05460040080964124</v>
+        <v>-0.2144547212325142</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.683863361680056</v>
+        <v>2.587950769426332</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793902</v>
+        <v>3.741328448793904</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.247117062056041</v>
+        <v>-4.345887469269003</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.01810374479159</v>
+        <v>0.9785955819064049</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.116496443979031</v>
+        <v>-0.276350764401904</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.647409127540335</v>
+        <v>2.551496535286611</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.750729377011236</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.067741640817273</v>
+        <v>-4.166512048030235</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.083640888593511</v>
+        <v>1.044132725708326</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.04028031419168765</v>
+        <v>-0.1195740062311853</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.73526215774918</v>
+        <v>2.639349565495456</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982229</v>
+        <v>3.71699171898223</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.112755854337879</v>
+        <v>-4.211526261550841</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.046442658516859</v>
+        <v>1.006934495631674</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.009931418877083042</v>
+        <v>-0.1499229015457899</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.697860275892007</v>
+        <v>2.601947683638284</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509537</v>
+        <v>3.737026608509539</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.379760364610314</v>
+        <v>-4.478530771823276</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9453324167468304</v>
+        <v>0.9058242538616454</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.1844316191658655</v>
+        <v>-0.3442859395887385</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.586934015405184</v>
+        <v>2.49102142315146</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.480958146047486</v>
+        <v>-4.579728553260448</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9040572260684627</v>
+        <v>0.864549063183278</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.2528404327111847</v>
+        <v>-0.4126947531340577</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.545092649174494</v>
+        <v>2.44918005692077</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.448482559876714</v>
+        <v>-4.547252967089676</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9146474220910883</v>
+        <v>0.8751392592059035</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.2528404327111847</v>
+        <v>-0.4126947531340577</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.542692610728811</v>
+        <v>2.446780018475087</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.429444432169417</v>
+        <v>-4.528214839382379</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.918787392382252</v>
+        <v>0.8792792294970673</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.3110240440423793</v>
+        <v>-0.4708783644652522</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.504307163138339</v>
+        <v>2.408394570884615</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.460571063320035</v>
+        <v>-4.559341470532997</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.083918608860685</v>
+        <v>1.044410445975501</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.3110240440423793</v>
+        <v>-0.4708783644652522</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.681889032077019</v>
+        <v>2.585976439823296</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.474437824653953</v>
+        <v>-4.573208231866915</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.079205233313252</v>
+        <v>1.039697070428067</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.3488819607762022</v>
+        <v>-0.5087362811990752</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.660007611022859</v>
+        <v>2.564095018769136</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.429633653114023</v>
+        <v>-4.528404060326985</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.10313543232615</v>
+        <v>1.063627269440965</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.3488819607762022</v>
+        <v>-0.5087362811990752</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.666016141419785</v>
+        <v>2.570103549166062</v>
       </c>
     </row>
     <row r="1966">
@@ -46766,19 +46766,19 @@
         <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.909559048546589</v>
+        <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.281890682879021</v>
+        <v>-4.380661090091983</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.196446351081233</v>
+        <v>1.201877105326988</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.181074603541319</v>
+        <v>-0.3409289239641921</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.800914286421798</v>
+        <v>2.749940611299013</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.80224592918117</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.91235267007807</v>
+        <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.383905365410242</v>
+        <v>-4.482675772623204</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.158434099600226</v>
+        <v>1.16386485384598</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.181074603541319</v>
+        <v>-0.3409289239641921</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.803707907953279</v>
+        <v>2.752734232830494</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394728</v>
+        <v>3.805608985394731</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.913015018469728</v>
+        <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.377752659357458</v>
+        <v>-4.47652306657042</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.161557530412998</v>
+        <v>1.166988284658752</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.1749218974885348</v>
+        <v>-0.3347762179114078</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.808061879976607</v>
+        <v>2.757088204853823</v>
       </c>
     </row>
     <row r="1969">
@@ -46835,19 +46835,19 @@
         <v>3.798239794890609</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.912095495209838</v>
+        <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.39456195750796</v>
+        <v>-4.493332364720922</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.153914287892907</v>
+        <v>1.159345042138662</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.1917311956390364</v>
+        <v>-0.3515855160619094</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.797056777826417</v>
+        <v>2.746083102703632</v>
       </c>
     </row>
     <row r="1970">
@@ -46858,19 +46858,19 @@
         <v>3.867362636798425</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.978431049006659</v>
+        <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.332263958731837</v>
+        <v>-4.431034365944799</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.245169041200177</v>
+        <v>1.250599795445932</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.1917311956390364</v>
+        <v>-0.3515855160619094</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.863392331623237</v>
+        <v>2.812418656500453</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992189</v>
+        <v>3.848729139992191</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.687011921396057</v>
+        <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.130473761066679</v>
+        <v>-4.229244168279641</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.034465992655638</v>
+        <v>1.039896746901393</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.006286996530117994</v>
+        <v>-0.153567323892755</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.690784119314128</v>
+        <v>2.639810444191344</v>
       </c>
     </row>
     <row r="1972">
@@ -46904,19 +46904,19 @@
         <v>3.841444817852421</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.757302153718233</v>
+        <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.070583079424086</v>
+        <v>-4.169353486637048</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.128712497634851</v>
+        <v>1.134143251880605</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.06617767817271147</v>
+        <v>-0.09367664225016153</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.79700876062186</v>
+        <v>2.746035085499075</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319544</v>
+        <v>3.819063300319545</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.771929889834276</v>
+        <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.16832362404906</v>
+        <v>-4.267094031262022</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.104244015900905</v>
+        <v>1.109674770146659</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.05028840003973128</v>
+        <v>-0.1095659203831417</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.802102929858115</v>
+        <v>2.751129254735331</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489383</v>
+        <v>3.831819032489384</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.770465870658948</v>
+        <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.34466138417199</v>
+        <v>-4.443431791384952</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.032244892676405</v>
+        <v>1.037675646922159</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.1260493600831981</v>
+        <v>-0.2859036805060711</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.694836254609029</v>
+        <v>2.643862579486245</v>
       </c>
     </row>
     <row r="1975">
@@ -46973,19 +46973,19 @@
         <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.768957488698876</v>
+        <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.268239337740063</v>
+        <v>-4.367009744953025</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.061305329289104</v>
+        <v>1.066736083534858</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.1260493600831981</v>
+        <v>-0.2859036805060711</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.693327872648958</v>
+        <v>2.642354197526173</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024961</v>
+        <v>3.836023391024962</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.768820356134313</v>
+        <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.223866206101494</v>
+        <v>-4.322636613314456</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.078917449379968</v>
+        <v>1.084348203625722</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.08167622844462952</v>
+        <v>-0.2415305488675025</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.719814619067535</v>
+        <v>2.668840943944751</v>
       </c>
     </row>
     <row r="1977">
@@ -47019,19 +47019,19 @@
         <v>3.821591150863222</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.768820356134313</v>
+        <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.215912235806722</v>
+        <v>-4.314682643019684</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.082099037497877</v>
+        <v>1.087529791743631</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.08167622844462952</v>
+        <v>-0.2415305488675025</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.719814619067535</v>
+        <v>2.668840943944751</v>
       </c>
     </row>
     <row r="1978">
@@ -47042,19 +47042,19 @@
         <v>3.833040181947581</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.775202113162117</v>
+        <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.168256505245666</v>
+        <v>-4.267026912458628</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.107543086750103</v>
+        <v>1.112973840995858</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.03402049788357386</v>
+        <v>-0.1938748183064469</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.754789814431973</v>
+        <v>2.703816139309189</v>
       </c>
     </row>
     <row r="1979">
@@ -47065,19 +47065,19 @@
         <v>3.822707244326873</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.780094486536842</v>
+        <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.04057219545137</v>
+        <v>-4.139342602664332</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.163509184042547</v>
+        <v>1.168939938288301</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.09366381191072259</v>
+        <v>-0.06619050851215041</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.836292773683276</v>
+        <v>2.785319098560491</v>
       </c>
     </row>
     <row r="1980">
@@ -47088,19 +47088,19 @@
         <v>3.828837911314548</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.766849159012714</v>
+        <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.101238785853759</v>
+        <v>-4.200009193066721</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.125997220357463</v>
+        <v>1.131427974603218</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.01196549519218892</v>
+        <v>-0.1478888252306841</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.774028456128028</v>
+        <v>2.723054781005243</v>
       </c>
     </row>
     <row r="1981">
@@ -47111,19 +47111,19 @@
         <v>3.816866067690023</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.770946861623343</v>
+        <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.056400384245361</v>
+        <v>-4.155170791458323</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.148030283611451</v>
+        <v>1.153461037857206</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.0165089281370584</v>
+        <v>-0.1433453922858146</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.780852218505578</v>
+        <v>2.729878543382794</v>
       </c>
     </row>
     <row r="1982">
@@ -47134,19 +47134,19 @@
         <v>3.817961388674307</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.775107801254421</v>
+        <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.157159020002359</v>
+        <v>-4.255929427215321</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.11188776893973</v>
+        <v>1.117318523185485</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.07231664058994702</v>
+        <v>-0.23217096101282</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.731717816900453</v>
+        <v>2.680744141777669</v>
       </c>
     </row>
     <row r="1983">
@@ -47157,19 +47157,19 @@
         <v>3.826713779163217</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.780987403782258</v>
+        <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.112956182916458</v>
+        <v>-4.211726590129421</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.135448506301927</v>
+        <v>1.140879260547682</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.02811380350404658</v>
+        <v>-0.1879681239269196</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.76411912167983</v>
+        <v>2.713145446557046</v>
       </c>
     </row>
     <row r="1984">
@@ -47180,19 +47180,19 @@
         <v>3.838228663022901</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.779397404251505</v>
+        <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.149935210579901</v>
+        <v>-4.248705617792863</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.119066895705798</v>
+        <v>1.124497649951552</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.008860098287283957</v>
+        <v>-0.1509942221355891</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.784713463223876</v>
+        <v>2.733739788101092</v>
       </c>
     </row>
     <row r="1985">
@@ -47203,19 +47203,19 @@
         <v>3.863924114042136</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.830645169434545</v>
+        <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.169993289444742</v>
+        <v>-4.268763696657704</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.162291429342901</v>
+        <v>1.167722183588656</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.008860098287283957</v>
+        <v>-0.1509942221355891</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.835961228406916</v>
+        <v>2.784987553284132</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865367715078277</v>
+        <v>3.865367715078278</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.829085874028798</v>
+        <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.130062616266851</v>
+        <v>-4.228833023479813</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.17670440320831</v>
+        <v>1.182135157454065</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.0487907714651743</v>
+        <v>-0.1110635489576987</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.858360336907903</v>
+        <v>2.807386661785118</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232394</v>
+        <v>3.864518876232395</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.824034102267068</v>
+        <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.079030523544324</v>
+        <v>-4.177800930757286</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.192065468535592</v>
+        <v>1.197496222781346</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.09982286418770225</v>
+        <v>-0.06003145623517075</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.88392782077969</v>
+        <v>2.832954145656906</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842576394162108</v>
+        <v>3.84257639416211</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.841221506359773</v>
+        <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.013806342417118</v>
+        <v>-4.11257674963008</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.235342545079179</v>
+        <v>1.240773299324933</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.1650470453149079</v>
+        <v>0.005192724892034872</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.940249733548718</v>
+        <v>2.889276058425934</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840090220639813</v>
+        <v>3.840090220639816</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.837182478659054</v>
+        <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.976379322345985</v>
+        <v>-4.075149729558946</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.246274325406912</v>
+        <v>1.251705079652667</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.1702985833440895</v>
+        <v>0.01044426292121653</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.939361628665508</v>
+        <v>2.888387953542723</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845198842749918</v>
+        <v>3.84519884274992</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.838439270990294</v>
+        <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.996490978380693</v>
+        <v>-4.095261385593655</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.239486455324269</v>
+        <v>1.244917209570024</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.1813259283415087</v>
+        <v>0.02147160791863573</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.947234827995199</v>
+        <v>2.896261152872415</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828690479393543</v>
+        <v>3.828690479393545</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.998997042011505</v>
+        <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.942746163953488</v>
+        <v>-4.04151657116645</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.421542152116362</v>
+        <v>1.426972906362117</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.1913892377819707</v>
+        <v>0.03153491735909769</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.113830584680688</v>
+        <v>3.062856909557903</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813251854714881</v>
+        <v>3.813251854714883</v>
       </c>
       <c r="C1992" t="n">
-        <v>3.119109951229322</v>
+        <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.918954595347346</v>
+        <v>-4.017725002560308</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.551171688776636</v>
+        <v>1.556602443022391</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.215180806388113</v>
+        <v>0.05532648596523998</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.24821843506219</v>
+        <v>3.197244759939406</v>
       </c>
     </row>
     <row r="1993">
@@ -47387,19 +47387,19 @@
         <v>3.814259761756009</v>
       </c>
       <c r="C1993" t="n">
-        <v>3.110817927243181</v>
+        <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.892870511083538</v>
+        <v>-3.9916409182965</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.553313298496018</v>
+        <v>1.558744052741773</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.215180806388113</v>
+        <v>0.05532648596523998</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.239926411076049</v>
+        <v>3.188952735953265</v>
       </c>
     </row>
     <row r="1994">
@@ -47410,19 +47410,19 @@
         <v>3.803426852654184</v>
       </c>
       <c r="C1994" t="n">
-        <v>3.10901112282696</v>
+        <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.88853620802649</v>
+        <v>-3.987306615239452</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.553240215302617</v>
+        <v>1.558670969548372</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.3668309097073169</v>
+        <v>0.2069765892844439</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.329109668651351</v>
+        <v>3.278135993528566</v>
       </c>
     </row>
     <row r="1995">
@@ -47433,19 +47433,19 @@
         <v>3.796293177717114</v>
       </c>
       <c r="C1995" t="n">
-        <v>3.126565528553752</v>
+        <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.879643746633207</v>
+        <v>-3.978414153846169</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.574351605586722</v>
+        <v>1.579782359832476</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.3668309097073169</v>
+        <v>0.2069765892844439</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.346664074378142</v>
+        <v>3.295690399255358</v>
       </c>
     </row>
     <row r="1996">
@@ -47456,19 +47456,19 @@
         <v>3.794453975702623</v>
       </c>
       <c r="C1996" t="n">
-        <v>3.118420575958336</v>
+        <v>3.163359493089275</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.048119863603084</v>
+        <v>-4.146890270816046</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.498816206203355</v>
+        <v>1.504246960449109</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.3388830739907361</v>
+        <v>0.1790287535678631</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.321750420352778</v>
+        <v>3.270776745229993</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795603100539965</v>
+        <v>3.795603100539966</v>
       </c>
       <c r="C1997" t="n">
-        <v>3.099690273146197</v>
+        <v>3.144629190277137</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.350320334741501</v>
+        <v>-3.449090741954463</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.75920571493585</v>
+        <v>1.764636469181605</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.2685350146203254</v>
+        <v>0.1086806941974524</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.260811281918393</v>
+        <v>3.209837606795609</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784700379389893</v>
+        <v>3.784700379389895</v>
       </c>
       <c r="C1998" t="n">
-        <v>3.090354295643102</v>
+        <v>3.135293212774041</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.327599231058348</v>
+        <v>-3.42636963827131</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.758958178906016</v>
+        <v>1.76438893315177</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.2685350146203254</v>
+        <v>0.1086806941974524</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.251475304415298</v>
+        <v>3.200501629292513</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783234730534931</v>
+        <v>3.783234730534933</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.249260421494271</v>
+        <v>3.29419933862521</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.467891830595541</v>
+        <v>-3.566662237808503</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.861747264942307</v>
+        <v>1.867178019188062</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.1282424150831328</v>
+        <v>-0.03161190533974023</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.326205870544151</v>
+        <v>3.275232195421367</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.77996275940167</v>
+        <v>3.779962759401672</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.286338243987918</v>
+        <v>3.331277161118857</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.622672837373796</v>
+        <v>-3.721443244586758</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.836912684724652</v>
+        <v>1.842343438970407</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.09487474102865667</v>
+        <v>-0.06497957939421634</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.343263088605112</v>
+        <v>3.292289413482327</v>
       </c>
     </row>
     <row r="2001">
@@ -47571,19 +47571,19 @@
         <v>3.76947265355722</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.283013599977463</v>
+        <v>3.327952517108402</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.689933281395713</v>
+        <v>-3.788703688608675</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.80668386310543</v>
+        <v>1.812114617351185</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.02761429700673956</v>
+        <v>-0.1322400234161334</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.299582178181507</v>
+        <v>3.248608503058722</v>
       </c>
     </row>
     <row r="2002">
@@ -47594,19 +47594,19 @@
         <v>3.766702530088375</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.293019753622204</v>
+        <v>3.337958670753144</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.667461747356881</v>
+        <v>-3.766232154569843</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.825678630365705</v>
+        <v>1.831109384611459</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.1633197818227108</v>
+        <v>0.003465461399837777</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.391011622715831</v>
+        <v>3.340037947593046</v>
       </c>
     </row>
     <row r="2003">
@@ -47617,19 +47617,19 @@
         <v>3.76808110154137</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.477122885767164</v>
+        <v>3.522061802898103</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.803414755413197</v>
+        <v>-3.902185162626159</v>
       </c>
       <c r="E2003" t="n">
-        <v>1.955400559288138</v>
+        <v>1.960831313533893</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.1633197818227108</v>
+        <v>0.003465461399837777</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.575114754860791</v>
+        <v>3.524141079738006</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.827531574668135</v>
+        <v>3.75733643413348</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.628519621976041</v>
+        <v>3.603858440300407</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.803414755413197</v>
+        <v>-3.902185162626159</v>
       </c>
       <c r="E2004" t="n">
-        <v>1.955400559288138</v>
+        <v>1.960831313533893</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.1633197818227108</v>
+        <v>0.003465461399837777</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.621583418962409</v>
+        <v>3.596922237286774</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240623.xlsx
+++ b/tame_output/ON/bt/strategyON_20240623.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>48.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>47.7%</t>
+          <t>15.8%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>79.4%</t>
+          <t>69.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>42.4%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -844,32 +844,32 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-6.9%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>48.8%</t>
+          <t>20.6%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-74.7%</t>
+          <t>-75.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.2%</t>
+          <t>108.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.0%</t>
+          <t>123.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>93.9%</t>
+          <t>92.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.3%</t>
+          <t>-71.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.5%</t>
+          <t>90.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>458.9%</t>
+          <t>454.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-13.0%</t>
+          <t>-12.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-551.8%</t>
+          <t>-571.9%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.2%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>-20.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>120.8%</t>
+          <t>-119.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-180.1%</t>
+          <t>-188.2%</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-16.3%</t>
+          <t>-17.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-3.6%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.9%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>47.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.9%</t>
+          <t>-16.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-86.3%</t>
+          <t>-114.5%</t>
         </is>
       </c>
     </row>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310978</v>
+        <v>3.284619513310979</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.30584953900653</v>
+        <v>3.305849539006531</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955326</v>
+        <v>3.728577929955327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232411</v>
+        <v>3.747702660232412</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45159,10 +45159,10 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.910203451054596</v>
+        <v>-10.04639241096861</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7976422958701521</v>
+        <v>-0.8521178798357565</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.61231323870328</v>
@@ -45182,10 +45182,10 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.812296412378105</v>
+        <v>-9.948485372292115</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.7587797953730169</v>
+        <v>-0.8132553793386208</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.544327488842724</v>
@@ -45205,10 +45205,10 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.788342871402147</v>
+        <v>-9.924531831316157</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.7485298728371399</v>
+        <v>-0.8030054568027443</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.520373947866766</v>
@@ -45228,10 +45228,10 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.52428293307935</v>
+        <v>-9.66047189299336</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6561662136697732</v>
+        <v>-0.7106417976353776</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.25631400954397</v>
@@ -45251,10 +45251,10 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.817203309574513</v>
+        <v>-8.953392269488523</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3761213979281393</v>
+        <v>-0.4305969818937436</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.25631400954397</v>
@@ -45274,10 +45274,10 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.777019011208322</v>
+        <v>-8.913207971122333</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3597040546938217</v>
+        <v>-0.4141796386594261</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.216129711177779</v>
@@ -45297,10 +45297,10 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.613619140268959</v>
+        <v>-8.749808100182971</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2949772850973194</v>
+        <v>-0.3494528690629242</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.052729840238417</v>
@@ -45320,10 +45320,10 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.38013791803936</v>
+        <v>-8.516326877953372</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1936603673676274</v>
+        <v>-0.2481359513332322</v>
       </c>
       <c r="F1903" t="n">
         <v>-1.819248618008818</v>
@@ -45343,10 +45343,10 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.230471527031845</v>
+        <v>-8.366660486945857</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1366860212775807</v>
+        <v>-0.1911616052431855</v>
       </c>
       <c r="F1904" t="n">
         <v>-1.726345126766282</v>
@@ -45366,10 +45366,10 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.098196053400958</v>
+        <v>-8.23438501331497</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.08840834507819872</v>
+        <v>-0.1428839290438035</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.594069653135396</v>
@@ -45389,10 +45389,10 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.942457720841216</v>
+        <v>-8.078646680755229</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.02329795136666535</v>
+        <v>-0.0777735353322706</v>
       </c>
       <c r="F1906" t="n">
         <v>-1.438331320575654</v>
@@ -45412,10 +45412,10 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.693457922157635</v>
+        <v>-7.829646882071648</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.08920830933042589</v>
+        <v>0.03473272536482064</v>
       </c>
       <c r="F1907" t="n">
         <v>-1.438331320575654</v>
@@ -45435,10 +45435,10 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.79904791193074</v>
+        <v>-7.935236871844753</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.08100361617803475</v>
+        <v>-0.13547920014364</v>
       </c>
       <c r="F1908" t="n">
         <v>-1.543921310348759</v>
@@ -45458,10 +45458,10 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.817782814049337</v>
+        <v>-7.95397177396335</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.03995323514838711</v>
+        <v>-0.09442881911399237</v>
       </c>
       <c r="F1909" t="n">
         <v>-1.54951732000889</v>
@@ -45481,10 +45481,10 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.669842772641737</v>
+        <v>-7.80603173255575</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.100656141273515</v>
+        <v>-0.1551317252391202</v>
       </c>
       <c r="F1910" t="n">
         <v>-1.529196404100332</v>
@@ -45504,10 +45504,10 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.616873250387749</v>
+        <v>-7.753062210301762</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.08818231862539783</v>
+        <v>-0.1426579025910031</v>
       </c>
       <c r="F1911" t="n">
         <v>-1.476226881846344</v>
@@ -45527,10 +45527,10 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.573324843617058</v>
+        <v>-7.709513803531071</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.07772356801221481</v>
+        <v>-0.1321991519778201</v>
       </c>
       <c r="F1912" t="n">
         <v>-1.476226881846344</v>
@@ -45550,10 +45550,10 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.3311764501632</v>
+        <v>-7.467365410077213</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.03359814375047154</v>
+        <v>-0.02087744021513371</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.476226881846344</v>
@@ -45573,10 +45573,10 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.222917313040679</v>
+        <v>-7.359106272954691</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.07143391905867524</v>
+        <v>0.01695833509306999</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.476226881846344</v>
@@ -45596,10 +45596,10 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.099626178223548</v>
+        <v>-7.235815138137561</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1182484669961044</v>
+        <v>0.06377288303049911</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.352935747029213</v>
@@ -45619,10 +45619,10 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.078476979320104</v>
+        <v>-7.214665939234117</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1344091247948072</v>
+        <v>0.0799335408292019</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.33178654812577</v>
@@ -45642,10 +45642,10 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.83471153733666</v>
+        <v>-6.970900497250673</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2276960099352352</v>
+        <v>0.1732204259696304</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.33178654812577</v>
@@ -45665,10 +45665,10 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.732948717059365</v>
+        <v>-6.869137676973378</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2705254519661695</v>
+        <v>0.2160498680005642</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.318567479733341</v>
@@ -45688,10 +45688,10 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.483098323110291</v>
+        <v>-6.619287283024303</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3632076845295011</v>
+        <v>0.3087321005638963</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.318567479733341</v>
@@ -45711,10 +45711,10 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.307206230642858</v>
+        <v>-6.44339519055687</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4371636450371228</v>
+        <v>0.382688061071518</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.318567479733341</v>
@@ -45734,10 +45734,10 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.135759767620395</v>
+        <v>-6.271948727534407</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5190697363006618</v>
+        <v>0.464594152335057</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.147121016710878</v>
@@ -45757,10 +45757,10 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.061470201882056</v>
+        <v>-6.197659161796068</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5478060402122944</v>
+        <v>0.4933304562466896</v>
       </c>
       <c r="F1922" t="n">
         <v>-1.072831450972539</v>
@@ -45774,16 +45774,16 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883074</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.997834459648121</v>
+        <v>-6.134023419562133</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5779551381601857</v>
+        <v>0.5234795541945809</v>
       </c>
       <c r="F1923" t="n">
         <v>-1.009195708738604</v>
@@ -45803,10 +45803,10 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.886407700322201</v>
+        <v>-6.022596660236213</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6037201006743493</v>
+        <v>0.5492445167087445</v>
       </c>
       <c r="F1924" t="n">
         <v>-1.009195708738604</v>
@@ -45826,10 +45826,10 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.645977203517341</v>
+        <v>-5.782166163431353</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7016353760211711</v>
+        <v>0.6471597920555663</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.7687652119337436</v>
@@ -45849,10 +45849,10 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.573734635346146</v>
+        <v>-5.709923595260158</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7344617171244692</v>
+        <v>0.6799861331588644</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.7687652119337436</v>
@@ -45872,10 +45872,10 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.520736313064758</v>
+        <v>-5.65692527297877</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7563396299543643</v>
+        <v>0.7018640459887595</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.7134289529318047</v>
@@ -45895,10 +45895,10 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.411931427585031</v>
+        <v>-5.548120387499043</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7968596553662484</v>
+        <v>0.7423840714006436</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.7134289529318047</v>
@@ -45918,10 +45918,10 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.191910629548021</v>
+        <v>-5.328099589462033</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8864470115916667</v>
+        <v>0.8319714276260619</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.5722091078638245</v>
@@ -45941,10 +45941,10 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.059042940484743</v>
+        <v>-5.195231900398755</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.955488270018801</v>
+        <v>0.9010126860531962</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.5722091078638245</v>
@@ -45964,10 +45964,10 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.938869857120245</v>
+        <v>-5.075058817034257</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.004703347804903</v>
+        <v>0.9502277638392975</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.4520360244993256</v>
@@ -45987,10 +45987,10 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.794197712020507</v>
+        <v>-4.930386671934519</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.072660308406237</v>
+        <v>1.018184724440633</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.3073638793995881</v>
@@ -46010,10 +46010,10 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.854072539378199</v>
+        <v>-4.990261499292211</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.034747868864586</v>
+        <v>0.9802722848989815</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.3672387067572803</v>
@@ -46033,10 +46033,10 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.767273041599191</v>
+        <v>-4.903462001513203</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.091868161298756</v>
+        <v>1.037392577333151</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.3672387067572803</v>
@@ -46056,10 +46056,10 @@
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.769742748060997</v>
+        <v>-4.905931707975009</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.090952680087445</v>
+        <v>1.036477096121841</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.3697084132190864</v>
@@ -46079,10 +46079,10 @@
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.838112934385007</v>
+        <v>-4.974301894299019</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.074611528032543</v>
+        <v>1.020135944066939</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.3604327141828715</v>
@@ -46102,10 +46102,10 @@
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.851900987232054</v>
+        <v>-4.988089947146066</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.059533015525616</v>
+        <v>1.005057431560011</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.3604327141828715</v>
@@ -46125,10 +46125,10 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.775735440199632</v>
+        <v>-5.019083106474771</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9147087993789715</v>
+        <v>0.817369732868916</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.3604327141828715</v>
@@ -46148,10 +46148,10 @@
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.600261180407163</v>
+        <v>-4.843608846682303</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9894657352877472</v>
+        <v>0.8921266687776912</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.3604327141828715</v>
@@ -46171,10 +46171,10 @@
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.711197433048412</v>
+        <v>-4.954545099323552</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9208332629924545</v>
+        <v>0.8234941964823985</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.3604327141828715</v>
@@ -46194,10 +46194,10 @@
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.677533887576129</v>
+        <v>-4.920881553851269</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9374300664012729</v>
+        <v>0.8400909998912169</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.3267691687105896</v>
@@ -46217,10 +46217,10 @@
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.617681268372406</v>
+        <v>-4.861028934647546</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9715435005148947</v>
+        <v>0.8742044340048387</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.3267691687105896</v>
@@ -46240,10 +46240,10 @@
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.531437805346028</v>
+        <v>-4.774785471621168</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.000987156299306</v>
+        <v>0.90364808978925</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.3267691687105896</v>
@@ -46263,10 +46263,10 @@
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.576744624745008</v>
+        <v>-4.820092291020148</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9746402039842397</v>
+        <v>0.8773011374741837</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.3675793317198204</v>
@@ -46286,10 +46286,10 @@
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.605777729447309</v>
+        <v>-4.849125395722449</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9635788351364207</v>
+        <v>0.8662397686263648</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.3675793317198204</v>
@@ -46309,10 +46309,10 @@
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.51296724799645</v>
+        <v>-4.75631491427159</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9299757196081302</v>
+        <v>0.8326366530980742</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.2747688502689611</v>
@@ -46332,10 +46332,10 @@
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.557356717325877</v>
+        <v>-4.800704383601017</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9140934078009602</v>
+        <v>0.8167543412909042</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.3191583195983888</v>
@@ -46355,10 +46355,10 @@
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.444685499089627</v>
+        <v>-4.688033165364767</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9542376036071831</v>
+        <v>0.8568985370971272</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.2064871013621385</v>
@@ -46378,10 +46378,10 @@
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.332308497906954</v>
+        <v>-4.575656164182094</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.00467969991092</v>
+        <v>0.9073406334008636</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.2064871013621385</v>
@@ -46401,10 +46401,10 @@
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.360088895808307</v>
+        <v>-4.603436562083447</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.005064742518918</v>
+        <v>0.9077256760088617</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.2342674992634916</v>
@@ -46424,10 +46424,10 @@
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.443090176833586</v>
+        <v>-4.686437843108726</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8102199501094594</v>
+        <v>0.7128808835994034</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.2528383837906654</v>
@@ -46447,10 +46447,10 @@
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.551704255276917</v>
+        <v>-4.795051921552057</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8869239794513324</v>
+        <v>0.7895849129412764</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.2528383837906654</v>
@@ -46470,10 +46470,10 @@
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.516295217028774</v>
+        <v>-4.759642883303914</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9156006208529126</v>
+        <v>0.8182615543428566</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.2528383837906654</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913425</v>
+        <v>3.741174069913426</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.477911554470623</v>
+        <v>-4.721259220745763</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9283735272185418</v>
+        <v>0.8310344607084859</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.2144547212325142</v>
@@ -46516,10 +46516,10 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.300795224435457</v>
+        <v>-4.544142890710597</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.99594908807791</v>
+        <v>0.8986100215678541</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.2144547212325142</v>
@@ -46539,10 +46539,10 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.345887469269003</v>
+        <v>-4.589235135544143</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9785955819064049</v>
+        <v>0.881256515396349</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.276350764401904</v>
@@ -46562,10 +46562,10 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.166512048030235</v>
+        <v>-4.409859714305375</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.044132725708326</v>
+        <v>0.9467936591982704</v>
       </c>
       <c r="F1957" t="n">
         <v>-0.1195740062311853</v>
@@ -46585,10 +46585,10 @@
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.211526261550841</v>
+        <v>-4.454873927825981</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.006934495631674</v>
+        <v>0.9095954291216177</v>
       </c>
       <c r="F1958" t="n">
         <v>-0.1499229015457899</v>
@@ -46608,10 +46608,10 @@
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.478530771823276</v>
+        <v>-4.721878438098416</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9058242538616454</v>
+        <v>0.8084851873515895</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.3442859395887385</v>
@@ -46631,10 +46631,10 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.579728553260448</v>
+        <v>-4.823076219535588</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.864549063183278</v>
+        <v>0.767209996673222</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.4126947531340577</v>
@@ -46654,10 +46654,10 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.547252967089676</v>
+        <v>-4.790600633364816</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8751392592059035</v>
+        <v>0.7778001926958475</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.4126947531340577</v>
@@ -46677,10 +46677,10 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.528214839382379</v>
+        <v>-4.771562505657519</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8792792294970673</v>
+        <v>0.7819401629870113</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.4708783644652522</v>
@@ -46700,10 +46700,10 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.559341470532997</v>
+        <v>-4.802689136808137</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.044410445975501</v>
+        <v>0.9470713794654446</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.4708783644652522</v>
@@ -46723,10 +46723,10 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.573208231866915</v>
+        <v>-4.816555898142055</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.039697070428067</v>
+        <v>0.9423580039180108</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.5087362811990752</v>
@@ -46746,10 +46746,10 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.528404060326985</v>
+        <v>-4.771751726602125</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.063627269440965</v>
+        <v>0.9662882029309088</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.5087362811990752</v>
@@ -46769,10 +46769,10 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.380661090091983</v>
+        <v>-4.624008756367123</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.201877105326988</v>
+        <v>1.104538038816932</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.3409289239641921</v>
@@ -46792,10 +46792,10 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.482675772623204</v>
+        <v>-4.726023438898344</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.16386485384598</v>
+        <v>1.066525787335924</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.3409289239641921</v>
@@ -46815,10 +46815,10 @@
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.47652306657042</v>
+        <v>-4.71987073284556</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.166988284658752</v>
+        <v>1.069649218148696</v>
       </c>
       <c r="F1968" t="n">
         <v>-0.3347762179114078</v>
@@ -46838,10 +46838,10 @@
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.493332364720922</v>
+        <v>-4.736680030996061</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.159345042138662</v>
+        <v>1.062005975628606</v>
       </c>
       <c r="F1969" t="n">
         <v>-0.3515855160619094</v>
@@ -46861,10 +46861,10 @@
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.431034365944799</v>
+        <v>-4.674382032219939</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.250599795445932</v>
+        <v>1.153260728935876</v>
       </c>
       <c r="F1970" t="n">
         <v>-0.3515855160619094</v>
@@ -46884,10 +46884,10 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.229244168279641</v>
+        <v>-4.472591834554781</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.039896746901393</v>
+        <v>0.9425576803913369</v>
       </c>
       <c r="F1971" t="n">
         <v>-0.153567323892755</v>
@@ -46907,10 +46907,10 @@
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.169353486637048</v>
+        <v>-4.412701152912188</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.134143251880605</v>
+        <v>1.036804185370549</v>
       </c>
       <c r="F1972" t="n">
         <v>-0.09367664225016153</v>
@@ -46930,10 +46930,10 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.267094031262022</v>
+        <v>-4.510441697537162</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.109674770146659</v>
+        <v>1.012335703636603</v>
       </c>
       <c r="F1973" t="n">
         <v>-0.1095659203831417</v>
@@ -46953,10 +46953,10 @@
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.443431791384952</v>
+        <v>-4.686779457660092</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.037675646922159</v>
+        <v>0.9403365804121031</v>
       </c>
       <c r="F1974" t="n">
         <v>-0.2859036805060711</v>
@@ -46976,10 +46976,10 @@
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.367009744953025</v>
+        <v>-4.610357411228165</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.066736083534858</v>
+        <v>0.9693970170248025</v>
       </c>
       <c r="F1975" t="n">
         <v>-0.2859036805060711</v>
@@ -46999,10 +46999,10 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.322636613314456</v>
+        <v>-4.565984279589596</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.084348203625722</v>
+        <v>0.9870091371156662</v>
       </c>
       <c r="F1976" t="n">
         <v>-0.2415305488675025</v>
@@ -47022,10 +47022,10 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.314682643019684</v>
+        <v>-4.558030309294824</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.087529791743631</v>
+        <v>0.9901907252335751</v>
       </c>
       <c r="F1977" t="n">
         <v>-0.2415305488675025</v>
@@ -47045,10 +47045,10 @@
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.267026912458628</v>
+        <v>-4.510374578733768</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.112973840995858</v>
+        <v>1.015634774485802</v>
       </c>
       <c r="F1978" t="n">
         <v>-0.1938748183064469</v>
@@ -47068,10 +47068,10 @@
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.139342602664332</v>
+        <v>-4.382690268939472</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.168939938288301</v>
+        <v>1.071600871778245</v>
       </c>
       <c r="F1979" t="n">
         <v>-0.06619050851215041</v>
@@ -47091,10 +47091,10 @@
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.200009193066721</v>
+        <v>-4.443356859341861</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.131427974603218</v>
+        <v>1.034088908093162</v>
       </c>
       <c r="F1980" t="n">
         <v>-0.1478888252306841</v>
@@ -47114,10 +47114,10 @@
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.155170791458323</v>
+        <v>-4.398518457733463</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.153461037857206</v>
+        <v>1.05612197134715</v>
       </c>
       <c r="F1981" t="n">
         <v>-0.1433453922858146</v>
@@ -47137,10 +47137,10 @@
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.255929427215321</v>
+        <v>-4.499277093490461</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.117318523185485</v>
+        <v>1.019979456675429</v>
       </c>
       <c r="F1982" t="n">
         <v>-0.23217096101282</v>
@@ -47160,10 +47160,10 @@
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.211726590129421</v>
+        <v>-4.45507425640456</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.140879260547682</v>
+        <v>1.043540194037626</v>
       </c>
       <c r="F1983" t="n">
         <v>-0.1879681239269196</v>
@@ -47183,10 +47183,10 @@
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.248705617792863</v>
+        <v>-4.492053284068003</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.124497649951552</v>
+        <v>1.027158583441496</v>
       </c>
       <c r="F1984" t="n">
         <v>-0.1509942221355891</v>
@@ -47206,10 +47206,10 @@
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.268763696657704</v>
+        <v>-4.512111362932844</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.167722183588656</v>
+        <v>1.0703831170786</v>
       </c>
       <c r="F1985" t="n">
         <v>-0.1509942221355891</v>
@@ -47229,10 +47229,10 @@
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.228833023479813</v>
+        <v>-4.472180689754953</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.182135157454065</v>
+        <v>1.084796090944009</v>
       </c>
       <c r="F1986" t="n">
         <v>-0.1110635489576987</v>
@@ -47252,10 +47252,10 @@
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.177800930757286</v>
+        <v>-4.421148597032426</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.197496222781346</v>
+        <v>1.10015715627129</v>
       </c>
       <c r="F1987" t="n">
         <v>-0.06003145623517075</v>
@@ -47269,16 +47269,16 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.84257639416211</v>
+        <v>3.842576394162109</v>
       </c>
       <c r="C1988" t="n">
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.11257674963008</v>
+        <v>-4.35592441590522</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.240773299324933</v>
+        <v>1.143434232814877</v>
       </c>
       <c r="F1988" t="n">
         <v>0.005192724892034872</v>
@@ -47292,16 +47292,16 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840090220639816</v>
+        <v>3.840090220639814</v>
       </c>
       <c r="C1989" t="n">
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.075149729558946</v>
+        <v>-4.318497395834086</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.251705079652667</v>
+        <v>1.154366013142611</v>
       </c>
       <c r="F1989" t="n">
         <v>0.01044426292121653</v>
@@ -47315,16 +47315,16 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.84519884274992</v>
+        <v>3.845198842749918</v>
       </c>
       <c r="C1990" t="n">
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.095261385593655</v>
+        <v>-4.338609051868795</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.244917209570024</v>
+        <v>1.147578143059968</v>
       </c>
       <c r="F1990" t="n">
         <v>0.02147160791863573</v>
@@ -47338,16 +47338,16 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828690479393545</v>
+        <v>3.828690479393543</v>
       </c>
       <c r="C1991" t="n">
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.04151657116645</v>
+        <v>-4.28486423744159</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.426972906362117</v>
+        <v>1.329633839852061</v>
       </c>
       <c r="F1991" t="n">
         <v>0.03153491735909769</v>
@@ -47361,16 +47361,16 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813251854714883</v>
+        <v>3.813251854714881</v>
       </c>
       <c r="C1992" t="n">
         <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.017725002560308</v>
+        <v>-4.261072668835448</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.556602443022391</v>
+        <v>1.459263376512335</v>
       </c>
       <c r="F1992" t="n">
         <v>0.05532648596523998</v>
@@ -47384,16 +47384,16 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814259761756009</v>
+        <v>3.814259761756007</v>
       </c>
       <c r="C1993" t="n">
         <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.9916409182965</v>
+        <v>-4.23498858457164</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.558744052741773</v>
+        <v>1.461404986231717</v>
       </c>
       <c r="F1993" t="n">
         <v>0.05532648596523998</v>
@@ -47407,16 +47407,16 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803426852654184</v>
+        <v>3.803426852654182</v>
       </c>
       <c r="C1994" t="n">
         <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.987306615239452</v>
+        <v>-4.230654281514592</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.558670969548372</v>
+        <v>1.461331903038316</v>
       </c>
       <c r="F1994" t="n">
         <v>0.2069765892844439</v>
@@ -47430,16 +47430,16 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796293177717114</v>
+        <v>3.796293177717112</v>
       </c>
       <c r="C1995" t="n">
         <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.978414153846169</v>
+        <v>-4.221761820121309</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.579782359832476</v>
+        <v>1.48244329332242</v>
       </c>
       <c r="F1995" t="n">
         <v>0.2069765892844439</v>
@@ -47453,16 +47453,16 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794453975702623</v>
+        <v>3.794453975702622</v>
       </c>
       <c r="C1996" t="n">
         <v>3.163359493089275</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.146890270816046</v>
+        <v>-4.390237937091186</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.504246960449109</v>
+        <v>1.406907893939053</v>
       </c>
       <c r="F1996" t="n">
         <v>0.1790287535678631</v>
@@ -47476,16 +47476,16 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795603100539966</v>
+        <v>3.795603100539964</v>
       </c>
       <c r="C1997" t="n">
         <v>3.144629190277137</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.449090741954463</v>
+        <v>-3.692438408229603</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.764636469181605</v>
+        <v>1.667297402671549</v>
       </c>
       <c r="F1997" t="n">
         <v>0.1086806941974524</v>
@@ -47499,16 +47499,16 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784700379389895</v>
+        <v>3.784700379389893</v>
       </c>
       <c r="C1998" t="n">
         <v>3.135293212774041</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.42636963827131</v>
+        <v>-3.627759568181236</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.76438893315177</v>
+        <v>1.6838329611878</v>
       </c>
       <c r="F1998" t="n">
         <v>0.1086806941974524</v>
@@ -47522,16 +47522,16 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783234730534933</v>
+        <v>3.783234730534931</v>
       </c>
       <c r="C1999" t="n">
         <v>3.29419933862521</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.566662237808503</v>
+        <v>-3.768052167718429</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.867178019188062</v>
+        <v>1.786622047224091</v>
       </c>
       <c r="F1999" t="n">
         <v>-0.03161190533974023</v>
@@ -47545,16 +47545,16 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779962759401672</v>
+        <v>3.77996275940167</v>
       </c>
       <c r="C2000" t="n">
         <v>3.331277161118857</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.721443244586758</v>
+        <v>-3.922833174496684</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.842343438970407</v>
+        <v>1.761787467006436</v>
       </c>
       <c r="F2000" t="n">
         <v>-0.06497957939421634</v>
@@ -47568,16 +47568,16 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.76947265355722</v>
+        <v>3.769472653557218</v>
       </c>
       <c r="C2001" t="n">
         <v>3.327952517108402</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.788703688608675</v>
+        <v>-3.990093618518602</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.812114617351185</v>
+        <v>1.731558645387214</v>
       </c>
       <c r="F2001" t="n">
         <v>-0.1322400234161334</v>
@@ -47591,16 +47591,16 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766702530088375</v>
+        <v>3.766702530088374</v>
       </c>
       <c r="C2002" t="n">
         <v>3.337958670753144</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.766232154569843</v>
+        <v>-3.96762208447977</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.831109384611459</v>
+        <v>1.750553412647488</v>
       </c>
       <c r="F2002" t="n">
         <v>0.003465461399837777</v>
@@ -47614,16 +47614,16 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.76808110154137</v>
+        <v>3.768081101541368</v>
       </c>
       <c r="C2003" t="n">
         <v>3.522061802898103</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.902185162626159</v>
+        <v>-4.103575092536086</v>
       </c>
       <c r="E2003" t="n">
-        <v>1.960831313533893</v>
+        <v>1.880275341569922</v>
       </c>
       <c r="F2003" t="n">
         <v>0.003465461399837777</v>
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.75733643413348</v>
+        <v>3.438720323326466</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.603858440300407</v>
+        <v>3.321794404591796</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.902185162626159</v>
+        <v>-4.103575092536086</v>
       </c>
       <c r="E2004" t="n">
-        <v>1.960831313533893</v>
+        <v>1.880275341569922</v>
       </c>
       <c r="F2004" t="n">
         <v>0.003465461399837777</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.596922237286774</v>
+        <v>3.314858201578164</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240623.xlsx
+++ b/tame_output/ON/bt/strategyON_20240623.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>48.6%</t>
+          <t>60.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.9%</t>
+          <t>-11.7%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>69.8%</t>
+          <t>81.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>42.4%</t>
+          <t>41.0%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -844,37 +844,37 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>66.2%</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>32.6%</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
           <t>0.2</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>54.7%</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>30.8%</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>1.8</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-6.1%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>60.7%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.5%</t>
+          <t>-74.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.7%</t>
+          <t>108.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.9%</t>
+          <t>122.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>92.9%</t>
+          <t>93.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.9%</t>
+          <t>-51.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-71.8%</t>
+          <t>-69.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.2%</t>
+          <t>89.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>454.8%</t>
+          <t>459.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-12.7%</t>
+          <t>-13.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-571.9%</t>
+          <t>-546.9%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>49.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.5%</t>
+          <t>99.2%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-40.5%</t>
+          <t>-37.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>22.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-20.2%</t>
+          <t>-6.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-119.9%</t>
+          <t>-20.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-188.2%</t>
+          <t>-158.1%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-23.0%</t>
+          <t>-22.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-33.2%</t>
+          <t>-32.9%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-16.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>24.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-171.6%</t>
+          <t>-175.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.2%</t>
+          <t>94.4%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.6%</t>
+          <t>-25.4%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>44.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.8%</t>
+          <t>-16.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-114.5%</t>
+          <t>-73.5%</t>
         </is>
       </c>
     </row>
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.368842742009937</v>
+        <v>-6.217510846464581</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5687854548111906</v>
+        <v>0.6293182130293329</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.227808940556759</v>
+        <v>-1.178715420471737</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.379993611594857</v>
+        <v>2.409449723645871</v>
       </c>
     </row>
     <row r="1864">
@@ -44420,19 +44420,19 @@
         <v>3.30081581833052</v>
       </c>
       <c r="C1864" t="n">
-        <v>3.115440519943672</v>
+        <v>3.434401300498924</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.777431519190616</v>
+        <v>-6.62609962364526</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4041114879536778</v>
+        <v>0.7836050267270727</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.636397717737438</v>
+        <v>-1.587304197652416</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.133601889301209</v>
+        <v>2.482018781907475</v>
       </c>
     </row>
     <row r="1865">
@@ -44443,19 +44443,19 @@
         <v>3.302618194191735</v>
       </c>
       <c r="C1865" t="n">
-        <v>3.110625952415132</v>
+        <v>3.429586732970384</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.054007619506448</v>
+        <v>-6.849646996198784</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.2886664802988057</v>
+        <v>0.6893715101771236</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.636397717737438</v>
+        <v>-1.587304197652416</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.12878732177267</v>
+        <v>2.477204214378935</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108636</v>
+        <v>3.305023265108638</v>
       </c>
       <c r="C1866" t="n">
-        <v>3.10862000302401</v>
+        <v>3.427580783579262</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.470399493793446</v>
+        <v>-7.266038870485781</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.120103781192884</v>
+        <v>0.5208088110712019</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.636397717737438</v>
+        <v>-1.587304197652416</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.126781372381547</v>
+        <v>2.475198264987813</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097818</v>
+        <v>3.341378723097819</v>
       </c>
       <c r="C1867" t="n">
-        <v>3.118878693692689</v>
+        <v>3.437839474247941</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.714670894520515</v>
+        <v>-7.510310271212851</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.03265391157073516</v>
+        <v>0.4333589414490531</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.636397717737438</v>
+        <v>-1.587304197652416</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.137040063050226</v>
+        <v>2.485456955656492</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094114</v>
+        <v>3.374439043094115</v>
       </c>
       <c r="C1868" t="n">
-        <v>3.114978258838384</v>
+        <v>3.433939039393636</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.919921913757276</v>
+        <v>-7.715561290449611</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.05334693097827392</v>
+        <v>0.347358098900044</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.636397717737438</v>
+        <v>-1.587304197652416</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.133139628195922</v>
+        <v>2.481556520802187</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199283</v>
+        <v>3.405960511199284</v>
       </c>
       <c r="C1869" t="n">
-        <v>3.113383178893385</v>
+        <v>3.432343959448637</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.083501791941659</v>
+        <v>-7.879141168633994</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1203739621970263</v>
+        <v>0.2803310676812916</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.636397717737438</v>
+        <v>-1.587304197652416</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.131544548250923</v>
+        <v>2.479961440857188</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969591</v>
+        <v>3.424633354969592</v>
       </c>
       <c r="C1870" t="n">
-        <v>3.117162154822593</v>
+        <v>3.436122935377845</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.380163133751857</v>
+        <v>-8.175802510444193</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2352595229918975</v>
+        <v>0.1654455068864205</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.705140853471316</v>
+        <v>-1.656047333386294</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.094077642739804</v>
+        <v>2.442494535346069</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923084</v>
+        <v>3.419979433923085</v>
       </c>
       <c r="C1871" t="n">
-        <v>3.11313585028819</v>
+        <v>3.432096630843442</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.56688284206116</v>
+        <v>-8.362522218753496</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.3139737108500213</v>
+        <v>0.08673131902829656</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.705140853471316</v>
+        <v>-1.656047333386294</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.0900513382054</v>
+        <v>2.438468230811666</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297747</v>
+        <v>3.458100091297748</v>
       </c>
       <c r="C1872" t="n">
-        <v>3.113033748966606</v>
+        <v>3.431994529521858</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.949884230803791</v>
+        <v>-8.745523607496127</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.4672763676686582</v>
+        <v>-0.0665713377903403</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.705140853471316</v>
+        <v>-1.656047333386294</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.089949236883816</v>
+        <v>2.438366129490082</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317615</v>
+        <v>3.447750501317616</v>
       </c>
       <c r="C1873" t="n">
-        <v>3.115605264938036</v>
+        <v>3.434566045493288</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.131754021788826</v>
+        <v>-8.927393398481161</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.5374527680912418</v>
+        <v>-0.1367477382129239</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.887010644456351</v>
+        <v>-1.837917124371329</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.983398878264226</v>
+        <v>2.331815770870491</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737169</v>
+        <v>3.50351550673717</v>
       </c>
       <c r="C1874" t="n">
-        <v>3.120955568236086</v>
+        <v>3.439916348791338</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.491284344292827</v>
+        <v>-9.286923720985163</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.6759145937947921</v>
+        <v>-0.2752095639164742</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.887010644456351</v>
+        <v>-1.837917124371329</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.988749181562276</v>
+        <v>2.337166074168541</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341312</v>
+        <v>3.503170282341313</v>
       </c>
       <c r="C1875" t="n">
-        <v>3.128871588193264</v>
+        <v>3.447832368748516</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.541633407747049</v>
+        <v>-9.337272784439385</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.6881381992193036</v>
+        <v>-0.2874331693409857</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.937359707910573</v>
+        <v>-1.888266187825551</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.96645576344692</v>
+        <v>2.314872656053185</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539462</v>
+        <v>3.501052558539463</v>
       </c>
       <c r="C1876" t="n">
-        <v>3.131913338815032</v>
+        <v>3.450874119370285</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.639252685168445</v>
+        <v>-9.434892061860781</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.7241441595660931</v>
+        <v>-0.3234391296877752</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.03497898533197</v>
+        <v>-1.985885465246948</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.91092594761585</v>
+        <v>2.259342840222116</v>
       </c>
     </row>
     <row r="1877">
@@ -44719,19 +44719,19 @@
         <v>3.492448711937497</v>
       </c>
       <c r="C1877" t="n">
-        <v>3.134806895136605</v>
+        <v>3.453767675691857</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.786778773174088</v>
+        <v>-9.582418149866424</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.7802610384467781</v>
+        <v>-0.3795560085684602</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.182505073337614</v>
+        <v>-2.133411553252591</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.825303851134037</v>
+        <v>2.173720743740302</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141699</v>
+        <v>3.5027903991417</v>
       </c>
       <c r="C1878" t="n">
-        <v>3.140320092255247</v>
+        <v>3.459280872810499</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.991036948503952</v>
+        <v>-9.786676325196288</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.856451111460081</v>
+        <v>-0.4557460815817631</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.310144017951603</v>
+        <v>-2.26105049786658</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.754233681484286</v>
+        <v>2.102650574090551</v>
       </c>
     </row>
     <row r="1879">
@@ -44765,19 +44765,19 @@
         <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
-        <v>3.144802646739683</v>
+        <v>3.463763427294935</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.06536992476412</v>
+        <v>-9.861009301456452</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.8817017474797111</v>
+        <v>-0.4809967176013932</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.454843541886275</v>
+        <v>-2.405750021801253</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.671896521607918</v>
+        <v>2.020313414214184</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440632</v>
+        <v>3.499971739440633</v>
       </c>
       <c r="C1880" t="n">
-        <v>3.160174348233104</v>
+        <v>3.479135128788356</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.991900093096667</v>
+        <v>-9.787539469789003</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.83694211331931</v>
+        <v>-0.4362370834409921</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.381373710218827</v>
+        <v>-2.332280190133805</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.731350122101808</v>
+        <v>2.079767014708074</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608598</v>
+        <v>3.490059241608599</v>
       </c>
       <c r="C1881" t="n">
-        <v>3.174729568980621</v>
+        <v>3.493690349535873</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.16702451048321</v>
+        <v>-9.962663887175546</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.8924366595264104</v>
+        <v>-0.4917316296480929</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.556498127605371</v>
+        <v>-2.507404607520348</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.640830692417399</v>
+        <v>1.989247585023664</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587859441027</v>
+        <v>3.485878594410271</v>
       </c>
       <c r="C1882" t="n">
-        <v>3.167510404079025</v>
+        <v>3.486471184634277</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.4014766044977</v>
+        <v>-10.19711598119004</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.9934366620338024</v>
+        <v>-0.5927316321554845</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.556498127605371</v>
+        <v>-2.507404607520348</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.633611527515803</v>
+        <v>1.982028420122068</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764395</v>
+        <v>3.480692492764396</v>
       </c>
       <c r="C1883" t="n">
-        <v>3.160838213305049</v>
+        <v>3.479798993860301</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.50585133552415</v>
+        <v>-10.30149071221648</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.041858745218357</v>
+        <v>-0.6411537153400393</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.660872858631816</v>
+        <v>-2.611779338546794</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.564314498125959</v>
+        <v>1.912731390732225</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390584</v>
+        <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
-        <v>3.161954003143605</v>
+        <v>3.480914783698857</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.55863749112447</v>
+        <v>-10.35427686781681</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.061857417619931</v>
+        <v>-0.6611523877416134</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.756548345214213</v>
+        <v>-2.707454825129191</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.508024996015078</v>
+        <v>1.856441888621343</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297398</v>
       </c>
       <c r="C1885" t="n">
-        <v>3.16464773177272</v>
+        <v>3.483608512327972</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.68467428449276</v>
+        <v>-10.4803136611851</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.109578406338132</v>
+        <v>-0.7088733764598145</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.731296722404471</v>
+        <v>-2.682203202319449</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.525869698330037</v>
+        <v>1.874286590936303</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322543</v>
       </c>
       <c r="C1886" t="n">
-        <v>3.168638067459121</v>
+        <v>3.487598848014373</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.63265877052395</v>
+        <v>-10.42829814721629</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.084781865064206</v>
+        <v>-0.6840768351858886</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.731296722404471</v>
+        <v>-2.682203202319449</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.529860034016438</v>
+        <v>1.878276926622704</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003826515892</v>
+        <v>3.600038265158921</v>
       </c>
       <c r="C1887" t="n">
-        <v>3.167162840560379</v>
+        <v>3.486123621115631</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.77433061224807</v>
+        <v>-10.56996998894041</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.142925828652596</v>
+        <v>-0.7422207987742784</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.731296722404471</v>
+        <v>-2.682203202319449</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.528384807117697</v>
+        <v>1.876801699723962</v>
       </c>
     </row>
     <row r="1888">
@@ -44972,19 +44972,19 @@
         <v>3.691571733940719</v>
       </c>
       <c r="C1888" t="n">
-        <v>3.182216250725251</v>
+        <v>3.501177031280503</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.72473976782324</v>
+        <v>-10.52037914451557</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.10803608071779</v>
+        <v>-0.7073310508394726</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.681705877979637</v>
+        <v>-2.632612357894615</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.573192723937469</v>
+        <v>1.921609616543734</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770579</v>
+        <v>3.67684154977058</v>
       </c>
       <c r="C1889" t="n">
-        <v>3.169165117078568</v>
+        <v>3.48812589763382</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.71193237481846</v>
+        <v>-10.5075717515108</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.115964257162564</v>
+        <v>-0.7152592272842457</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.730561652988538</v>
+        <v>-2.681468132903516</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.530828125285446</v>
+        <v>1.879245017891711</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615282</v>
+        <v>3.685161381615283</v>
       </c>
       <c r="C1890" t="n">
-        <v>3.178744190114777</v>
+        <v>3.497704970670029</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.48608722209905</v>
+        <v>-10.28172659879139</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.016047123038591</v>
+        <v>-0.6153420931602729</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.688634977401374</v>
+        <v>-2.639541457316352</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.565563203673952</v>
+        <v>1.913980096280218</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812101</v>
+        <v>3.684843823812102</v>
       </c>
       <c r="C1891" t="n">
-        <v>3.179883334670836</v>
+        <v>3.498844115226088</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.36150856576146</v>
+        <v>-10.1571479424538</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.9650765159474957</v>
+        <v>-0.5643714860691778</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.688634977401374</v>
+        <v>-2.639541457316352</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.566702348230011</v>
+        <v>1.915119240836277</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646215</v>
+        <v>3.710935533646216</v>
       </c>
       <c r="C1892" t="n">
-        <v>3.182517108832943</v>
+        <v>3.501477889388195</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.41440385380575</v>
+        <v>-10.21004323049808</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.9836008570031023</v>
+        <v>-0.5828958271247844</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.683679631312928</v>
+        <v>-2.634586111227906</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.572309330045187</v>
+        <v>1.920726222651452</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611567</v>
+        <v>3.768951674611568</v>
       </c>
       <c r="C1893" t="n">
-        <v>3.18825081307158</v>
+        <v>3.507211593626832</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.34227067851787</v>
+        <v>-10.1379100552102</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.9490138826493135</v>
+        <v>-0.5483088527709956</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.683679631312928</v>
+        <v>-2.634586111227906</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.578043034283823</v>
+        <v>1.926459926890089</v>
       </c>
     </row>
     <row r="1894">
@@ -45110,19 +45110,19 @@
         <v>3.728577929955327</v>
       </c>
       <c r="C1894" t="n">
-        <v>3.178513550677715</v>
+        <v>3.497474331232967</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.27090428590822</v>
+        <v>-10.06654366260055</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.9302045879993202</v>
+        <v>-0.5294995581210022</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.61231323870328</v>
+        <v>-2.563219718618258</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.611125607455747</v>
+        <v>1.959542500062012</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232412</v>
+        <v>3.747702660232413</v>
       </c>
       <c r="C1895" t="n">
-        <v>3.168630069364807</v>
+        <v>3.487590849920059</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.17744525192299</v>
+        <v>-9.973084628615329</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.9027044557181374</v>
+        <v>-0.5019994258398195</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.61231323870328</v>
+        <v>-2.563219718618258</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.601242126142839</v>
+        <v>1.949659018749105</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436227</v>
+        <v>3.766317079436229</v>
       </c>
       <c r="C1896" t="n">
-        <v>3.166795508865433</v>
+        <v>3.485756289420685</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.04639241096861</v>
+        <v>-9.705842827746931</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.8521178798357565</v>
+        <v>-0.3969372659918342</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.61231323870328</v>
+        <v>-2.563219718618258</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.599407565643466</v>
+        <v>1.947824458249731</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311948</v>
+        <v>3.78468452131195</v>
       </c>
       <c r="C1897" t="n">
-        <v>3.166495193891973</v>
+        <v>3.485455974447225</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.948485372292115</v>
+        <v>-9.60793578907044</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.8132553793386208</v>
+        <v>-0.358074765494699</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.544327488842724</v>
+        <v>-2.495233968757701</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.639898700586339</v>
+        <v>1.988315593192604</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097243</v>
+        <v>3.800829354097245</v>
       </c>
       <c r="C1898" t="n">
-        <v>3.167163700037466</v>
+        <v>3.486124480592718</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.924531831316157</v>
+        <v>-9.583982248094483</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.8030054568027443</v>
+        <v>-0.347824842958822</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.520373947866766</v>
+        <v>-2.471280427781744</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.654939331317407</v>
+        <v>2.003356223923672</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017772</v>
+        <v>3.789311112017773</v>
       </c>
       <c r="C1899" t="n">
-        <v>3.153903383875714</v>
+        <v>3.472864164430966</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.66047189299336</v>
+        <v>-9.319922309771686</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.7106417976353776</v>
+        <v>-0.2554611837914553</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.25631400954397</v>
+        <v>-2.207220489458948</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.800114978149332</v>
+        <v>2.148531870755598</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839725</v>
+        <v>3.833252747839726</v>
       </c>
       <c r="C1900" t="n">
-        <v>3.151116350215413</v>
+        <v>3.470077130770665</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.953392269488523</v>
+        <v>-8.612842686266848</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.4305969818937436</v>
+        <v>0.02458363195017865</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.25631400954397</v>
+        <v>-2.207220489458948</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.797327944489031</v>
+        <v>2.145744837095297</v>
       </c>
     </row>
     <row r="1901">
@@ -45271,19 +45271,19 @@
         <v>3.83937444738873</v>
       </c>
       <c r="C1901" t="n">
-        <v>3.151459974103255</v>
+        <v>3.470420754658507</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.913207971122333</v>
+        <v>-8.572658387900658</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.4141796386594261</v>
+        <v>0.04100097518449619</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.216129711177779</v>
+        <v>-2.167036191092757</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.821782147396587</v>
+        <v>2.170199040002853</v>
       </c>
     </row>
     <row r="1902">
@@ -45294,19 +45294,19 @@
         <v>3.856161751626476</v>
       </c>
       <c r="C1902" t="n">
-        <v>3.150826795324011</v>
+        <v>3.469787575879264</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.749808100182971</v>
+        <v>-8.409258516961295</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.3494528690629242</v>
+        <v>0.1057277447809986</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.052729840238417</v>
+        <v>-2.003636320153395</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.919188891180962</v>
+        <v>2.267605783787227</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291812</v>
+        <v>3.787330429291811</v>
       </c>
       <c r="C1903" t="n">
-        <v>3.158751224161864</v>
+        <v>3.477712004717116</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.516326877953372</v>
+        <v>-8.175777294731695</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.2481359513332322</v>
+        <v>0.2070446625106905</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.819248618008818</v>
+        <v>-1.770155097923796</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.067202053356573</v>
+        <v>2.415618945962839</v>
       </c>
     </row>
     <row r="1904">
@@ -45340,19 +45340,19 @@
         <v>3.801637122785788</v>
       </c>
       <c r="C1904" t="n">
-        <v>3.155859013848905</v>
+        <v>3.474819794404157</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.366660486945857</v>
+        <v>-8.026110903724181</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1911616052431855</v>
+        <v>0.2640190086007372</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.726345126766282</v>
+        <v>-1.67725160668126</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.120051937789135</v>
+        <v>2.468468830395401</v>
       </c>
     </row>
     <row r="1905">
@@ -45363,19 +45363,19 @@
         <v>3.763182248390428</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.151226500595932</v>
+        <v>3.470187281151184</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.23438501331497</v>
+        <v>-7.893835430093294</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.1428839290438035</v>
+        <v>0.3122966848001187</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.594069653135396</v>
+        <v>-1.544976133050374</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.194784708714694</v>
+        <v>2.54320160132096</v>
       </c>
     </row>
     <row r="1906">
@@ -45386,19 +45386,19 @@
         <v>3.784718794105952</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.154041561283568</v>
+        <v>3.473002341838821</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.078646680755229</v>
+        <v>-7.738097097533553</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.0777735353322706</v>
+        <v>0.3774070785116521</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.438331320575654</v>
+        <v>-1.389237800490632</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.291042768938176</v>
+        <v>2.639459661544441</v>
       </c>
     </row>
     <row r="1907">
@@ -45409,19 +45409,19 @@
         <v>3.753882571960987</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.166947902507227</v>
+        <v>3.485908683062479</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.829646882071648</v>
+        <v>-7.489097298849972</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.03473272536482064</v>
+        <v>0.4899133392087434</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.438331320575654</v>
+        <v>-1.389237800490632</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.303949110161835</v>
+        <v>2.6523660027681</v>
       </c>
     </row>
     <row r="1908">
@@ -45432,19 +45432,19 @@
         <v>3.692931855607646</v>
       </c>
       <c r="C1908" t="n">
-        <v>3.038971972908008</v>
+        <v>3.357932753463261</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.935236871844753</v>
+        <v>-7.594687288623076</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.13547920014364</v>
+        <v>0.3197014137002827</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.543921310348759</v>
+        <v>-1.494827790263736</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.112619186698754</v>
+        <v>2.461036079305019</v>
       </c>
     </row>
     <row r="1909">
@@ -45455,19 +45455,19 @@
         <v>3.770422583987903</v>
       </c>
       <c r="C1909" t="n">
-        <v>3.087516314785095</v>
+        <v>3.406477095340347</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.95397177396335</v>
+        <v>-7.613422190741673</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.09442881911399237</v>
+        <v>0.3607517947299304</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.54951732000889</v>
+        <v>-1.500423799923868</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.157805922779761</v>
+        <v>2.506222815386026</v>
       </c>
     </row>
     <row r="1910">
@@ -45478,19 +45478,19 @@
         <v>3.760333686710812</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.967637392096927</v>
+        <v>3.286598172652179</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.80603173255575</v>
+        <v>-7.465482149334074</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.1551317252391202</v>
+        <v>0.3000488886048025</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.529196404100332</v>
+        <v>-1.48010288401531</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.050119549636728</v>
+        <v>2.398536442242993</v>
       </c>
     </row>
     <row r="1911">
@@ -45501,19 +45501,19 @@
         <v>3.723566229409205</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.958923405843449</v>
+        <v>3.277884186398701</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.753062210301762</v>
+        <v>-7.412512627080085</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.1426579025910031</v>
+        <v>0.3125227112529196</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.476226881846344</v>
+        <v>-1.427133361761321</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.073187276735643</v>
+        <v>2.421604169341909</v>
       </c>
     </row>
     <row r="1912">
@@ -45524,19 +45524,19 @@
         <v>3.729969716098109</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.951962793748356</v>
+        <v>3.270923574303608</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.709513803531071</v>
+        <v>-7.368964220309395</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.1321991519778201</v>
+        <v>0.3229814618661027</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.476226881846344</v>
+        <v>-1.427133361761321</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.06622666464055</v>
+        <v>2.414643557246816</v>
       </c>
     </row>
     <row r="1913">
@@ -45547,19 +45547,19 @@
         <v>3.782922533493419</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.966425148129499</v>
+        <v>3.285385928684751</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.467365410077213</v>
+        <v>-7.126815826855537</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.02087744021513371</v>
+        <v>0.434303173628789</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.476226881846344</v>
+        <v>-1.427133361761321</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.080689019021693</v>
+        <v>2.429105911627959</v>
       </c>
     </row>
     <row r="1914">
@@ -45570,19 +45570,19 @@
         <v>3.828551486722816</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.960957268588694</v>
+        <v>3.279918049143946</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.359106272954691</v>
+        <v>-7.018556689733015</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.01695833509306999</v>
+        <v>0.4721389489369927</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.476226881846344</v>
+        <v>-1.427133361761321</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.075221139480888</v>
+        <v>2.423638032087154</v>
       </c>
     </row>
     <row r="1915">
@@ -45593,19 +45593,19 @@
         <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.958455362599271</v>
+        <v>3.277416143154523</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.235815138137561</v>
+        <v>-6.895265554915884</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.06377288303049911</v>
+        <v>0.5189534968744218</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.352935747029213</v>
+        <v>-1.303842226944191</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.146693914381743</v>
+        <v>2.495110806988009</v>
       </c>
     </row>
     <row r="1916">
@@ -45616,19 +45616,19 @@
         <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.966156340836596</v>
+        <v>3.285117121391848</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.214665939234117</v>
+        <v>-6.874116356012441</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.0799335408292019</v>
+        <v>0.5351141546731246</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.33178654812577</v>
+        <v>-1.282693028040748</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.167084411961135</v>
+        <v>2.5155013045674</v>
       </c>
     </row>
     <row r="1917">
@@ -45639,19 +45639,19 @@
         <v>3.748328408318093</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.961937049183647</v>
+        <v>3.280897829738899</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.970900497250673</v>
+        <v>-6.630350914028996</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.1732204259696304</v>
+        <v>0.6284010398135531</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.33178654812577</v>
+        <v>-1.282693028040748</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.162865120308185</v>
+        <v>2.51128201291445</v>
       </c>
     </row>
     <row r="1918">
@@ -45662,19 +45662,19 @@
         <v>3.824311233057526</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.964061363103663</v>
+        <v>3.283022143658915</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.869137676973378</v>
+        <v>-6.528588093751702</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2160498680005642</v>
+        <v>0.671230481844487</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.318567479733341</v>
+        <v>-1.269473959648319</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.172920875263658</v>
+        <v>2.521337767869924</v>
       </c>
     </row>
     <row r="1919">
@@ -45685,19 +45685,19 @@
         <v>3.826354974279186</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.956803438087365</v>
+        <v>3.275764218642617</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.619287283024303</v>
+        <v>-6.278737699802627</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3087321005638963</v>
+        <v>0.763912714407819</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.318567479733341</v>
+        <v>-1.269473959648319</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.165662950247361</v>
+        <v>2.514079842853626</v>
       </c>
     </row>
     <row r="1920">
@@ -45708,19 +45708,19 @@
         <v>3.835957987011499</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.960402561608014</v>
+        <v>3.279363342163266</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.44339519055687</v>
+        <v>-6.102845607335194</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.382688061071518</v>
+        <v>0.8378686749154407</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.318567479733341</v>
+        <v>-1.269473959648319</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.169262073768009</v>
+        <v>2.517678966374275</v>
       </c>
     </row>
     <row r="1921">
@@ -45731,19 +45731,19 @@
         <v>3.780933911392987</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.973730067662567</v>
+        <v>3.292690848217819</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.271948727534407</v>
+        <v>-5.931399144312731</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.464594152335057</v>
+        <v>0.9197747661789801</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.147121016710878</v>
+        <v>-1.098027496625856</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.285457457636041</v>
+        <v>2.633874350242306</v>
       </c>
     </row>
     <row r="1922">
@@ -45754,19 +45754,19 @@
         <v>3.773765222632782</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.972750545278864</v>
+        <v>3.291711325834116</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.197659161796068</v>
+        <v>-5.857109578574391</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.4933304562466896</v>
+        <v>0.9485110700906128</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.072831450972539</v>
+        <v>-1.023737930887516</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.329051674695342</v>
+        <v>2.677468567301607</v>
       </c>
     </row>
     <row r="1923">
@@ -45777,19 +45777,19 @@
         <v>3.764617879883074</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.977445346333182</v>
+        <v>3.296406126888434</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.134023419562133</v>
+        <v>-5.793473836340457</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5234795541945809</v>
+        <v>0.9786601680385036</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.009195708738604</v>
+        <v>-0.9601021886535818</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.37192792109002</v>
+        <v>2.720344813696285</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074783</v>
+        <v>3.798814771074784</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.958639605116977</v>
+        <v>3.277600385672229</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.022596660236213</v>
+        <v>-5.682047077014537</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.5492445167087445</v>
+        <v>1.004425130552667</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.009195708738604</v>
+        <v>-0.9601021886535818</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.353122179873815</v>
+        <v>2.701539072480081</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242294</v>
+        <v>3.797694884242295</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.960382681741855</v>
+        <v>3.279343462297107</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.782166163431353</v>
+        <v>-5.441616580209677</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.6471597920555663</v>
+        <v>1.102340405899489</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.7687652119337436</v>
+        <v>-0.7196716918487215</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.499123554581609</v>
+        <v>2.847540447187874</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367685</v>
+        <v>3.821593509367686</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.964311995576675</v>
+        <v>3.283272776131927</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.709923595260158</v>
+        <v>-5.369374012038482</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6799861331588644</v>
+        <v>1.135166747002787</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.7687652119337436</v>
+        <v>-0.7196716918487215</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.503052868416429</v>
+        <v>2.851469761022694</v>
       </c>
     </row>
     <row r="1927">
@@ -45869,19 +45869,19 @@
         <v>3.822326997879967</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.964990579494015</v>
+        <v>3.283951360049267</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.65692527297877</v>
+        <v>-5.316375689757094</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7018640459887595</v>
+        <v>1.157044659832682</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.7134289529318047</v>
+        <v>-0.6643354328467826</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.536933207734932</v>
+        <v>2.885350100341197</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502339</v>
+        <v>3.84861662650234</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.961988650714008</v>
+        <v>3.28094943126926</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.548120387499043</v>
+        <v>-5.207570804277367</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7423840714006436</v>
+        <v>1.197564685244566</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.7134289529318047</v>
+        <v>-0.6643354328467826</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.533931278954926</v>
+        <v>2.882348171561191</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.81866895167594</v>
+        <v>3.818668951675941</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.963567687724622</v>
+        <v>3.282528468279875</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.328099589462033</v>
+        <v>-4.987550006240356</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8319714276260619</v>
+        <v>1.287152041469985</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.5722091078638245</v>
+        <v>-0.5231155877788024</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.620242223006328</v>
+        <v>2.968659115612593</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539951</v>
+        <v>3.843274527539952</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.979461870526446</v>
+        <v>3.298422651081698</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.195231900398755</v>
+        <v>-4.854682317177079</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9010126860531962</v>
+        <v>1.356193299897119</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.5722091078638245</v>
+        <v>-0.5231155877788024</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.636136405808151</v>
+        <v>2.984553298414417</v>
       </c>
     </row>
     <row r="1931">
@@ -45961,19 +45961,19 @@
         <v>3.845047386496261</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.980607714966748</v>
+        <v>3.299568495522</v>
       </c>
       <c r="D1931" t="n">
-        <v>-5.075058817034257</v>
+        <v>-4.73450923381258</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.9502277638392975</v>
+        <v>1.40540837768322</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.4520360244993256</v>
+        <v>-0.4029425044143035</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.709386100267153</v>
+        <v>3.057802992873418</v>
       </c>
     </row>
     <row r="1932">
@@ -45984,19 +45984,19 @@
         <v>3.791273551576998</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.990695817528187</v>
+        <v>3.30965659808344</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.930386671934519</v>
+        <v>-4.589837088712843</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.018184724440633</v>
+        <v>1.473365338284555</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.3073638793995881</v>
+        <v>-0.258270359314566</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.806277489888435</v>
+        <v>3.1546943824947</v>
       </c>
     </row>
     <row r="1933">
@@ -46007,19 +46007,19 @@
         <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.976733308929613</v>
+        <v>3.295694089484865</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.990261499292211</v>
+        <v>-4.649711916070535</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.9802722848989815</v>
+        <v>1.435452898742904</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.3672387067572803</v>
+        <v>-0.3181451866722582</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.756390084875245</v>
+        <v>3.104806977481511</v>
       </c>
     </row>
     <row r="1934">
@@ -46030,19 +46030,19 @@
         <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.999133802252179</v>
+        <v>3.318094582807432</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.903462001513203</v>
+        <v>-4.562912418291527</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.037392577333151</v>
+        <v>1.492573191177074</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.3672387067572803</v>
+        <v>-0.3181451866722582</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.778790578197811</v>
+        <v>3.127207470804077</v>
       </c>
     </row>
     <row r="1935">
@@ -46053,19 +46053,19 @@
         <v>3.729146398430695</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.999206203625592</v>
+        <v>3.318166984180844</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.905931707975009</v>
+        <v>-4.565382124753333</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.036477096121841</v>
+        <v>1.491657709965763</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.3697084132190864</v>
+        <v>-0.3206148931340643</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.77738115569414</v>
+        <v>3.125798048300406</v>
       </c>
     </row>
     <row r="1936">
@@ -46076,19 +46076,19 @@
         <v>3.743220196003602</v>
       </c>
       <c r="C1936" t="n">
-        <v>3.010213126100294</v>
+        <v>3.329173906655546</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.974301894299019</v>
+        <v>-4.633752311077343</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.020135944066939</v>
+        <v>1.475316557910861</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.3604327141828715</v>
+        <v>-0.3113391940978494</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.793953497590571</v>
+        <v>3.142370390196836</v>
       </c>
     </row>
     <row r="1937">
@@ -46099,19 +46099,19 @@
         <v>3.71417913950837</v>
       </c>
       <c r="C1937" t="n">
-        <v>3.000649834732185</v>
+        <v>3.319610615287437</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.988089947146066</v>
+        <v>-4.64754036392439</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.005057431560011</v>
+        <v>1.460238045403934</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.3604327141828715</v>
+        <v>-0.3113391940978494</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.784390206222462</v>
+        <v>3.132807098828728</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417704</v>
+        <v>3.710906731417705</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.825359399772572</v>
+        <v>3.144320180327824</v>
       </c>
       <c r="D1938" t="n">
-        <v>-5.019083106474771</v>
+        <v>-4.678533523253095</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.817369732868916</v>
+        <v>1.272550346712839</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.3604327141828715</v>
+        <v>-0.3113391940978494</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.609099771262849</v>
+        <v>2.957516663869114</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.7460425262059</v>
+        <v>3.746042526205901</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.829926631764359</v>
+        <v>3.148887412319612</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.843608846682303</v>
+        <v>-4.503059263460626</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.8921266687776912</v>
+        <v>1.347307282621614</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.3604327141828715</v>
+        <v>-0.3113391940978494</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.613667003254637</v>
+        <v>2.962083895860902</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225445</v>
+        <v>3.765024323225446</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.805668660525567</v>
+        <v>3.124629441080819</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.954545099323552</v>
+        <v>-4.613995516101875</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8234941964823985</v>
+        <v>1.278674810326321</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.3604327141828715</v>
+        <v>-0.3113391940978494</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.589409032015844</v>
+        <v>2.937825924622109</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111293</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.808800045745472</v>
+        <v>3.127760826300724</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.920881553851269</v>
+        <v>-4.580331970629593</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8400909998912169</v>
+        <v>1.29527161373514</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.3267691687105896</v>
+        <v>-0.2776756486255675</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.612738544519118</v>
+        <v>2.961155437125384</v>
       </c>
     </row>
     <row r="1942">
@@ -46214,19 +46214,19 @@
         <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.818972432177604</v>
+        <v>3.137933212732857</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.861028934647546</v>
+        <v>-4.52047935142587</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.8742044340048387</v>
+        <v>1.329385047848761</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.3267691687105896</v>
+        <v>-0.2776756486255675</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.622910930951251</v>
+        <v>2.971327823557516</v>
       </c>
     </row>
     <row r="1943">
@@ -46237,19 +46237,19 @@
         <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.813918702751465</v>
+        <v>3.132879483306717</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.774785471621168</v>
+        <v>-4.434235888399492</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.90364808978925</v>
+        <v>1.358828703633173</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.3267691687105896</v>
+        <v>-0.2776756486255675</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.617857201525111</v>
+        <v>2.966274094131377</v>
       </c>
     </row>
     <row r="1944">
@@ -46260,19 +46260,19 @@
         <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.80569447819599</v>
+        <v>3.124655258751242</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.820092291020148</v>
+        <v>-4.479542707798472</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8773011374741837</v>
+        <v>1.332481751318106</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.3675793317198204</v>
+        <v>-0.3184858116347983</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.585146879164098</v>
+        <v>2.933563771770364</v>
       </c>
     </row>
     <row r="1945">
@@ -46283,19 +46283,19 @@
         <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.806246351229092</v>
+        <v>3.125207131784344</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.849125395722449</v>
+        <v>-4.508575812500773</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.8662397686263648</v>
+        <v>1.321420382470287</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.3675793317198204</v>
+        <v>-0.3184858116347983</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.5856987521972</v>
+        <v>2.934115644803465</v>
       </c>
     </row>
     <row r="1946">
@@ -46306,19 +46306,19 @@
         <v>3.733390600809497</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.735519043120457</v>
+        <v>3.05447982367571</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.75631491427159</v>
+        <v>-4.415765331049913</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8326366530980742</v>
+        <v>1.287817266941997</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.2747688502689611</v>
+        <v>-0.225675330183939</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.570657732959081</v>
+        <v>2.919074625565346</v>
       </c>
     </row>
     <row r="1947">
@@ -46329,19 +46329,19 @@
         <v>3.748285816560425</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.737392519045058</v>
+        <v>3.05635329960031</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.800704383601017</v>
+        <v>-4.460154800379341</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8167543412909042</v>
+        <v>1.271934955134827</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.3191583195983888</v>
+        <v>-0.2700647995133666</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.545897527286025</v>
+        <v>2.894314419892291</v>
       </c>
     </row>
     <row r="1948">
@@ -46352,19 +46352,19 @@
         <v>3.721077195472738</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.732468227556781</v>
+        <v>3.051429008112033</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.688033165364767</v>
+        <v>-4.347483582143091</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.8568985370971272</v>
+        <v>1.31207915094105</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.2064871013621385</v>
+        <v>-0.1573935812771164</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.608575966739498</v>
+        <v>2.956992859345764</v>
       </c>
     </row>
     <row r="1949">
@@ -46375,19 +46375,19 @@
         <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.737959523387449</v>
+        <v>3.056920303942701</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.575656164182094</v>
+        <v>-4.235106580960418</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9073406334008636</v>
+        <v>1.362521247244786</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.2064871013621385</v>
+        <v>-0.1573935812771164</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.614067262570166</v>
+        <v>2.962484155176431</v>
       </c>
     </row>
     <row r="1950">
@@ -46398,19 +46398,19 @@
         <v>3.689597840498865</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.749456725155988</v>
+        <v>3.06841750571124</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.603436562083447</v>
+        <v>-4.26288697886177</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9077256760088617</v>
+        <v>1.362906289852784</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.2342674992634916</v>
+        <v>-0.1851739791784695</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.608896225597893</v>
+        <v>2.957313118204158</v>
       </c>
     </row>
     <row r="1951">
@@ -46421,19 +46421,19 @@
         <v>3.643069621705325</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.587812445156641</v>
+        <v>2.906773225711893</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.686437843108726</v>
+        <v>-4.345888259887049</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7128808835994034</v>
+        <v>1.168061497443326</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.2528383837906654</v>
+        <v>-0.2037448637056433</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.436109414882242</v>
+        <v>2.784526307488507</v>
       </c>
     </row>
     <row r="1952">
@@ -46444,19 +46444,19 @@
         <v>3.68271631072927</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.707962105875847</v>
+        <v>3.026922886431099</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.795051921552057</v>
+        <v>-4.45450233833038</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.7895849129412764</v>
+        <v>1.244765526785199</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.2528383837906654</v>
+        <v>-0.2037448637056433</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.556259075601448</v>
+        <v>2.904675968207713</v>
       </c>
     </row>
     <row r="1953">
@@ -46467,19 +46467,19 @@
         <v>3.733012441190769</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.722475131978169</v>
+        <v>3.041435912533422</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.759642883303914</v>
+        <v>-4.419093300082237</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8182615543428566</v>
+        <v>1.273442168186779</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.2528383837906654</v>
+        <v>-0.2037448637056433</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.570772101703771</v>
+        <v>2.919188994310036</v>
       </c>
     </row>
     <row r="1954">
@@ -46490,19 +46490,19 @@
         <v>3.741174069913426</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.719894573320538</v>
+        <v>3.03885535387579</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.721259220745763</v>
+        <v>-4.380709637524086</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8310344607084859</v>
+        <v>1.286215074552409</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.2144547212325142</v>
+        <v>-0.1653612011474921</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.59122174058103</v>
+        <v>2.939638633187295</v>
       </c>
     </row>
     <row r="1955">
@@ -46513,19 +46513,19 @@
         <v>3.751147197532486</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.71662360216584</v>
+        <v>3.035584382721092</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.544142890710597</v>
+        <v>-4.20359330748892</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8986100215678541</v>
+        <v>1.353790635411777</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.2144547212325142</v>
+        <v>-0.1653612011474921</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.587950769426332</v>
+        <v>2.936367662032597</v>
       </c>
     </row>
     <row r="1956">
@@ -46536,19 +46536,19 @@
         <v>3.741328448793904</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.717306993927753</v>
+        <v>3.036267774483005</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.589235135544143</v>
+        <v>-4.248685552322466</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.881256515396349</v>
+        <v>1.336437129240272</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.276350764401904</v>
+        <v>-0.2272572443168819</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.551496535286611</v>
+        <v>2.899913427892876</v>
       </c>
     </row>
     <row r="1957">
@@ -46559,19 +46559,19 @@
         <v>3.750729377011236</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.711093969234168</v>
+        <v>3.03005474978942</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.409859714305375</v>
+        <v>-4.069310131083698</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9467936591982704</v>
+        <v>1.401974273042193</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.1195740062311853</v>
+        <v>-0.0704804861461632</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.639349565495456</v>
+        <v>2.987766458101722</v>
       </c>
     </row>
     <row r="1958">
@@ -46582,19 +46582,19 @@
         <v>3.71699171898223</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.691901424565757</v>
+        <v>3.010862205121009</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.454873927825981</v>
+        <v>-4.114324344604304</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9095954291216177</v>
+        <v>1.36477604296554</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.1499229015457899</v>
+        <v>-0.1008293814607678</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.601947683638284</v>
+        <v>2.950364576244549</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509539</v>
+        <v>3.73702660850954</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.697592986904703</v>
+        <v>3.016553767459955</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.721878438098416</v>
+        <v>-4.381328854876739</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8084851873515895</v>
+        <v>1.263665801195512</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.3442859395887385</v>
+        <v>-0.2951924195037164</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.49102142315146</v>
+        <v>2.839438315757726</v>
       </c>
     </row>
     <row r="1960">
@@ -46628,19 +46628,19 @@
         <v>3.70230945476081</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.696796908801204</v>
+        <v>3.015757689356457</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.823076219535588</v>
+        <v>-4.482526636313912</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.767209996673222</v>
+        <v>1.222390610517145</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.4126947531340577</v>
+        <v>-0.3636012330490356</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.44918005692077</v>
+        <v>2.797596949527036</v>
       </c>
     </row>
     <row r="1961">
@@ -46651,19 +46651,19 @@
         <v>3.705571661815455</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.694396870355521</v>
+        <v>3.013357650910773</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.790600633364816</v>
+        <v>-4.45005105014314</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.7778001926958475</v>
+        <v>1.23298080653977</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.4126947531340577</v>
+        <v>-0.3636012330490356</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.446780018475087</v>
+        <v>2.795196911081352</v>
       </c>
     </row>
     <row r="1962">
@@ -46674,19 +46674,19 @@
         <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.690921589563766</v>
+        <v>3.009882370119018</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.771562505657519</v>
+        <v>-4.431012922435842</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.7819401629870113</v>
+        <v>1.237120776830934</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.4708783644652522</v>
+        <v>-0.4217848443802301</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.408394570884615</v>
+        <v>2.75681146349088</v>
       </c>
     </row>
     <row r="1963">
@@ -46697,19 +46697,19 @@
         <v>3.73106447313125</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.868503458502447</v>
+        <v>3.187464239057699</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.802689136808137</v>
+        <v>-4.462139553586461</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9470713794654446</v>
+        <v>1.402251993309367</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.4708783644652522</v>
+        <v>-0.4217848443802301</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.585976439823296</v>
+        <v>2.934393332429561</v>
       </c>
     </row>
     <row r="1964">
@@ -46720,19 +46720,19 @@
         <v>3.722447362067865</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.86933678748858</v>
+        <v>3.188297568043832</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.816555898142055</v>
+        <v>-4.476006314920379</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9423580039180108</v>
+        <v>1.397538617761934</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.5087362811990752</v>
+        <v>-0.4596427611140531</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.564095018769136</v>
+        <v>2.912511911375401</v>
       </c>
     </row>
     <row r="1965">
@@ -46743,19 +46743,19 @@
         <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.875345317885506</v>
+        <v>3.194306098440758</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.771751726602125</v>
+        <v>-4.431202143380449</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9662882029309088</v>
+        <v>1.421468816774832</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.5087362811990752</v>
+        <v>-0.4596427611140531</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.570103549166062</v>
+        <v>2.918520441772327</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519908</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.954497965677528</v>
+        <v>3.27345874623278</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.624008756367123</v>
+        <v>-4.283459173145446</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.104538038816932</v>
+        <v>1.559718652660854</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.3409289239641921</v>
+        <v>-0.2918354038791699</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.749940611299013</v>
+        <v>3.098357503905278</v>
       </c>
     </row>
     <row r="1967">
@@ -46789,19 +46789,19 @@
         <v>3.80224592918117</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.957291587209009</v>
+        <v>3.276252367764261</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.726023438898344</v>
+        <v>-4.385473855676667</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.066525787335924</v>
+        <v>1.521706401179847</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.3409289239641921</v>
+        <v>-0.2918354038791699</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.752734232830494</v>
+        <v>3.101151125436759</v>
       </c>
     </row>
     <row r="1968">
@@ -46812,19 +46812,19 @@
         <v>3.805608985394731</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.957953935600667</v>
+        <v>3.27691471615592</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.71987073284556</v>
+        <v>-4.379321149623883</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.069649218148696</v>
+        <v>1.524829831992619</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.3347762179114078</v>
+        <v>-0.2856826978263856</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.757088204853823</v>
+        <v>3.105505097460088</v>
       </c>
     </row>
     <row r="1969">
@@ -46835,19 +46835,19 @@
         <v>3.798239794890609</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.957034412340778</v>
+        <v>3.27599519289603</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.736680030996061</v>
+        <v>-4.396130447774385</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.062005975628606</v>
+        <v>1.517186589472528</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.3515855160619094</v>
+        <v>-0.3024919959768873</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.746083102703632</v>
+        <v>3.094499995309897</v>
       </c>
     </row>
     <row r="1970">
@@ -46858,19 +46858,19 @@
         <v>3.867362636798425</v>
       </c>
       <c r="C1970" t="n">
-        <v>3.023369966137599</v>
+        <v>3.342330746692851</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.674382032219939</v>
+        <v>-4.333832448998263</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.153260728935876</v>
+        <v>1.608441342779798</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.3515855160619094</v>
+        <v>-0.3024919959768873</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.812418656500453</v>
+        <v>3.160835549106719</v>
       </c>
     </row>
     <row r="1971">
@@ -46881,19 +46881,19 @@
         <v>3.848729139992191</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.731950838526997</v>
+        <v>3.050911619082249</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.472591834554781</v>
+        <v>-4.132042251333105</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9425576803913369</v>
+        <v>1.39773829423526</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.153567323892755</v>
+        <v>-0.1044738038077329</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.639810444191344</v>
+        <v>2.988227336797609</v>
       </c>
     </row>
     <row r="1972">
@@ -46904,19 +46904,19 @@
         <v>3.841444817852421</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.802241070849172</v>
+        <v>3.121201851404424</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.412701152912188</v>
+        <v>-4.072151569690512</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.036804185370549</v>
+        <v>1.491984799214472</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.09367664225016153</v>
+        <v>-0.04458312216513938</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.746035085499075</v>
+        <v>3.094451978105341</v>
       </c>
     </row>
     <row r="1973">
@@ -46927,19 +46927,19 @@
         <v>3.819063300319545</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.816868806965215</v>
+        <v>3.135829587520468</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.510441697537162</v>
+        <v>-4.169892114315486</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.012335703636603</v>
+        <v>1.467516317480526</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.1095659203831417</v>
+        <v>-0.06047240029811957</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.751129254735331</v>
+        <v>3.099546147341596</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489384</v>
+        <v>3.831819032489385</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.815404787789887</v>
+        <v>3.134365568345139</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.686779457660092</v>
+        <v>-4.346229874438415</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9403365804121031</v>
+        <v>1.395517194256026</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.2859036805060711</v>
+        <v>-0.236810160421049</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.643862579486245</v>
+        <v>2.99227947209251</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397793</v>
+        <v>3.836411672397794</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.813896405829816</v>
+        <v>3.132857186385068</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.610357411228165</v>
+        <v>-4.269807828006488</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9693970170248025</v>
+        <v>1.424577630868725</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.2859036805060711</v>
+        <v>-0.236810160421049</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.642354197526173</v>
+        <v>2.990771090132439</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024962</v>
+        <v>3.836023391024963</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.813759273265252</v>
+        <v>3.132720053820504</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.565984279589596</v>
+        <v>-4.22543469636792</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9870091371156662</v>
+        <v>1.442189750959589</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.2415305488675025</v>
+        <v>-0.1924370287824804</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.668840943944751</v>
+        <v>3.017257836551016</v>
       </c>
     </row>
     <row r="1977">
@@ -47019,19 +47019,19 @@
         <v>3.821591150863222</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.813759273265252</v>
+        <v>3.132720053820504</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.558030309294824</v>
+        <v>-4.217480726073148</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9901907252335751</v>
+        <v>1.445371339077498</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.2415305488675025</v>
+        <v>-0.1924370287824804</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.668840943944751</v>
+        <v>3.017257836551016</v>
       </c>
     </row>
     <row r="1978">
@@ -47042,19 +47042,19 @@
         <v>3.833040181947581</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.820141030293057</v>
+        <v>3.139101810848309</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.510374578733768</v>
+        <v>-4.169824995512092</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.015634774485802</v>
+        <v>1.470815388329725</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.1938748183064469</v>
+        <v>-0.1447812982214247</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.703816139309189</v>
+        <v>3.052233031915454</v>
       </c>
     </row>
     <row r="1979">
@@ -47065,19 +47065,19 @@
         <v>3.822707244326873</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.825033403667781</v>
+        <v>3.143994184223033</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.382690268939472</v>
+        <v>-4.042140685717795</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.071600871778245</v>
+        <v>1.526781485622168</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.06619050851215041</v>
+        <v>-0.01709698842712826</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.785319098560491</v>
+        <v>3.133735991166757</v>
       </c>
     </row>
     <row r="1980">
@@ -47088,19 +47088,19 @@
         <v>3.828837911314548</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.811788076143654</v>
+        <v>3.130748856698906</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.443356859341861</v>
+        <v>-4.102807276120185</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.034088908093162</v>
+        <v>1.489269521937084</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.1478888252306841</v>
+        <v>-0.09879530514566193</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.723054781005243</v>
+        <v>3.071471673611509</v>
       </c>
     </row>
     <row r="1981">
@@ -47111,19 +47111,19 @@
         <v>3.816866067690023</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.815885778754282</v>
+        <v>3.134846559309534</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.398518457733463</v>
+        <v>-4.057968874511786</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.05612197134715</v>
+        <v>1.511302585191072</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.1433453922858146</v>
+        <v>-0.09425187220079245</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.729878543382794</v>
+        <v>3.078295435989059</v>
       </c>
     </row>
     <row r="1982">
@@ -47134,19 +47134,19 @@
         <v>3.817961388674307</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.82004671838536</v>
+        <v>3.139007498940612</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.499277093490461</v>
+        <v>-4.158727510268784</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.019979456675429</v>
+        <v>1.475160070519351</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.23217096101282</v>
+        <v>-0.1830774409277979</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.680744141777669</v>
+        <v>3.029161034383934</v>
       </c>
     </row>
     <row r="1983">
@@ -47157,19 +47157,19 @@
         <v>3.826713779163217</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.825926320913197</v>
+        <v>3.144887101468449</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.45507425640456</v>
+        <v>-4.114524673182884</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.043540194037626</v>
+        <v>1.498720807881549</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.1879681239269196</v>
+        <v>-0.1388746038418974</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.713145446557046</v>
+        <v>3.061562339163311</v>
       </c>
     </row>
     <row r="1984">
@@ -47180,19 +47180,19 @@
         <v>3.838228663022901</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.824336321382445</v>
+        <v>3.143297101937697</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.492053284068003</v>
+        <v>-4.151503700846327</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.027158583441496</v>
+        <v>1.482339197285419</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.1509942221355891</v>
+        <v>-0.1019007020505669</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.733739788101092</v>
+        <v>3.082156680707357</v>
       </c>
     </row>
     <row r="1985">
@@ -47203,19 +47203,19 @@
         <v>3.863924114042136</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.875584086565484</v>
+        <v>3.194544867120737</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.512111362932844</v>
+        <v>-4.171561779711167</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.0703831170786</v>
+        <v>1.525563730922523</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.1509942221355891</v>
+        <v>-0.1019007020505669</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.784987553284132</v>
+        <v>3.133404445890397</v>
       </c>
     </row>
     <row r="1986">
@@ -47226,19 +47226,19 @@
         <v>3.865367715078278</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.874024791159738</v>
+        <v>3.19298557171499</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.472180689754953</v>
+        <v>-4.131631106533277</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.084796090944009</v>
+        <v>1.539976704787932</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.1110635489576987</v>
+        <v>-0.06197002887267655</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.807386661785118</v>
+        <v>3.155803554391384</v>
       </c>
     </row>
     <row r="1987">
@@ -47249,19 +47249,19 @@
         <v>3.864518876232395</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.868973019398008</v>
+        <v>3.18793379995326</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.421148597032426</v>
+        <v>-4.080599013810749</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.10015715627129</v>
+        <v>1.555337770115213</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.06003145623517075</v>
+        <v>-0.0109379361501486</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.832954145656906</v>
+        <v>3.181371038263171</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842576394162109</v>
+        <v>3.842576394162111</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.886160423490713</v>
+        <v>3.205121204045965</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.35592441590522</v>
+        <v>-4.015374832683544</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.143434232814877</v>
+        <v>1.5986148466588</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.005192724892034872</v>
+        <v>0.05428624497705703</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.889276058425934</v>
+        <v>3.237692951032199</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840090220639814</v>
+        <v>3.840090220639816</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.882121395789993</v>
+        <v>3.201082176345245</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.318497395834086</v>
+        <v>-3.97794781261241</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.154366013142611</v>
+        <v>1.609546626986534</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.01044426292121653</v>
+        <v>0.05953778300623869</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.888387953542723</v>
+        <v>3.236804846148988</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845198842749918</v>
+        <v>3.84519884274992</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.883378188121233</v>
+        <v>3.202338968676485</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.338609051868795</v>
+        <v>-3.998059468647118</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.147578143059968</v>
+        <v>1.602758756903891</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.02147160791863573</v>
+        <v>0.07056512800365788</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.896261152872415</v>
+        <v>3.24467804547868</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828690479393543</v>
+        <v>3.828690479393547</v>
       </c>
       <c r="C1991" t="n">
-        <v>3.043935959142444</v>
+        <v>3.362896739697696</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.28486423744159</v>
+        <v>-3.944314654219914</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.329633839852061</v>
+        <v>1.784814453695983</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.03153491735909769</v>
+        <v>0.08062843744411985</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.062856909557903</v>
+        <v>3.411273802164168</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813251854714881</v>
+        <v>3.813251854714885</v>
       </c>
       <c r="C1992" t="n">
-        <v>3.164048868360261</v>
+        <v>3.483009648915513</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.261072668835448</v>
+        <v>-3.920523085613771</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.459263376512335</v>
+        <v>1.914443990356258</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.05532648596523998</v>
+        <v>0.1044200060502621</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.197244759939406</v>
+        <v>3.545661652545671</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814259761756007</v>
+        <v>3.81425976175601</v>
       </c>
       <c r="C1993" t="n">
-        <v>3.15575684437412</v>
+        <v>3.474717624929372</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.23498858457164</v>
+        <v>-3.894439001349963</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.461404986231717</v>
+        <v>1.916585600075639</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.05532648596523998</v>
+        <v>0.1044200060502621</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.188952735953265</v>
+        <v>3.53736962855953</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803426852654182</v>
+        <v>3.803426852654184</v>
       </c>
       <c r="C1994" t="n">
-        <v>3.1539500399579</v>
+        <v>3.472910820513152</v>
       </c>
       <c r="D1994" t="n">
-        <v>-4.230654281514592</v>
+        <v>-3.890104698292915</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.461331903038316</v>
+        <v>1.916512516882238</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.2069765892844439</v>
+        <v>0.2560701093694661</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.278135993528566</v>
+        <v>3.626552886134832</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796293177717112</v>
+        <v>3.796293177717114</v>
       </c>
       <c r="C1995" t="n">
-        <v>3.171504445684691</v>
+        <v>3.490465226239943</v>
       </c>
       <c r="D1995" t="n">
-        <v>-4.221761820121309</v>
+        <v>-3.881212236899632</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.48244329332242</v>
+        <v>1.937623907166343</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.2069765892844439</v>
+        <v>0.2560701093694661</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.295690399255358</v>
+        <v>3.644107291861623</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794453975702622</v>
+        <v>3.794453975702623</v>
       </c>
       <c r="C1996" t="n">
-        <v>3.163359493089275</v>
+        <v>3.482320273644527</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.390237937091186</v>
+        <v>-4.049688353869509</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.406907893939053</v>
+        <v>1.862088507782976</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.1790287535678631</v>
+        <v>0.2281222736528853</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.270776745229993</v>
+        <v>3.619193637836259</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795603100539964</v>
+        <v>3.795603100539966</v>
       </c>
       <c r="C1997" t="n">
-        <v>3.144629190277137</v>
+        <v>3.463589970832389</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.692438408229603</v>
+        <v>-3.351888825007926</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.667297402671549</v>
+        <v>2.122478016515471</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.1086806941974524</v>
+        <v>0.1577742142824746</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.209837606795609</v>
+        <v>3.558254499401874</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784700379389893</v>
+        <v>3.784700379389895</v>
       </c>
       <c r="C1998" t="n">
-        <v>3.135293212774041</v>
+        <v>3.454253993329294</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.627759568181236</v>
+        <v>-3.329167721324774</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.6838329611878</v>
+        <v>2.122230480485637</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.1086806941974524</v>
+        <v>0.1577742142824746</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.200501629292513</v>
+        <v>3.548918521898778</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783234730534931</v>
+        <v>3.783234730534932</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.29419933862521</v>
+        <v>3.613160119180463</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.768052167718429</v>
+        <v>-3.469460320861966</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.786622047224091</v>
+        <v>2.225019566521929</v>
       </c>
       <c r="F1999" t="n">
-        <v>-0.03161190533974023</v>
+        <v>0.01748161474528193</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.275232195421367</v>
+        <v>3.623649088027632</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.77996275940167</v>
+        <v>3.779962759401671</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.331277161118857</v>
+        <v>3.650237941674109</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.922833174496684</v>
+        <v>-3.624241327640221</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.761787467006436</v>
+        <v>2.200184986304273</v>
       </c>
       <c r="F2000" t="n">
-        <v>-0.06497957939421634</v>
+        <v>-0.01588605930919418</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.292289413482327</v>
+        <v>3.640706306088593</v>
       </c>
     </row>
     <row r="2001">
@@ -47571,19 +47571,19 @@
         <v>3.769472653557218</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.327952517108402</v>
+        <v>3.646913297663654</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.990093618518602</v>
+        <v>-3.691501771662138</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.731558645387214</v>
+        <v>2.169956164685051</v>
       </c>
       <c r="F2001" t="n">
-        <v>-0.1322400234161334</v>
+        <v>-0.08314650333111129</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.248608503058722</v>
+        <v>3.597025395664988</v>
       </c>
     </row>
     <row r="2002">
@@ -47594,19 +47594,19 @@
         <v>3.766702530088374</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.337958670753144</v>
+        <v>3.656919451308396</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.96762208447977</v>
+        <v>-3.669030237623307</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.750553412647488</v>
+        <v>2.188950931945326</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.003465461399837777</v>
+        <v>0.05255898148485993</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.340037947593046</v>
+        <v>3.688454840199312</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768081101541368</v>
+        <v>3.768081101541367</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.522061802898103</v>
+        <v>3.841022583453356</v>
       </c>
       <c r="D2003" t="n">
-        <v>-4.103575092536086</v>
+        <v>-3.804983245679622</v>
       </c>
       <c r="E2003" t="n">
-        <v>1.880275341569922</v>
+        <v>2.31867286086776</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.003465461399837777</v>
+        <v>0.05255898148485993</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.524141079738006</v>
+        <v>3.872557972344272</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.438720323326466</v>
+        <v>3.780796393081655</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.321794404591796</v>
+        <v>3.723290650538015</v>
       </c>
       <c r="D2004" t="n">
-        <v>-4.103575092536086</v>
+        <v>-3.853683399057854</v>
       </c>
       <c r="E2004" t="n">
-        <v>1.880275341569922</v>
+        <v>2.181460866601126</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.003465461399837777</v>
+        <v>0.003858828106628631</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.314858201578164</v>
+        <v>3.725605947401992</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240623.xlsx
+++ b/tame_output/ON/bt/strategyON_20240623.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.2%</t>
+          <t>48.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.7%</t>
+          <t>-12.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>15.6%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>81.8%</t>
+          <t>77.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>41.0%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>64.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>32.6%</t>
+          <t>30.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-6.1%</t>
+          <t>-6.5%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>60.7%</t>
+          <t>42.0%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-74.1%</t>
+          <t>-75.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.2%</t>
+          <t>109.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.2%</t>
+          <t>124.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>93.8%</t>
+          <t>93.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>23.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.1%</t>
+          <t>-51.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-69.6%</t>
+          <t>-71.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.7%</t>
+          <t>90.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>459.2%</t>
+          <t>454.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-13.2%</t>
+          <t>-12.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-546.9%</t>
+          <t>-563.0%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>49.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.2%</t>
+          <t>99.5%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-37.4%</t>
+          <t>-40.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>22.4%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,22 +1175,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-6.5%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-20.0%</t>
+          <t>121.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-158.1%</t>
+          <t>-183.3%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-22.7%</t>
+          <t>-23.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,22 +1298,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-5.9%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-32.9%</t>
+          <t>-31.7%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-16.0%</t>
+          <t>-16.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>24.9%</t>
+          <t>32.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-175.9%</t>
+          <t>-166.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-223.6%</t>
+          <t>-226.6%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>94.4%</t>
+          <t>96.2%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-25.4%</t>
+          <t>-28.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.6%</t>
+          <t>-17.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-73.5%</t>
+          <t>-94.0%</t>
         </is>
       </c>
     </row>
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970902</v>
+        <v>3.304715716970903</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.217510846464581</v>
+        <v>-6.368842742009937</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.6293182130293329</v>
+        <v>0.5687854548111906</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.178715420471737</v>
+        <v>-1.227808940556759</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.409449723645871</v>
+        <v>2.379993611594857</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.30081581833052</v>
+        <v>3.300815818330521</v>
       </c>
       <c r="C1864" t="n">
-        <v>3.434401300498924</v>
+        <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.62609962364526</v>
+        <v>-6.777431519190616</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.7836050267270727</v>
+        <v>0.4041114879536778</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.587304197652416</v>
+        <v>-1.636397717737438</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.482018781907475</v>
+        <v>2.133601889301209</v>
       </c>
     </row>
     <row r="1865">
@@ -44443,19 +44443,19 @@
         <v>3.302618194191735</v>
       </c>
       <c r="C1865" t="n">
-        <v>3.429586732970384</v>
+        <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.849646996198784</v>
+        <v>-7.054007619506448</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.6893715101771236</v>
+        <v>0.2886664802988057</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.587304197652416</v>
+        <v>-1.636397717737438</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.477204214378935</v>
+        <v>2.12878732177267</v>
       </c>
     </row>
     <row r="1866">
@@ -44466,19 +44466,19 @@
         <v>3.305023265108638</v>
       </c>
       <c r="C1866" t="n">
-        <v>3.427580783579262</v>
+        <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.266038870485781</v>
+        <v>-7.470399493793446</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.5208088110712019</v>
+        <v>0.120103781192884</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.587304197652416</v>
+        <v>-1.636397717737438</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.475198264987813</v>
+        <v>2.126781372381547</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097819</v>
+        <v>3.34137872309782</v>
       </c>
       <c r="C1867" t="n">
-        <v>3.437839474247941</v>
+        <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.510310271212851</v>
+        <v>-7.714670894520515</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.4333589414490531</v>
+        <v>0.03265391157073516</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.587304197652416</v>
+        <v>-1.636397717737438</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.485456955656492</v>
+        <v>2.137040063050226</v>
       </c>
     </row>
     <row r="1868">
@@ -44512,19 +44512,19 @@
         <v>3.374439043094115</v>
       </c>
       <c r="C1868" t="n">
-        <v>3.433939039393636</v>
+        <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.715561290449611</v>
+        <v>-7.919921913757276</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.347358098900044</v>
+        <v>-0.05334693097827392</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.587304197652416</v>
+        <v>-1.636397717737438</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.481556520802187</v>
+        <v>2.133139628195922</v>
       </c>
     </row>
     <row r="1869">
@@ -44535,19 +44535,19 @@
         <v>3.405960511199284</v>
       </c>
       <c r="C1869" t="n">
-        <v>3.432343959448637</v>
+        <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.879141168633994</v>
+        <v>-8.083501791941659</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.2803310676812916</v>
+        <v>-0.1203739621970263</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.587304197652416</v>
+        <v>-1.636397717737438</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.479961440857188</v>
+        <v>2.131544548250923</v>
       </c>
     </row>
     <row r="1870">
@@ -44558,19 +44558,19 @@
         <v>3.424633354969592</v>
       </c>
       <c r="C1870" t="n">
-        <v>3.436122935377845</v>
+        <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.175802510444193</v>
+        <v>-8.380163133751857</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.1654455068864205</v>
+        <v>-0.2352595229918975</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.656047333386294</v>
+        <v>-1.705140853471316</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.442494535346069</v>
+        <v>2.094077642739804</v>
       </c>
     </row>
     <row r="1871">
@@ -44581,19 +44581,19 @@
         <v>3.419979433923085</v>
       </c>
       <c r="C1871" t="n">
-        <v>3.432096630843442</v>
+        <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.362522218753496</v>
+        <v>-8.56688284206116</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.08673131902829656</v>
+        <v>-0.3139737108500213</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.656047333386294</v>
+        <v>-1.705140853471316</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.438468230811666</v>
+        <v>2.0900513382054</v>
       </c>
     </row>
     <row r="1872">
@@ -44604,19 +44604,19 @@
         <v>3.458100091297748</v>
       </c>
       <c r="C1872" t="n">
-        <v>3.431994529521858</v>
+        <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.745523607496127</v>
+        <v>-8.949884230803791</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.0665713377903403</v>
+        <v>-0.4672763676686582</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.656047333386294</v>
+        <v>-1.705140853471316</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.438366129490082</v>
+        <v>2.089949236883816</v>
       </c>
     </row>
     <row r="1873">
@@ -44627,19 +44627,19 @@
         <v>3.447750501317616</v>
       </c>
       <c r="C1873" t="n">
-        <v>3.434566045493288</v>
+        <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-8.927393398481161</v>
+        <v>-9.131754021788826</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.1367477382129239</v>
+        <v>-0.5374527680912418</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.837917124371329</v>
+        <v>-1.887010644456351</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.331815770870491</v>
+        <v>1.983398878264226</v>
       </c>
     </row>
     <row r="1874">
@@ -44650,19 +44650,19 @@
         <v>3.50351550673717</v>
       </c>
       <c r="C1874" t="n">
-        <v>3.439916348791338</v>
+        <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.286923720985163</v>
+        <v>-9.491284344292827</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.2752095639164742</v>
+        <v>-0.6759145937947921</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.837917124371329</v>
+        <v>-1.887010644456351</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.337166074168541</v>
+        <v>1.988749181562276</v>
       </c>
     </row>
     <row r="1875">
@@ -44673,19 +44673,19 @@
         <v>3.503170282341313</v>
       </c>
       <c r="C1875" t="n">
-        <v>3.447832368748516</v>
+        <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.337272784439385</v>
+        <v>-9.541633407747049</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.2874331693409857</v>
+        <v>-0.6881381992193036</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.888266187825551</v>
+        <v>-1.937359707910573</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.314872656053185</v>
+        <v>1.96645576344692</v>
       </c>
     </row>
     <row r="1876">
@@ -44696,19 +44696,19 @@
         <v>3.501052558539463</v>
       </c>
       <c r="C1876" t="n">
-        <v>3.450874119370285</v>
+        <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.434892061860781</v>
+        <v>-9.639252685168445</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.3234391296877752</v>
+        <v>-0.7241441595660931</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.985885465246948</v>
+        <v>-2.03497898533197</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.259342840222116</v>
+        <v>1.91092594761585</v>
       </c>
     </row>
     <row r="1877">
@@ -44719,19 +44719,19 @@
         <v>3.492448711937497</v>
       </c>
       <c r="C1877" t="n">
-        <v>3.453767675691857</v>
+        <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.582418149866424</v>
+        <v>-9.786778773174088</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.3795560085684602</v>
+        <v>-0.7802610384467781</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.133411553252591</v>
+        <v>-2.182505073337614</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.173720743740302</v>
+        <v>1.825303851134037</v>
       </c>
     </row>
     <row r="1878">
@@ -44742,19 +44742,19 @@
         <v>3.5027903991417</v>
       </c>
       <c r="C1878" t="n">
-        <v>3.459280872810499</v>
+        <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.786676325196288</v>
+        <v>-9.991036948503952</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.4557460815817631</v>
+        <v>-0.856451111460081</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.26105049786658</v>
+        <v>-2.310144017951603</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.102650574090551</v>
+        <v>1.754233681484286</v>
       </c>
     </row>
     <row r="1879">
@@ -44765,19 +44765,19 @@
         <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
-        <v>3.463763427294935</v>
+        <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.861009301456452</v>
+        <v>-10.06536992476412</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.4809967176013932</v>
+        <v>-0.8817017474797111</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.405750021801253</v>
+        <v>-2.454843541886275</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.020313414214184</v>
+        <v>1.671896521607918</v>
       </c>
     </row>
     <row r="1880">
@@ -44788,19 +44788,19 @@
         <v>3.499971739440633</v>
       </c>
       <c r="C1880" t="n">
-        <v>3.479135128788356</v>
+        <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.787539469789003</v>
+        <v>-9.991900093096667</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.4362370834409921</v>
+        <v>-0.83694211331931</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.332280190133805</v>
+        <v>-2.381373710218827</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.079767014708074</v>
+        <v>1.731350122101808</v>
       </c>
     </row>
     <row r="1881">
@@ -44811,19 +44811,19 @@
         <v>3.490059241608599</v>
       </c>
       <c r="C1881" t="n">
-        <v>3.493690349535873</v>
+        <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-9.962663887175546</v>
+        <v>-10.16702451048321</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.4917316296480929</v>
+        <v>-0.8924366595264104</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.507404607520348</v>
+        <v>-2.556498127605371</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.989247585023664</v>
+        <v>1.640830692417399</v>
       </c>
     </row>
     <row r="1882">
@@ -44834,19 +44834,19 @@
         <v>3.485878594410271</v>
       </c>
       <c r="C1882" t="n">
-        <v>3.486471184634277</v>
+        <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.19711598119004</v>
+        <v>-10.4014766044977</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.5927316321554845</v>
+        <v>-0.9934366620338024</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.507404607520348</v>
+        <v>-2.556498127605371</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.982028420122068</v>
+        <v>1.633611527515803</v>
       </c>
     </row>
     <row r="1883">
@@ -44857,19 +44857,19 @@
         <v>3.480692492764396</v>
       </c>
       <c r="C1883" t="n">
-        <v>3.479798993860301</v>
+        <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.30149071221648</v>
+        <v>-10.50585133552415</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.6411537153400393</v>
+        <v>-1.041858745218357</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.611779338546794</v>
+        <v>-2.660872858631816</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.912731390732225</v>
+        <v>1.564314498125959</v>
       </c>
     </row>
     <row r="1884">
@@ -44880,19 +44880,19 @@
         <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
-        <v>3.480914783698857</v>
+        <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.35427686781681</v>
+        <v>-10.55863749112447</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.6611523877416134</v>
+        <v>-1.061857417619931</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.707454825129191</v>
+        <v>-2.756548345214213</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.856441888621343</v>
+        <v>1.508024996015078</v>
       </c>
     </row>
     <row r="1885">
@@ -44903,19 +44903,19 @@
         <v>3.492101641297398</v>
       </c>
       <c r="C1885" t="n">
-        <v>3.483608512327972</v>
+        <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.4803136611851</v>
+        <v>-10.68467428449276</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.7088733764598145</v>
+        <v>-1.109578406338132</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.682203202319449</v>
+        <v>-2.731296722404471</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.874286590936303</v>
+        <v>1.525869698330037</v>
       </c>
     </row>
     <row r="1886">
@@ -44926,19 +44926,19 @@
         <v>3.573674025322543</v>
       </c>
       <c r="C1886" t="n">
-        <v>3.487598848014373</v>
+        <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.42829814721629</v>
+        <v>-10.63265877052395</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.6840768351858886</v>
+        <v>-1.084781865064206</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.682203202319449</v>
+        <v>-2.731296722404471</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.878276926622704</v>
+        <v>1.529860034016438</v>
       </c>
     </row>
     <row r="1887">
@@ -44949,19 +44949,19 @@
         <v>3.600038265158921</v>
       </c>
       <c r="C1887" t="n">
-        <v>3.486123621115631</v>
+        <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.56996998894041</v>
+        <v>-10.77433061224807</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.7422207987742784</v>
+        <v>-1.142925828652596</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.682203202319449</v>
+        <v>-2.731296722404471</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.876801699723962</v>
+        <v>1.528384807117697</v>
       </c>
     </row>
     <row r="1888">
@@ -44972,19 +44972,19 @@
         <v>3.691571733940719</v>
       </c>
       <c r="C1888" t="n">
-        <v>3.501177031280503</v>
+        <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.52037914451557</v>
+        <v>-10.72473976782324</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.7073310508394726</v>
+        <v>-1.10803608071779</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.632612357894615</v>
+        <v>-2.681705877979637</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.921609616543734</v>
+        <v>1.573192723937469</v>
       </c>
     </row>
     <row r="1889">
@@ -44995,19 +44995,19 @@
         <v>3.67684154977058</v>
       </c>
       <c r="C1889" t="n">
-        <v>3.48812589763382</v>
+        <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.5075717515108</v>
+        <v>-10.71193237481846</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.7152592272842457</v>
+        <v>-1.115964257162564</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.681468132903516</v>
+        <v>-2.730561652988538</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.879245017891711</v>
+        <v>1.530828125285446</v>
       </c>
     </row>
     <row r="1890">
@@ -45018,19 +45018,19 @@
         <v>3.685161381615283</v>
       </c>
       <c r="C1890" t="n">
-        <v>3.497704970670029</v>
+        <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.28172659879139</v>
+        <v>-10.48608722209905</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.6153420931602729</v>
+        <v>-1.016047123038591</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.639541457316352</v>
+        <v>-2.688634977401374</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.913980096280218</v>
+        <v>1.565563203673952</v>
       </c>
     </row>
     <row r="1891">
@@ -45041,19 +45041,19 @@
         <v>3.684843823812102</v>
       </c>
       <c r="C1891" t="n">
-        <v>3.498844115226088</v>
+        <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.1571479424538</v>
+        <v>-10.36150856576146</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.5643714860691778</v>
+        <v>-0.9650765159474957</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.639541457316352</v>
+        <v>-2.688634977401374</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.915119240836277</v>
+        <v>1.566702348230011</v>
       </c>
     </row>
     <row r="1892">
@@ -45064,19 +45064,19 @@
         <v>3.710935533646216</v>
       </c>
       <c r="C1892" t="n">
-        <v>3.501477889388195</v>
+        <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.21004323049808</v>
+        <v>-10.41440385380575</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.5828958271247844</v>
+        <v>-0.9836008570031023</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.634586111227906</v>
+        <v>-2.683679631312928</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.920726222651452</v>
+        <v>1.572309330045187</v>
       </c>
     </row>
     <row r="1893">
@@ -45087,19 +45087,19 @@
         <v>3.768951674611568</v>
       </c>
       <c r="C1893" t="n">
-        <v>3.507211593626832</v>
+        <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.1379100552102</v>
+        <v>-10.34227067851787</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.5483088527709956</v>
+        <v>-0.9490138826493135</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.634586111227906</v>
+        <v>-2.683679631312928</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.926459926890089</v>
+        <v>1.578043034283823</v>
       </c>
     </row>
     <row r="1894">
@@ -45110,19 +45110,19 @@
         <v>3.728577929955327</v>
       </c>
       <c r="C1894" t="n">
-        <v>3.497474331232967</v>
+        <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.06654366260055</v>
+        <v>-10.27090428590822</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.5294995581210022</v>
+        <v>-0.9302045879993202</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.563219718618258</v>
+        <v>-2.61231323870328</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.959542500062012</v>
+        <v>1.611125607455747</v>
       </c>
     </row>
     <row r="1895">
@@ -45133,19 +45133,19 @@
         <v>3.747702660232413</v>
       </c>
       <c r="C1895" t="n">
-        <v>3.487590849920059</v>
+        <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.973084628615329</v>
+        <v>-10.17744525192299</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.5019994258398195</v>
+        <v>-0.9027044557181374</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.563219718618258</v>
+        <v>-2.61231323870328</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.949659018749105</v>
+        <v>1.601242126142839</v>
       </c>
     </row>
     <row r="1896">
@@ -45156,19 +45156,19 @@
         <v>3.766317079436229</v>
       </c>
       <c r="C1896" t="n">
-        <v>3.485756289420685</v>
+        <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.705842827746931</v>
+        <v>-9.910203451054596</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.3969372659918342</v>
+        <v>-0.7976422958701521</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.563219718618258</v>
+        <v>-2.61231323870328</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.947824458249731</v>
+        <v>1.599407565643466</v>
       </c>
     </row>
     <row r="1897">
@@ -45179,19 +45179,19 @@
         <v>3.78468452131195</v>
       </c>
       <c r="C1897" t="n">
-        <v>3.485455974447225</v>
+        <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.60793578907044</v>
+        <v>-9.812296412378105</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.358074765494699</v>
+        <v>-0.7587797953730169</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.495233968757701</v>
+        <v>-2.544327488842724</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.988315593192604</v>
+        <v>1.639898700586339</v>
       </c>
     </row>
     <row r="1898">
@@ -45202,19 +45202,19 @@
         <v>3.800829354097245</v>
       </c>
       <c r="C1898" t="n">
-        <v>3.486124480592718</v>
+        <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.583982248094483</v>
+        <v>-9.788342871402147</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.347824842958822</v>
+        <v>-0.7485298728371399</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.471280427781744</v>
+        <v>-2.520373947866766</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.003356223923672</v>
+        <v>1.654939331317407</v>
       </c>
     </row>
     <row r="1899">
@@ -45225,19 +45225,19 @@
         <v>3.789311112017773</v>
       </c>
       <c r="C1899" t="n">
-        <v>3.472864164430966</v>
+        <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.319922309771686</v>
+        <v>-9.52428293307935</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.2554611837914553</v>
+        <v>-0.6561662136697732</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.207220489458948</v>
+        <v>-2.25631400954397</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.148531870755598</v>
+        <v>1.800114978149332</v>
       </c>
     </row>
     <row r="1900">
@@ -45248,19 +45248,19 @@
         <v>3.833252747839726</v>
       </c>
       <c r="C1900" t="n">
-        <v>3.470077130770665</v>
+        <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.612842686266848</v>
+        <v>-8.817203309574513</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.02458363195017865</v>
+        <v>-0.3761213979281393</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.207220489458948</v>
+        <v>-2.25631400954397</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.145744837095297</v>
+        <v>1.797327944489031</v>
       </c>
     </row>
     <row r="1901">
@@ -45271,19 +45271,19 @@
         <v>3.83937444738873</v>
       </c>
       <c r="C1901" t="n">
-        <v>3.470420754658507</v>
+        <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.572658387900658</v>
+        <v>-8.777019011208322</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.04100097518449619</v>
+        <v>-0.3597040546938217</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.167036191092757</v>
+        <v>-2.216129711177779</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.170199040002853</v>
+        <v>1.821782147396587</v>
       </c>
     </row>
     <row r="1902">
@@ -45294,19 +45294,19 @@
         <v>3.856161751626476</v>
       </c>
       <c r="C1902" t="n">
-        <v>3.469787575879264</v>
+        <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.409258516961295</v>
+        <v>-8.613619140268959</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.1057277447809986</v>
+        <v>-0.2949772850973194</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.003636320153395</v>
+        <v>-2.052729840238417</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.267605783787227</v>
+        <v>1.919188891180962</v>
       </c>
     </row>
     <row r="1903">
@@ -45317,19 +45317,19 @@
         <v>3.787330429291811</v>
       </c>
       <c r="C1903" t="n">
-        <v>3.477712004717116</v>
+        <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.175777294731695</v>
+        <v>-8.38013791803936</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.2070446625106905</v>
+        <v>-0.1936603673676274</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.770155097923796</v>
+        <v>-1.819248618008818</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.415618945962839</v>
+        <v>2.067202053356573</v>
       </c>
     </row>
     <row r="1904">
@@ -45340,19 +45340,19 @@
         <v>3.801637122785788</v>
       </c>
       <c r="C1904" t="n">
-        <v>3.474819794404157</v>
+        <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.026110903724181</v>
+        <v>-8.230471527031845</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.2640190086007372</v>
+        <v>-0.1366860212775807</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.67725160668126</v>
+        <v>-1.726345126766282</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.468468830395401</v>
+        <v>2.120051937789135</v>
       </c>
     </row>
     <row r="1905">
@@ -45363,19 +45363,19 @@
         <v>3.763182248390428</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.470187281151184</v>
+        <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.893835430093294</v>
+        <v>-8.098196053400958</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.3122966848001187</v>
+        <v>-0.08840834507819872</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.544976133050374</v>
+        <v>-1.594069653135396</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.54320160132096</v>
+        <v>2.194784708714694</v>
       </c>
     </row>
     <row r="1906">
@@ -45386,19 +45386,19 @@
         <v>3.784718794105952</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.473002341838821</v>
+        <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.738097097533553</v>
+        <v>-7.942457720841216</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.3774070785116521</v>
+        <v>-0.02329795136666535</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.389237800490632</v>
+        <v>-1.438331320575654</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.639459661544441</v>
+        <v>2.291042768938176</v>
       </c>
     </row>
     <row r="1907">
@@ -45409,19 +45409,19 @@
         <v>3.753882571960987</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.485908683062479</v>
+        <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.489097298849972</v>
+        <v>-7.693457922157635</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.4899133392087434</v>
+        <v>0.08920830933042589</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.389237800490632</v>
+        <v>-1.438331320575654</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.6523660027681</v>
+        <v>2.303949110161835</v>
       </c>
     </row>
     <row r="1908">
@@ -45432,19 +45432,19 @@
         <v>3.692931855607646</v>
       </c>
       <c r="C1908" t="n">
-        <v>3.357932753463261</v>
+        <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.594687288623076</v>
+        <v>-7.79904791193074</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.3197014137002827</v>
+        <v>-0.08100361617803475</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.494827790263736</v>
+        <v>-1.543921310348759</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.461036079305019</v>
+        <v>2.112619186698754</v>
       </c>
     </row>
     <row r="1909">
@@ -45455,19 +45455,19 @@
         <v>3.770422583987903</v>
       </c>
       <c r="C1909" t="n">
-        <v>3.406477095340347</v>
+        <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.613422190741673</v>
+        <v>-7.817782814049337</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.3607517947299304</v>
+        <v>-0.03995323514838711</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.500423799923868</v>
+        <v>-1.54951732000889</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.506222815386026</v>
+        <v>2.157805922779761</v>
       </c>
     </row>
     <row r="1910">
@@ -45478,19 +45478,19 @@
         <v>3.760333686710812</v>
       </c>
       <c r="C1910" t="n">
-        <v>3.286598172652179</v>
+        <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.465482149334074</v>
+        <v>-7.669842772641737</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.3000488886048025</v>
+        <v>-0.100656141273515</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.48010288401531</v>
+        <v>-1.529196404100332</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.398536442242993</v>
+        <v>2.050119549636728</v>
       </c>
     </row>
     <row r="1911">
@@ -45501,19 +45501,19 @@
         <v>3.723566229409205</v>
       </c>
       <c r="C1911" t="n">
-        <v>3.277884186398701</v>
+        <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.412512627080085</v>
+        <v>-7.616873250387749</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.3125227112529196</v>
+        <v>-0.08818231862539783</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.427133361761321</v>
+        <v>-1.476226881846344</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.421604169341909</v>
+        <v>2.073187276735643</v>
       </c>
     </row>
     <row r="1912">
@@ -45524,19 +45524,19 @@
         <v>3.729969716098109</v>
       </c>
       <c r="C1912" t="n">
-        <v>3.270923574303608</v>
+        <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.368964220309395</v>
+        <v>-7.573324843617058</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.3229814618661027</v>
+        <v>-0.07772356801221481</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.427133361761321</v>
+        <v>-1.476226881846344</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.414643557246816</v>
+        <v>2.06622666464055</v>
       </c>
     </row>
     <row r="1913">
@@ -45547,19 +45547,19 @@
         <v>3.782922533493419</v>
       </c>
       <c r="C1913" t="n">
-        <v>3.285385928684751</v>
+        <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.126815826855537</v>
+        <v>-7.3311764501632</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.434303173628789</v>
+        <v>0.03359814375047154</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.427133361761321</v>
+        <v>-1.476226881846344</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.429105911627959</v>
+        <v>2.080689019021693</v>
       </c>
     </row>
     <row r="1914">
@@ -45570,19 +45570,19 @@
         <v>3.828551486722816</v>
       </c>
       <c r="C1914" t="n">
-        <v>3.279918049143946</v>
+        <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.018556689733015</v>
+        <v>-7.222917313040679</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.4721389489369927</v>
+        <v>0.07143391905867524</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.427133361761321</v>
+        <v>-1.476226881846344</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.423638032087154</v>
+        <v>2.075221139480888</v>
       </c>
     </row>
     <row r="1915">
@@ -45593,19 +45593,19 @@
         <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
-        <v>3.277416143154523</v>
+        <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.895265554915884</v>
+        <v>-7.099626178223548</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5189534968744218</v>
+        <v>0.1182484669961044</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.303842226944191</v>
+        <v>-1.352935747029213</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.495110806988009</v>
+        <v>2.146693914381743</v>
       </c>
     </row>
     <row r="1916">
@@ -45616,19 +45616,19 @@
         <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
-        <v>3.285117121391848</v>
+        <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.874116356012441</v>
+        <v>-7.078476979320104</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5351141546731246</v>
+        <v>0.1344091247948072</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.282693028040748</v>
+        <v>-1.33178654812577</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.5155013045674</v>
+        <v>2.167084411961135</v>
       </c>
     </row>
     <row r="1917">
@@ -45639,19 +45639,19 @@
         <v>3.748328408318093</v>
       </c>
       <c r="C1917" t="n">
-        <v>3.280897829738899</v>
+        <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.630350914028996</v>
+        <v>-6.83471153733666</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.6284010398135531</v>
+        <v>0.2276960099352352</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.282693028040748</v>
+        <v>-1.33178654812577</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.51128201291445</v>
+        <v>2.162865120308185</v>
       </c>
     </row>
     <row r="1918">
@@ -45662,19 +45662,19 @@
         <v>3.824311233057526</v>
       </c>
       <c r="C1918" t="n">
-        <v>3.283022143658915</v>
+        <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.528588093751702</v>
+        <v>-6.732948717059365</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.671230481844487</v>
+        <v>0.2705254519661695</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.269473959648319</v>
+        <v>-1.318567479733341</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.521337767869924</v>
+        <v>2.172920875263658</v>
       </c>
     </row>
     <row r="1919">
@@ -45685,19 +45685,19 @@
         <v>3.826354974279186</v>
       </c>
       <c r="C1919" t="n">
-        <v>3.275764218642617</v>
+        <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.278737699802627</v>
+        <v>-6.483098323110291</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.763912714407819</v>
+        <v>0.3632076845295011</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.269473959648319</v>
+        <v>-1.318567479733341</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.514079842853626</v>
+        <v>2.165662950247361</v>
       </c>
     </row>
     <row r="1920">
@@ -45708,19 +45708,19 @@
         <v>3.835957987011499</v>
       </c>
       <c r="C1920" t="n">
-        <v>3.279363342163266</v>
+        <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.102845607335194</v>
+        <v>-6.307206230642858</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8378686749154407</v>
+        <v>0.4371636450371228</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.269473959648319</v>
+        <v>-1.318567479733341</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.517678966374275</v>
+        <v>2.169262073768009</v>
       </c>
     </row>
     <row r="1921">
@@ -45731,19 +45731,19 @@
         <v>3.780933911392987</v>
       </c>
       <c r="C1921" t="n">
-        <v>3.292690848217819</v>
+        <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.931399144312731</v>
+        <v>-6.135759767620395</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9197747661789801</v>
+        <v>0.5190697363006618</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.098027496625856</v>
+        <v>-1.147121016710878</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.633874350242306</v>
+        <v>2.285457457636041</v>
       </c>
     </row>
     <row r="1922">
@@ -45754,19 +45754,19 @@
         <v>3.773765222632782</v>
       </c>
       <c r="C1922" t="n">
-        <v>3.291711325834116</v>
+        <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.857109578574391</v>
+        <v>-6.061470201882056</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9485110700906128</v>
+        <v>0.5478060402122944</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.023737930887516</v>
+        <v>-1.072831450972539</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.677468567301607</v>
+        <v>2.329051674695342</v>
       </c>
     </row>
     <row r="1923">
@@ -45777,19 +45777,19 @@
         <v>3.764617879883074</v>
       </c>
       <c r="C1923" t="n">
-        <v>3.296406126888434</v>
+        <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.793473836340457</v>
+        <v>-5.997834459648121</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.9786601680385036</v>
+        <v>0.5779551381601857</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.9601021886535818</v>
+        <v>-1.009195708738604</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.720344813696285</v>
+        <v>2.37192792109002</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074784</v>
+        <v>3.798814771074785</v>
       </c>
       <c r="C1924" t="n">
-        <v>3.277600385672229</v>
+        <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.682047077014537</v>
+        <v>-5.886407700322201</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.004425130552667</v>
+        <v>0.6037201006743493</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.9601021886535818</v>
+        <v>-1.009195708738604</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.701539072480081</v>
+        <v>2.353122179873815</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242295</v>
+        <v>3.797694884242296</v>
       </c>
       <c r="C1925" t="n">
-        <v>3.279343462297107</v>
+        <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.441616580209677</v>
+        <v>-5.645977203517341</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.102340405899489</v>
+        <v>0.7016353760211711</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.7196716918487215</v>
+        <v>-0.7687652119337436</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.847540447187874</v>
+        <v>2.499123554581609</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367686</v>
+        <v>3.821593509367687</v>
       </c>
       <c r="C1926" t="n">
-        <v>3.283272776131927</v>
+        <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.369374012038482</v>
+        <v>-5.573734635346146</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.135166747002787</v>
+        <v>0.7344617171244692</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.7196716918487215</v>
+        <v>-0.7687652119337436</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.851469761022694</v>
+        <v>2.503052868416429</v>
       </c>
     </row>
     <row r="1927">
@@ -45869,19 +45869,19 @@
         <v>3.822326997879967</v>
       </c>
       <c r="C1927" t="n">
-        <v>3.283951360049267</v>
+        <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.316375689757094</v>
+        <v>-5.520736313064758</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.157044659832682</v>
+        <v>0.7563396299543643</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.6643354328467826</v>
+        <v>-0.7134289529318047</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.885350100341197</v>
+        <v>2.536933207734932</v>
       </c>
     </row>
     <row r="1928">
@@ -45892,19 +45892,19 @@
         <v>3.84861662650234</v>
       </c>
       <c r="C1928" t="n">
-        <v>3.28094943126926</v>
+        <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.207570804277367</v>
+        <v>-5.411931427585031</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.197564685244566</v>
+        <v>0.7968596553662484</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.6643354328467826</v>
+        <v>-0.7134289529318047</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.882348171561191</v>
+        <v>2.533931278954926</v>
       </c>
     </row>
     <row r="1929">
@@ -45915,19 +45915,19 @@
         <v>3.818668951675941</v>
       </c>
       <c r="C1929" t="n">
-        <v>3.282528468279875</v>
+        <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.987550006240356</v>
+        <v>-5.191910629548021</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.287152041469985</v>
+        <v>0.8864470115916667</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.5231155877788024</v>
+        <v>-0.5722091078638245</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.968659115612593</v>
+        <v>2.620242223006328</v>
       </c>
     </row>
     <row r="1930">
@@ -45938,19 +45938,19 @@
         <v>3.843274527539952</v>
       </c>
       <c r="C1930" t="n">
-        <v>3.298422651081698</v>
+        <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.854682317177079</v>
+        <v>-5.059042940484743</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.356193299897119</v>
+        <v>0.955488270018801</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.5231155877788024</v>
+        <v>-0.5722091078638245</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.984553298414417</v>
+        <v>2.636136405808151</v>
       </c>
     </row>
     <row r="1931">
@@ -45961,19 +45961,19 @@
         <v>3.845047386496261</v>
       </c>
       <c r="C1931" t="n">
-        <v>3.299568495522</v>
+        <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.73450923381258</v>
+        <v>-4.938869857120245</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.40540837768322</v>
+        <v>1.004703347804903</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.4029425044143035</v>
+        <v>-0.4520360244993256</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.057802992873418</v>
+        <v>2.709386100267153</v>
       </c>
     </row>
     <row r="1932">
@@ -45984,19 +45984,19 @@
         <v>3.791273551576998</v>
       </c>
       <c r="C1932" t="n">
-        <v>3.30965659808344</v>
+        <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.589837088712843</v>
+        <v>-4.794197712020507</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.473365338284555</v>
+        <v>1.072660308406237</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.258270359314566</v>
+        <v>-0.3073638793995881</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.1546943824947</v>
+        <v>2.806277489888435</v>
       </c>
     </row>
     <row r="1933">
@@ -46007,19 +46007,19 @@
         <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
-        <v>3.295694089484865</v>
+        <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.649711916070535</v>
+        <v>-4.854072539378199</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.435452898742904</v>
+        <v>1.034747868864586</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.3181451866722582</v>
+        <v>-0.3672387067572803</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.104806977481511</v>
+        <v>2.756390084875245</v>
       </c>
     </row>
     <row r="1934">
@@ -46030,19 +46030,19 @@
         <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
-        <v>3.318094582807432</v>
+        <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.562912418291527</v>
+        <v>-4.767273041599191</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.492573191177074</v>
+        <v>1.091868161298756</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.3181451866722582</v>
+        <v>-0.3672387067572803</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.127207470804077</v>
+        <v>2.778790578197811</v>
       </c>
     </row>
     <row r="1935">
@@ -46053,19 +46053,19 @@
         <v>3.729146398430695</v>
       </c>
       <c r="C1935" t="n">
-        <v>3.318166984180844</v>
+        <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.565382124753333</v>
+        <v>-4.769742748060997</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.491657709965763</v>
+        <v>1.090952680087445</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.3206148931340643</v>
+        <v>-0.3697084132190864</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.125798048300406</v>
+        <v>2.77738115569414</v>
       </c>
     </row>
     <row r="1936">
@@ -46076,19 +46076,19 @@
         <v>3.743220196003602</v>
       </c>
       <c r="C1936" t="n">
-        <v>3.329173906655546</v>
+        <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.633752311077343</v>
+        <v>-4.838112934385007</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.475316557910861</v>
+        <v>1.074611528032543</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.3113391940978494</v>
+        <v>-0.3604327141828715</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.142370390196836</v>
+        <v>2.793953497590571</v>
       </c>
     </row>
     <row r="1937">
@@ -46099,19 +46099,19 @@
         <v>3.71417913950837</v>
       </c>
       <c r="C1937" t="n">
-        <v>3.319610615287437</v>
+        <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.64754036392439</v>
+        <v>-4.851900987232054</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.460238045403934</v>
+        <v>1.059533015525616</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.3113391940978494</v>
+        <v>-0.3604327141828715</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.132807098828728</v>
+        <v>2.784390206222462</v>
       </c>
     </row>
     <row r="1938">
@@ -46122,19 +46122,19 @@
         <v>3.710906731417705</v>
       </c>
       <c r="C1938" t="n">
-        <v>3.144320180327824</v>
+        <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.678533523253095</v>
+        <v>-4.882894146560759</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.272550346712839</v>
+        <v>0.8718453168345206</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.3113391940978494</v>
+        <v>-0.3604327141828715</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.957516663869114</v>
+        <v>2.609099771262849</v>
       </c>
     </row>
     <row r="1939">
@@ -46145,19 +46145,19 @@
         <v>3.746042526205901</v>
       </c>
       <c r="C1939" t="n">
-        <v>3.148887412319612</v>
+        <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.503059263460626</v>
+        <v>-4.707419886768291</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.347307282621614</v>
+        <v>0.946602252743296</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.3113391940978494</v>
+        <v>-0.3604327141828715</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.962083895860902</v>
+        <v>2.613667003254637</v>
       </c>
     </row>
     <row r="1940">
@@ -46168,19 +46168,19 @@
         <v>3.765024323225446</v>
       </c>
       <c r="C1940" t="n">
-        <v>3.124629441080819</v>
+        <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.613995516101875</v>
+        <v>-4.81835613940954</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.278674810326321</v>
+        <v>0.8779697804480033</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.3113391940978494</v>
+        <v>-0.3604327141828715</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.937825924622109</v>
+        <v>2.589409032015844</v>
       </c>
     </row>
     <row r="1941">
@@ -46191,19 +46191,19 @@
         <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
-        <v>3.127760826300724</v>
+        <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.580331970629593</v>
+        <v>-4.784692593937257</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.29527161373514</v>
+        <v>0.8945665838568218</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.2776756486255675</v>
+        <v>-0.3267691687105896</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.961155437125384</v>
+        <v>2.612738544519118</v>
       </c>
     </row>
     <row r="1942">
@@ -46214,19 +46214,19 @@
         <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
-        <v>3.137933212732857</v>
+        <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.52047935142587</v>
+        <v>-4.724839974733534</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.329385047848761</v>
+        <v>0.9286800179704435</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.2776756486255675</v>
+        <v>-0.3267691687105896</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.971327823557516</v>
+        <v>2.622910930951251</v>
       </c>
     </row>
     <row r="1943">
@@ -46237,19 +46237,19 @@
         <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
-        <v>3.132879483306717</v>
+        <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.434235888399492</v>
+        <v>-4.638596511707156</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.358828703633173</v>
+        <v>0.9581236737548549</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.2776756486255675</v>
+        <v>-0.3267691687105896</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.966274094131377</v>
+        <v>2.617857201525111</v>
       </c>
     </row>
     <row r="1944">
@@ -46260,19 +46260,19 @@
         <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
-        <v>3.124655258751242</v>
+        <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.479542707798472</v>
+        <v>-4.683903331106136</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.332481751318106</v>
+        <v>0.9317767214397885</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.3184858116347983</v>
+        <v>-0.3675793317198204</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.933563771770364</v>
+        <v>2.585146879164098</v>
       </c>
     </row>
     <row r="1945">
@@ -46283,19 +46283,19 @@
         <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
-        <v>3.125207131784344</v>
+        <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.508575812500773</v>
+        <v>-4.712936435808437</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.321420382470287</v>
+        <v>0.9207153525919696</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.3184858116347983</v>
+        <v>-0.3675793317198204</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.934115644803465</v>
+        <v>2.5856987521972</v>
       </c>
     </row>
     <row r="1946">
@@ -46306,19 +46306,19 @@
         <v>3.733390600809497</v>
       </c>
       <c r="C1946" t="n">
-        <v>3.05447982367571</v>
+        <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.415765331049913</v>
+        <v>-4.620125954357578</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.287817266941997</v>
+        <v>0.887112237063679</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.225675330183939</v>
+        <v>-0.2747688502689611</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.919074625565346</v>
+        <v>2.570657732959081</v>
       </c>
     </row>
     <row r="1947">
@@ -46329,19 +46329,19 @@
         <v>3.748285816560425</v>
       </c>
       <c r="C1947" t="n">
-        <v>3.05635329960031</v>
+        <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.460154800379341</v>
+        <v>-4.664515423687005</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.271934955134827</v>
+        <v>0.871229925256509</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.2700647995133666</v>
+        <v>-0.3191583195983888</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.894314419892291</v>
+        <v>2.545897527286025</v>
       </c>
     </row>
     <row r="1948">
@@ -46352,19 +46352,19 @@
         <v>3.721077195472738</v>
       </c>
       <c r="C1948" t="n">
-        <v>3.051429008112033</v>
+        <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.347483582143091</v>
+        <v>-4.551844205450755</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.31207915094105</v>
+        <v>0.911374121062732</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.1573935812771164</v>
+        <v>-0.2064871013621385</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.956992859345764</v>
+        <v>2.608575966739498</v>
       </c>
     </row>
     <row r="1949">
@@ -46375,19 +46375,19 @@
         <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
-        <v>3.056920303942701</v>
+        <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.235106580960418</v>
+        <v>-4.439467204268082</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.362521247244786</v>
+        <v>0.9618162173664684</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.1573935812771164</v>
+        <v>-0.2064871013621385</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.962484155176431</v>
+        <v>2.614067262570166</v>
       </c>
     </row>
     <row r="1950">
@@ -46398,19 +46398,19 @@
         <v>3.689597840498865</v>
       </c>
       <c r="C1950" t="n">
-        <v>3.06841750571124</v>
+        <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.26288697886177</v>
+        <v>-4.467247602169435</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.362906289852784</v>
+        <v>0.9622012599744665</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.1851739791784695</v>
+        <v>-0.2342674992634916</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.957313118204158</v>
+        <v>2.608896225597893</v>
       </c>
     </row>
     <row r="1951">
@@ -46421,19 +46421,19 @@
         <v>3.643069621705325</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.906773225711893</v>
+        <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.345888259887049</v>
+        <v>-4.550248883194714</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.168061497443326</v>
+        <v>0.7673564675650082</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.2037448637056433</v>
+        <v>-0.2528383837906654</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.784526307488507</v>
+        <v>2.436109414882242</v>
       </c>
     </row>
     <row r="1952">
@@ -46444,19 +46444,19 @@
         <v>3.68271631072927</v>
       </c>
       <c r="C1952" t="n">
-        <v>3.026922886431099</v>
+        <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.45450233833038</v>
+        <v>-4.658862961638045</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.244765526785199</v>
+        <v>0.8440604969068812</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.2037448637056433</v>
+        <v>-0.2528383837906654</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.904675968207713</v>
+        <v>2.556259075601448</v>
       </c>
     </row>
     <row r="1953">
@@ -46467,19 +46467,19 @@
         <v>3.733012441190769</v>
       </c>
       <c r="C1953" t="n">
-        <v>3.041435912533422</v>
+        <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.419093300082237</v>
+        <v>-4.623453923389902</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.273442168186779</v>
+        <v>0.8727371383084614</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.2037448637056433</v>
+        <v>-0.2528383837906654</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.919188994310036</v>
+        <v>2.570772101703771</v>
       </c>
     </row>
     <row r="1954">
@@ -46490,19 +46490,19 @@
         <v>3.741174069913426</v>
       </c>
       <c r="C1954" t="n">
-        <v>3.03885535387579</v>
+        <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.380709637524086</v>
+        <v>-4.585070260831751</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.286215074552409</v>
+        <v>0.8855100446740907</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.1653612011474921</v>
+        <v>-0.2144547212325142</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.939638633187295</v>
+        <v>2.59122174058103</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532486</v>
+        <v>3.751147197532487</v>
       </c>
       <c r="C1955" t="n">
-        <v>3.035584382721092</v>
+        <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.20359330748892</v>
+        <v>-4.407953930796585</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.353790635411777</v>
+        <v>0.9530856055334589</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.1653612011474921</v>
+        <v>-0.2144547212325142</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.936367662032597</v>
+        <v>2.587950769426332</v>
       </c>
     </row>
     <row r="1956">
@@ -46536,19 +46536,19 @@
         <v>3.741328448793904</v>
       </c>
       <c r="C1956" t="n">
-        <v>3.036267774483005</v>
+        <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.248685552322466</v>
+        <v>-4.45304617563013</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.336437129240272</v>
+        <v>0.9357320993619538</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.2272572443168819</v>
+        <v>-0.276350764401904</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.899913427892876</v>
+        <v>2.551496535286611</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011236</v>
+        <v>3.750729377011237</v>
       </c>
       <c r="C1957" t="n">
-        <v>3.03005474978942</v>
+        <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.069310131083698</v>
+        <v>-4.416018863561854</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.401974273042193</v>
+        <v>0.9443299994956786</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.0704804861461632</v>
+        <v>-0.2858513296539649</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.987766458101722</v>
+        <v>2.539583171441789</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.71699171898223</v>
+        <v>3.716991718982231</v>
       </c>
       <c r="C1958" t="n">
-        <v>3.010862205121009</v>
+        <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.114324344604304</v>
+        <v>-4.46103307708246</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.36477604296554</v>
+        <v>0.907131769419026</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.1008293814607678</v>
+        <v>-0.3162002249685695</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.950364576244549</v>
+        <v>2.502181289584616</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.73702660850954</v>
+        <v>3.737026608509541</v>
       </c>
       <c r="C1959" t="n">
-        <v>3.016553767459955</v>
+        <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.381328854876739</v>
+        <v>-4.728037587354895</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.263665801195512</v>
+        <v>0.8060215276489977</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.2951924195037164</v>
+        <v>-0.510563263011518</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.839438315757726</v>
+        <v>2.391255029097792</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.70230945476081</v>
+        <v>3.702309454760811</v>
       </c>
       <c r="C1960" t="n">
-        <v>3.015757689356457</v>
+        <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.482526636313912</v>
+        <v>-4.829235368792068</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.222390610517145</v>
+        <v>0.7647463369706302</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.3636012330490356</v>
+        <v>-0.5789720765568371</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.797596949527036</v>
+        <v>2.349413662867102</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815455</v>
+        <v>3.705571661815456</v>
       </c>
       <c r="C1961" t="n">
-        <v>3.013357650910773</v>
+        <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.45005105014314</v>
+        <v>-4.796759782621296</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.23298080653977</v>
+        <v>0.7753365329932558</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.3636012330490356</v>
+        <v>-0.5789720765568371</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.795196911081352</v>
+        <v>2.347013624421419</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378099</v>
+        <v>3.7095104433781</v>
       </c>
       <c r="C1962" t="n">
-        <v>3.009882370119018</v>
+        <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.431012922435842</v>
+        <v>-4.777721654913998</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.237120776830934</v>
+        <v>0.7794765032844195</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.4217848443802301</v>
+        <v>-0.6371556878880317</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.75681146349088</v>
+        <v>2.308628176830947</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.73106447313125</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
-        <v>3.187464239057699</v>
+        <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.462139553586461</v>
+        <v>-4.808848286064617</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.402251993309367</v>
+        <v>0.9446077197628528</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.4217848443802301</v>
+        <v>-0.6371556878880317</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.934393332429561</v>
+        <v>2.486210045769628</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067865</v>
+        <v>3.722447362067867</v>
       </c>
       <c r="C1964" t="n">
-        <v>3.188297568043832</v>
+        <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.476006314920379</v>
+        <v>-4.822715047398535</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.397538617761934</v>
+        <v>0.9398943442154191</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.4596427611140531</v>
+        <v>-0.6750136046218547</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.912511911375401</v>
+        <v>2.464328624715467</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.787425580789123</v>
       </c>
       <c r="C1965" t="n">
-        <v>3.194306098440758</v>
+        <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.431202143380449</v>
+        <v>-4.777910875858605</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.421468816774832</v>
+        <v>0.963824543228317</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.4596427611140531</v>
+        <v>-0.6750136046218547</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.918520441772327</v>
+        <v>2.470337155112393</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519908</v>
+        <v>3.78150125051991</v>
       </c>
       <c r="C1966" t="n">
-        <v>3.27345874623278</v>
+        <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.283459173145446</v>
+        <v>-4.630167905623602</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.559718652660854</v>
+        <v>1.10207437911434</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.2918354038791699</v>
+        <v>-0.5072062473869715</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.098357503905278</v>
+        <v>2.650174217245346</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.80224592918117</v>
+        <v>3.802245929181172</v>
       </c>
       <c r="C1967" t="n">
-        <v>3.276252367764261</v>
+        <v>2.965833206713181</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.385473855676667</v>
+        <v>-4.732182588154823</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.521706401179847</v>
+        <v>1.072603747137505</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.2918354038791699</v>
+        <v>-0.5072062473869715</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.101151125436759</v>
+        <v>2.661509458280999</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394731</v>
+        <v>3.805608985394732</v>
       </c>
       <c r="C1968" t="n">
-        <v>3.27691471615592</v>
+        <v>2.96649555510484</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.379321149623883</v>
+        <v>-4.726029882102039</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.524829831992619</v>
+        <v>1.075727177950277</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.2856826978263856</v>
+        <v>-0.5010535413341872</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.105505097460088</v>
+        <v>2.665863430304327</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890609</v>
+        <v>3.798239794890611</v>
       </c>
       <c r="C1969" t="n">
-        <v>3.27599519289603</v>
+        <v>2.96557603184495</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.396130447774385</v>
+        <v>-4.742839180252541</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.517186589472528</v>
+        <v>1.068083935430186</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.3024919959768873</v>
+        <v>-0.5178628394846889</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.094499995309897</v>
+        <v>2.654858328154137</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798425</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
-        <v>3.342330746692851</v>
+        <v>3.031911585641771</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.333832448998263</v>
+        <v>-4.680541181476419</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.608441342779798</v>
+        <v>1.159338688737456</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.3024919959768873</v>
+        <v>-0.5178628394846889</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.160835549106719</v>
+        <v>2.721193881950958</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992191</v>
+        <v>3.848729139992193</v>
       </c>
       <c r="C1971" t="n">
-        <v>3.050911619082249</v>
+        <v>2.740492458031169</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.132042251333105</v>
+        <v>-4.478750983811261</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.39773829423526</v>
+        <v>0.9486356401929172</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.1044738038077329</v>
+        <v>-0.3198446473155345</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.988227336797609</v>
+        <v>2.548585669641848</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852421</v>
+        <v>3.841444817852423</v>
       </c>
       <c r="C1972" t="n">
-        <v>3.121201851404424</v>
+        <v>2.810782690353344</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.072151569690512</v>
+        <v>-4.418860302168667</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.491984799214472</v>
+        <v>1.04288214517213</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.04458312216513938</v>
+        <v>-0.259953965672941</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.094451978105341</v>
+        <v>2.654810310949579</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319545</v>
+        <v>3.819063300319548</v>
       </c>
       <c r="C1973" t="n">
-        <v>3.135829587520468</v>
+        <v>2.825410426469388</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.169892114315486</v>
+        <v>-4.516600846793642</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.467516317480526</v>
+        <v>1.018413663438184</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.06047240029811957</v>
+        <v>-0.2758432438059212</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.099546147341596</v>
+        <v>2.659904480185835</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489385</v>
+        <v>3.831819032489387</v>
       </c>
       <c r="C1974" t="n">
-        <v>3.134365568345139</v>
+        <v>2.823946407294059</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.346229874438415</v>
+        <v>-4.692938606916571</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.395517194256026</v>
+        <v>0.9464145402136834</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.236810160421049</v>
+        <v>-0.4521810039288506</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.99227947209251</v>
+        <v>2.552637804936749</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397794</v>
+        <v>3.836411672397796</v>
       </c>
       <c r="C1975" t="n">
-        <v>3.132857186385068</v>
+        <v>2.822438025333988</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.269807828006488</v>
+        <v>-4.616516560484644</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.424577630868725</v>
+        <v>0.9754749768263828</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.236810160421049</v>
+        <v>-0.4521810039288506</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.990771090132439</v>
+        <v>2.551129422976678</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024963</v>
+        <v>3.836023391024964</v>
       </c>
       <c r="C1976" t="n">
-        <v>3.132720053820504</v>
+        <v>2.822300892769424</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.22543469636792</v>
+        <v>-4.572143428846076</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.442189750959589</v>
+        <v>0.9930870969172465</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.1924370287824804</v>
+        <v>-0.407807872290282</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.017257836551016</v>
+        <v>2.577616169395255</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863222</v>
+        <v>3.821591150863224</v>
       </c>
       <c r="C1977" t="n">
-        <v>3.132720053820504</v>
+        <v>2.822300892769424</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.217480726073148</v>
+        <v>-4.564189458551303</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.445371339077498</v>
+        <v>0.9962686850351554</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.1924370287824804</v>
+        <v>-0.407807872290282</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.017257836551016</v>
+        <v>2.577616169395255</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947581</v>
+        <v>3.833040181947583</v>
       </c>
       <c r="C1978" t="n">
-        <v>3.139101810848309</v>
+        <v>2.828682649797228</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.169824995512092</v>
+        <v>-4.516533727990248</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.470815388329725</v>
+        <v>1.021712734287382</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.1447812982214247</v>
+        <v>-0.3601521417292264</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.052233031915454</v>
+        <v>2.612591364759692</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326873</v>
+        <v>3.822707244326875</v>
       </c>
       <c r="C1979" t="n">
-        <v>3.143994184223033</v>
+        <v>2.833575023171953</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.042140685717795</v>
+        <v>-4.388849418195951</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.526781485622168</v>
+        <v>1.077678831579825</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.01709698842712826</v>
+        <v>-0.2324678319349299</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.133735991166757</v>
+        <v>2.694094324010995</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314548</v>
+        <v>3.82883791131455</v>
       </c>
       <c r="C1980" t="n">
-        <v>3.130748856698906</v>
+        <v>2.820329695647825</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.102807276120185</v>
+        <v>-4.449516008598341</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.489269521937084</v>
+        <v>1.040166867894742</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.09879530514566193</v>
+        <v>-0.3141661486534636</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.071471673611509</v>
+        <v>2.631830006455747</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690023</v>
+        <v>3.816866067690025</v>
       </c>
       <c r="C1981" t="n">
-        <v>3.134846559309534</v>
+        <v>2.824427398258454</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.057968874511786</v>
+        <v>-4.404677606989942</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.511302585191072</v>
+        <v>1.06219993114873</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.09425187220079245</v>
+        <v>-0.3096227157085941</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.078295435989059</v>
+        <v>2.638653768833298</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674307</v>
+        <v>3.817961388674309</v>
       </c>
       <c r="C1982" t="n">
-        <v>3.139007498940612</v>
+        <v>2.828588337889532</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.158727510268784</v>
+        <v>-4.50543624274694</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.475160070519351</v>
+        <v>1.026057416477008</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.1830774409277979</v>
+        <v>-0.3984482844355995</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.029161034383934</v>
+        <v>2.589519367228172</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826713779163217</v>
+        <v>3.826713779163219</v>
       </c>
       <c r="C1983" t="n">
-        <v>3.144887101468449</v>
+        <v>2.834467940417369</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.114524673182884</v>
+        <v>-4.46123340566104</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.498720807881549</v>
+        <v>1.049618153839206</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.1388746038418974</v>
+        <v>-0.3542454473496991</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.061562339163311</v>
+        <v>2.621920672007549</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022901</v>
+        <v>3.838228663022903</v>
       </c>
       <c r="C1984" t="n">
-        <v>3.143297101937697</v>
+        <v>2.832877940886616</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.151503700846327</v>
+        <v>-4.498212433324483</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.482339197285419</v>
+        <v>1.033236543243076</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.1019007020505669</v>
+        <v>-0.3172715455583686</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.082156680707357</v>
+        <v>2.642515013551595</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042136</v>
+        <v>3.863924114042137</v>
       </c>
       <c r="C1985" t="n">
-        <v>3.194544867120737</v>
+        <v>2.884125706069656</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.171561779711167</v>
+        <v>-4.518270512189323</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.525563730922523</v>
+        <v>1.07646107688018</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.1019007020505669</v>
+        <v>-0.3172715455583686</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.133404445890397</v>
+        <v>2.693762778734635</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865367715078278</v>
+        <v>3.86536771507828</v>
       </c>
       <c r="C1986" t="n">
-        <v>3.19298557171499</v>
+        <v>2.882566410663909</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.131631106533277</v>
+        <v>-4.478339839011433</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.539976704787932</v>
+        <v>1.090874050745589</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.06197002887267655</v>
+        <v>-0.2773408723804782</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.155803554391384</v>
+        <v>2.716161887235622</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232395</v>
+        <v>3.864518876232397</v>
       </c>
       <c r="C1987" t="n">
-        <v>3.18793379995326</v>
+        <v>2.877514638902179</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.080599013810749</v>
+        <v>-4.427307746288905</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.555337770115213</v>
+        <v>1.10623511607287</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.0109379361501486</v>
+        <v>-0.2263087796579503</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.181371038263171</v>
+        <v>2.741729371107409</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842576394162111</v>
+        <v>3.842576394162113</v>
       </c>
       <c r="C1988" t="n">
-        <v>3.205121204045965</v>
+        <v>2.894702042994884</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.015374832683544</v>
+        <v>-4.3620835651617</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.5986148466588</v>
+        <v>1.149512192616457</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.05428624497705703</v>
+        <v>-0.1610845985307446</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.237692951032199</v>
+        <v>2.798051283876438</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840090220639816</v>
+        <v>3.840090220639817</v>
       </c>
       <c r="C1989" t="n">
-        <v>3.201082176345245</v>
+        <v>2.890663015294165</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.97794781261241</v>
+        <v>-4.324656545090566</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.609546626986534</v>
+        <v>1.160443972944191</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.05953778300623869</v>
+        <v>-0.155833060501563</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.236804846148988</v>
+        <v>2.797163178993227</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.84519884274992</v>
+        <v>3.845198842749921</v>
       </c>
       <c r="C1990" t="n">
-        <v>3.202338968676485</v>
+        <v>2.891919807625405</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.998059468647118</v>
+        <v>-4.344768201125274</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.602758756903891</v>
+        <v>1.153656102861548</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.07056512800365788</v>
+        <v>-0.1448057155041438</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.24467804547868</v>
+        <v>2.805036378322919</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828690479393547</v>
+        <v>3.828690479393548</v>
       </c>
       <c r="C1991" t="n">
-        <v>3.362896739697696</v>
+        <v>3.052477578646616</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.944314654219914</v>
+        <v>-4.291023386698069</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.784814453695983</v>
+        <v>1.335711799653641</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.08062843744411985</v>
+        <v>-0.1347424060636818</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.411273802164168</v>
+        <v>2.971632135008407</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813251854714885</v>
+        <v>3.813251854714886</v>
       </c>
       <c r="C1992" t="n">
-        <v>3.483009648915513</v>
+        <v>3.172590487864433</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.920523085613771</v>
+        <v>-4.267231818091927</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.914443990356258</v>
+        <v>1.465341336313915</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.1044200060502621</v>
+        <v>-0.1109508374575395</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.545661652545671</v>
+        <v>3.106019985389909</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.81425976175601</v>
+        <v>3.814259761756011</v>
       </c>
       <c r="C1993" t="n">
-        <v>3.474717624929372</v>
+        <v>3.164298463878292</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.894439001349963</v>
+        <v>-4.241147733828119</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.916585600075639</v>
+        <v>1.467482946033297</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.1044200060502621</v>
+        <v>-0.1109508374575395</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.53736962855953</v>
+        <v>3.097727961403768</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803426852654184</v>
+        <v>3.803426852654185</v>
       </c>
       <c r="C1994" t="n">
-        <v>3.472910820513152</v>
+        <v>3.162491659462071</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.890104698292915</v>
+        <v>-4.236813430771071</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.916512516882238</v>
+        <v>1.467409862839896</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.2560701093694661</v>
+        <v>0.04069926586166439</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.626552886134832</v>
+        <v>3.18691121897907</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796293177717114</v>
+        <v>3.796293177717116</v>
       </c>
       <c r="C1995" t="n">
-        <v>3.490465226239943</v>
+        <v>3.180046065188863</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.881212236899632</v>
+        <v>-4.227920969377788</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.937623907166343</v>
+        <v>1.488521253124</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.2560701093694661</v>
+        <v>0.04069926586166439</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.644107291861623</v>
+        <v>3.204465624705862</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794453975702623</v>
+        <v>3.794453975702625</v>
       </c>
       <c r="C1996" t="n">
-        <v>3.482320273644527</v>
+        <v>3.171901112593447</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.049688353869509</v>
+        <v>-4.396397086347665</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.862088507782976</v>
+        <v>1.412985853740633</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.2281222736528853</v>
+        <v>0.01275143014508362</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.619193637836259</v>
+        <v>3.179551970680497</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795603100539966</v>
+        <v>3.795603100539967</v>
       </c>
       <c r="C1997" t="n">
-        <v>3.463589970832389</v>
+        <v>3.153170809781308</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.351888825007926</v>
+        <v>-3.698597557486082</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.122478016515471</v>
+        <v>1.673375362473128</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.1577742142824746</v>
+        <v>-0.0575966292253271</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.558254499401874</v>
+        <v>3.118612832246112</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784700379389895</v>
+        <v>3.784700379389897</v>
       </c>
       <c r="C1998" t="n">
-        <v>3.454253993329294</v>
+        <v>3.143834832278213</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.329167721324774</v>
+        <v>-3.67587645380293</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.122230480485637</v>
+        <v>1.673127826443294</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.1577742142824746</v>
+        <v>-0.0575966292253271</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.548918521898778</v>
+        <v>3.109276854743017</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783234730534932</v>
+        <v>3.783234730534935</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.613160119180463</v>
+        <v>3.302740958129382</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.469460320861966</v>
+        <v>-3.816169053340122</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.225019566521929</v>
+        <v>1.775916912479586</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.01748161474528193</v>
+        <v>-0.1978892287625197</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.623649088027632</v>
+        <v>3.18400742087187</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779962759401671</v>
+        <v>3.779962759401673</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.650237941674109</v>
+        <v>3.339818780623029</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.624241327640221</v>
+        <v>-3.970950060118377</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.200184986304273</v>
+        <v>1.75108233226193</v>
       </c>
       <c r="F2000" t="n">
-        <v>-0.01588605930919418</v>
+        <v>-0.2312569028169958</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.640706306088593</v>
+        <v>3.201064638932831</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769472653557218</v>
+        <v>3.769472653557221</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.646913297663654</v>
+        <v>3.336494136612574</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.691501771662138</v>
+        <v>-4.038210504140294</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.169956164685051</v>
+        <v>1.720853510642709</v>
       </c>
       <c r="F2001" t="n">
-        <v>-0.08314650333111129</v>
+        <v>-0.298517346838913</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.597025395664988</v>
+        <v>3.157383728509226</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766702530088374</v>
+        <v>3.766702530088376</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.656919451308396</v>
+        <v>3.346500290257315</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.669030237623307</v>
+        <v>-4.015738970101462</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.188950931945326</v>
+        <v>1.739848277902983</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.05255898148485993</v>
+        <v>-0.1628118620229417</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.688454840199312</v>
+        <v>3.24881317304355</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768081101541367</v>
+        <v>3.76808110154137</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.841022583453356</v>
+        <v>3.530603422402275</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.804983245679622</v>
+        <v>-4.151691978157778</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.31867286086776</v>
+        <v>1.869570206825417</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.05255898148485993</v>
+        <v>-0.1628118620229417</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.872557972344272</v>
+        <v>3.43291630518851</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.780796393081655</v>
+        <v>3.437151927579688</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.723290650538015</v>
+        <v>3.535804622669891</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.853683399057854</v>
+        <v>-4.014646830627897</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.181460866601126</v>
+        <v>1.929589466104985</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.003858828106628631</v>
+        <v>-0.02576671449306028</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.725605947401992</v>
+        <v>3.520344593974055</v>
       </c>
     </row>
   </sheetData>
